--- a/项目效益审核表.xlsx
+++ b/项目效益审核表.xlsx
@@ -36,7 +36,6 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>于</author>
-    <author>Administrator</author>
     <author>51458</author>
     <author>Admin</author>
   </authors>
@@ -470,45 +469,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M38" authorId="1">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">**同财务账面合同履约成本/工程施工成本/机械租赁费数据一致**
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M46" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>于:
-**同财务账面合同履约成本/工程施工成本其他直接费数据一致**</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M61" authorId="1">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>**同财务账面合同履约成本/工程施工成本/间接费数据一致**</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D69" authorId="2">
+    <comment ref="D69" authorId="1">
       <text>
         <r>
           <rPr>
@@ -520,7 +481,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E78" authorId="3">
+    <comment ref="E78" authorId="2">
       <text>
         <r>
           <rPr>
@@ -533,7 +494,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E79" authorId="3">
+    <comment ref="E79" authorId="2">
       <text>
         <r>
           <rPr>
@@ -1181,7 +1142,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1220,13 +1181,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor theme="0" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFADD88D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1618,7 +1585,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1642,16 +1609,16 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1660,85 +1627,85 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
@@ -1752,7 +1719,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3">
@@ -1860,7 +1827,7 @@
     <xf numFmtId="177" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -2027,18 +1994,12 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="43" fontId="6" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="8" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
@@ -2072,10 +2033,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
@@ -2104,12 +2061,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
@@ -2118,6 +2069,9 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
@@ -2184,14 +2138,14 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
@@ -2209,7 +2163,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="43" fontId="6" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="10" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2218,6 +2178,9 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="43" fontId="6" fillId="5" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="7" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="6" fillId="5" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2277,11 +2240,15 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="9" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="10" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2889,9 +2856,9 @@
     <col min="2" max="2" width="21.8181818181818" style="5" customWidth="1"/>
     <col min="3" max="3" width="16.7636363636364" style="5" customWidth="1"/>
     <col min="4" max="4" width="37.7545454545455" style="5" customWidth="1"/>
-    <col min="5" max="5" width="35.0545454545455" style="5" customWidth="1"/>
-    <col min="6" max="6" width="20" style="5" customWidth="1"/>
-    <col min="7" max="7" width="19.1909090909091" style="5" customWidth="1"/>
+    <col min="5" max="5" width="35.0545454545455" style="5" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="20" style="5" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="19.1909090909091" style="5" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="20.9090909090909" style="5" customWidth="1"/>
     <col min="9" max="9" width="25.2545454545455" style="5" customWidth="1"/>
     <col min="10" max="11" width="20.9090909090909" style="5" customWidth="1"/>
@@ -2942,18 +2909,18 @@
       <c r="X1" s="61"/>
       <c r="Y1" s="61"/>
       <c r="Z1" s="61"/>
-      <c r="AA1" s="89"/>
-      <c r="AB1" s="90"/>
-      <c r="AC1" s="90"/>
-      <c r="AD1" s="90"/>
-      <c r="AE1" s="90"/>
-      <c r="AF1" s="90"/>
-      <c r="AG1" s="90"/>
-      <c r="AH1" s="90"/>
-      <c r="AI1" s="90"/>
-      <c r="AJ1" s="90"/>
-      <c r="AK1" s="90"/>
-      <c r="AL1" s="98"/>
+      <c r="AA1" s="86"/>
+      <c r="AB1" s="87"/>
+      <c r="AC1" s="87"/>
+      <c r="AD1" s="87"/>
+      <c r="AE1" s="87"/>
+      <c r="AF1" s="87"/>
+      <c r="AG1" s="87"/>
+      <c r="AH1" s="87"/>
+      <c r="AI1" s="87"/>
+      <c r="AJ1" s="87"/>
+      <c r="AK1" s="87"/>
+      <c r="AL1" s="93"/>
     </row>
     <row r="2" ht="25.5" spans="1:38">
       <c r="A2" s="10"/>
@@ -2982,18 +2949,18 @@
       <c r="X2" s="61"/>
       <c r="Y2" s="61"/>
       <c r="Z2" s="61"/>
-      <c r="AA2" s="91"/>
-      <c r="AB2" s="90"/>
-      <c r="AC2" s="90"/>
-      <c r="AD2" s="90"/>
-      <c r="AE2" s="90"/>
-      <c r="AF2" s="90"/>
-      <c r="AG2" s="90"/>
-      <c r="AH2" s="90"/>
-      <c r="AI2" s="90"/>
-      <c r="AJ2" s="90"/>
-      <c r="AK2" s="90"/>
-      <c r="AL2" s="98"/>
+      <c r="AA2" s="88"/>
+      <c r="AB2" s="87"/>
+      <c r="AC2" s="87"/>
+      <c r="AD2" s="87"/>
+      <c r="AE2" s="87"/>
+      <c r="AF2" s="87"/>
+      <c r="AG2" s="87"/>
+      <c r="AH2" s="87"/>
+      <c r="AI2" s="87"/>
+      <c r="AJ2" s="87"/>
+      <c r="AK2" s="87"/>
+      <c r="AL2" s="93"/>
     </row>
     <row r="3" ht="25.5" spans="1:38">
       <c r="A3" s="11" t="s">
@@ -3026,26 +2993,26 @@
       <c r="P3" s="61"/>
       <c r="Q3" s="61"/>
       <c r="R3" s="61"/>
-      <c r="S3" s="80"/>
-      <c r="T3" s="80"/>
-      <c r="U3" s="80"/>
-      <c r="V3" s="80"/>
-      <c r="W3" s="80"/>
-      <c r="X3" s="80"/>
-      <c r="Y3" s="80"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="78"/>
+      <c r="W3" s="78"/>
+      <c r="X3" s="78"/>
+      <c r="Y3" s="78"/>
       <c r="Z3" s="61"/>
-      <c r="AA3" s="91"/>
-      <c r="AB3" s="90"/>
-      <c r="AC3" s="90"/>
-      <c r="AD3" s="90"/>
-      <c r="AE3" s="90"/>
-      <c r="AF3" s="90"/>
-      <c r="AG3" s="90"/>
-      <c r="AH3" s="90"/>
-      <c r="AI3" s="90"/>
-      <c r="AJ3" s="90"/>
-      <c r="AK3" s="90"/>
-      <c r="AL3" s="98"/>
+      <c r="AA3" s="88"/>
+      <c r="AB3" s="87"/>
+      <c r="AC3" s="87"/>
+      <c r="AD3" s="87"/>
+      <c r="AE3" s="87"/>
+      <c r="AF3" s="87"/>
+      <c r="AG3" s="87"/>
+      <c r="AH3" s="87"/>
+      <c r="AI3" s="87"/>
+      <c r="AJ3" s="87"/>
+      <c r="AK3" s="87"/>
+      <c r="AL3" s="93"/>
     </row>
     <row r="4" ht="14" spans="1:38">
       <c r="A4" s="13"/>
@@ -3081,8 +3048,8 @@
       <c r="O4" s="65"/>
       <c r="P4" s="65"/>
       <c r="Q4" s="65"/>
-      <c r="R4" s="81"/>
-      <c r="S4" s="82" t="s">
+      <c r="R4" s="79"/>
+      <c r="S4" s="80" t="s">
         <v>15</v>
       </c>
       <c r="T4" s="65"/>
@@ -3090,8 +3057,8 @@
       <c r="V4" s="65"/>
       <c r="W4" s="65"/>
       <c r="X4" s="65"/>
-      <c r="Y4" s="81"/>
-      <c r="Z4" s="92" t="s">
+      <c r="Y4" s="79"/>
+      <c r="Z4" s="89" t="s">
         <v>16</v>
       </c>
       <c r="AA4" s="65"/>
@@ -3104,8 +3071,8 @@
       <c r="AH4" s="65"/>
       <c r="AI4" s="65"/>
       <c r="AJ4" s="65"/>
-      <c r="AK4" s="81"/>
-      <c r="AL4" s="99" t="s">
+      <c r="AK4" s="79"/>
+      <c r="AL4" s="94" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3150,61 +3117,61 @@
       <c r="R5" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="S5" s="83" t="s">
+      <c r="S5" s="81" t="s">
         <v>29</v>
       </c>
-      <c r="T5" s="83" t="s">
+      <c r="T5" s="81" t="s">
         <v>30</v>
       </c>
-      <c r="U5" s="83" t="s">
+      <c r="U5" s="81" t="s">
         <v>31</v>
       </c>
-      <c r="V5" s="83" t="s">
+      <c r="V5" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="W5" s="83" t="s">
+      <c r="W5" s="81" t="s">
         <v>33</v>
       </c>
-      <c r="X5" s="83" t="s">
+      <c r="X5" s="81" t="s">
         <v>34</v>
       </c>
-      <c r="Y5" s="83" t="s">
+      <c r="Y5" s="81" t="s">
         <v>35</v>
       </c>
-      <c r="Z5" s="93" t="s">
+      <c r="Z5" s="90" t="s">
         <v>36</v>
       </c>
-      <c r="AA5" s="93" t="s">
+      <c r="AA5" s="90" t="s">
         <v>37</v>
       </c>
-      <c r="AB5" s="93" t="s">
+      <c r="AB5" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="AC5" s="93" t="s">
+      <c r="AC5" s="90" t="s">
         <v>39</v>
       </c>
-      <c r="AD5" s="93" t="s">
+      <c r="AD5" s="90" t="s">
         <v>40</v>
       </c>
-      <c r="AE5" s="93" t="s">
+      <c r="AE5" s="90" t="s">
         <v>41</v>
       </c>
-      <c r="AF5" s="93" t="s">
+      <c r="AF5" s="90" t="s">
         <v>42</v>
       </c>
-      <c r="AG5" s="93" t="s">
+      <c r="AG5" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="AH5" s="93" t="s">
+      <c r="AH5" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="AI5" s="93" t="s">
+      <c r="AI5" s="90" t="s">
         <v>44</v>
       </c>
-      <c r="AJ5" s="93" t="s">
+      <c r="AJ5" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="AK5" s="93" t="s">
+      <c r="AK5" s="90" t="s">
         <v>46</v>
       </c>
       <c r="AL5" s="28"/>
@@ -3240,36 +3207,36 @@
         <f>K6-N6</f>
         <v>0</v>
       </c>
-      <c r="Q6" s="84">
+      <c r="Q6" s="82">
         <f>M6+O6</f>
         <v>0</v>
       </c>
-      <c r="R6" s="84">
+      <c r="R6" s="82">
         <f>M6+N6+O6+P6</f>
         <v>0</v>
       </c>
-      <c r="S6" s="85"/>
-      <c r="T6" s="85"/>
-      <c r="U6" s="85"/>
-      <c r="V6" s="85"/>
-      <c r="W6" s="85"/>
-      <c r="X6" s="85"/>
-      <c r="Y6" s="85"/>
+      <c r="S6" s="83"/>
+      <c r="T6" s="83"/>
+      <c r="U6" s="83"/>
+      <c r="V6" s="83"/>
+      <c r="W6" s="83"/>
+      <c r="X6" s="83"/>
+      <c r="Y6" s="83"/>
       <c r="Z6" s="36">
         <f>SUM(AA6:AJ6)</f>
         <v>0</v>
       </c>
-      <c r="AA6" s="85"/>
-      <c r="AB6" s="85"/>
-      <c r="AC6" s="85"/>
-      <c r="AD6" s="85"/>
-      <c r="AE6" s="85"/>
-      <c r="AF6" s="85"/>
-      <c r="AG6" s="85"/>
-      <c r="AH6" s="85"/>
-      <c r="AI6" s="85"/>
-      <c r="AJ6" s="85"/>
-      <c r="AK6" s="85">
+      <c r="AA6" s="83"/>
+      <c r="AB6" s="83"/>
+      <c r="AC6" s="83"/>
+      <c r="AD6" s="83"/>
+      <c r="AE6" s="83"/>
+      <c r="AF6" s="83"/>
+      <c r="AG6" s="83"/>
+      <c r="AH6" s="83"/>
+      <c r="AI6" s="83"/>
+      <c r="AJ6" s="83"/>
+      <c r="AK6" s="83">
         <f>AB6/1.17*0.17+AC6/1.16*0.16+AD6/1.11*0.11+AE6/1.1*0.1+AF6/1.09*0.09+AI6/1.03*0.03</f>
         <v>0</v>
       </c>
@@ -3310,7 +3277,7 @@
       <c r="P7" s="71"/>
       <c r="Q7" s="71"/>
       <c r="R7" s="72"/>
-      <c r="S7" s="86" t="s">
+      <c r="S7" s="84" t="s">
         <v>53</v>
       </c>
       <c r="T7" s="71"/>
@@ -3319,7 +3286,7 @@
       <c r="W7" s="71"/>
       <c r="X7" s="71"/>
       <c r="Y7" s="72"/>
-      <c r="Z7" s="94" t="s">
+      <c r="Z7" s="91" t="s">
         <v>16</v>
       </c>
       <c r="AA7" s="71"/>
@@ -3376,64 +3343,64 @@
       <c r="R8" s="74" t="s">
         <v>63</v>
       </c>
-      <c r="S8" s="87" t="s">
+      <c r="S8" s="85" t="s">
         <v>64</v>
       </c>
-      <c r="T8" s="87" t="s">
+      <c r="T8" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="U8" s="87" t="s">
+      <c r="U8" s="85" t="s">
         <v>66</v>
       </c>
-      <c r="V8" s="87" t="s">
+      <c r="V8" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="W8" s="87" t="s">
+      <c r="W8" s="85" t="s">
         <v>68</v>
       </c>
-      <c r="X8" s="87" t="s">
+      <c r="X8" s="85" t="s">
         <v>69</v>
       </c>
-      <c r="Y8" s="87" t="s">
+      <c r="Y8" s="85" t="s">
         <v>35</v>
       </c>
-      <c r="Z8" s="95" t="s">
+      <c r="Z8" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="AA8" s="95" t="s">
+      <c r="AA8" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="AB8" s="95" t="s">
+      <c r="AB8" s="92" t="s">
         <v>72</v>
       </c>
-      <c r="AC8" s="95" t="s">
+      <c r="AC8" s="92" t="s">
         <v>73</v>
       </c>
-      <c r="AD8" s="95" t="s">
+      <c r="AD8" s="92" t="s">
         <v>74</v>
       </c>
-      <c r="AE8" s="95" t="s">
+      <c r="AE8" s="92" t="s">
         <v>75</v>
       </c>
-      <c r="AF8" s="95" t="s">
+      <c r="AF8" s="92" t="s">
         <v>76</v>
       </c>
-      <c r="AG8" s="95"/>
-      <c r="AH8" s="95" t="s">
+      <c r="AG8" s="92"/>
+      <c r="AH8" s="92" t="s">
         <v>77</v>
       </c>
-      <c r="AI8" s="95" t="s">
+      <c r="AI8" s="92" t="s">
         <v>78</v>
       </c>
-      <c r="AJ8" s="95" t="s">
+      <c r="AJ8" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="AK8" s="95" t="s">
+      <c r="AK8" s="92" t="s">
         <v>79</v>
       </c>
       <c r="AL8" s="28"/>
     </row>
-    <row r="9" ht="14" spans="1:38">
+    <row r="9" spans="1:38">
       <c r="A9" s="30"/>
       <c r="B9" s="20"/>
       <c r="C9" s="20"/>
@@ -3583,7 +3550,7 @@
       <c r="AK10" s="32">
         <v>36</v>
       </c>
-      <c r="AL10" s="30"/>
+      <c r="AL10" s="95"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A11" s="33"/>
@@ -3597,53 +3564,35 @@
       <c r="G11" s="34"/>
       <c r="H11" s="36"/>
       <c r="I11" s="36"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="75"/>
-      <c r="L11" s="76"/>
-      <c r="M11" s="58"/>
-      <c r="N11" s="58"/>
-      <c r="O11" s="36">
-        <f t="shared" ref="O11:O16" si="0">L11-M11</f>
-        <v>0</v>
-      </c>
-      <c r="P11" s="36">
-        <f t="shared" ref="P11:P16" si="1">K11-N11</f>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="36">
-        <f t="shared" ref="Q11:Q16" si="2">M11+O11</f>
-        <v>0</v>
-      </c>
-      <c r="R11" s="36">
-        <f t="shared" ref="R11:R16" si="3">M11+N11+O11+P11</f>
-        <v>0</v>
-      </c>
-      <c r="S11" s="88">
-        <f t="shared" ref="S11:S16" si="4">SUM(T11:V11)</f>
-        <v>0</v>
-      </c>
-      <c r="T11" s="88"/>
-      <c r="U11" s="88"/>
-      <c r="V11" s="88"/>
-      <c r="W11" s="88"/>
-      <c r="X11" s="88"/>
-      <c r="Y11" s="88"/>
-      <c r="Z11" s="88"/>
-      <c r="AA11" s="88"/>
-      <c r="AB11" s="88"/>
-      <c r="AC11" s="88"/>
-      <c r="AD11" s="88"/>
-      <c r="AE11" s="88"/>
-      <c r="AF11" s="88"/>
-      <c r="AG11" s="88"/>
-      <c r="AH11" s="88"/>
-      <c r="AI11" s="88"/>
-      <c r="AJ11" s="88"/>
-      <c r="AK11" s="85">
-        <f t="shared" ref="AK11:AK16" si="5">AB11/1.17*0.17+AC11/1.16*0.16+AD11/1.11*0.11+AE11/1.1*0.1+AF11/1.09*0.09+AI11/1.03*0.03</f>
-        <v>0</v>
-      </c>
-      <c r="AL11" s="100"/>
+      <c r="J11" s="75"/>
+      <c r="K11" s="36"/>
+      <c r="L11" s="75"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="75"/>
+      <c r="P11" s="75"/>
+      <c r="Q11" s="75"/>
+      <c r="R11" s="75"/>
+      <c r="S11" s="36"/>
+      <c r="T11" s="36"/>
+      <c r="U11" s="36"/>
+      <c r="V11" s="36"/>
+      <c r="W11" s="36"/>
+      <c r="X11" s="36"/>
+      <c r="Y11" s="36"/>
+      <c r="Z11" s="36"/>
+      <c r="AA11" s="36"/>
+      <c r="AB11" s="36"/>
+      <c r="AC11" s="36"/>
+      <c r="AD11" s="36"/>
+      <c r="AE11" s="36"/>
+      <c r="AF11" s="36"/>
+      <c r="AG11" s="36"/>
+      <c r="AH11" s="36"/>
+      <c r="AI11" s="36"/>
+      <c r="AJ11" s="36"/>
+      <c r="AK11" s="36"/>
+      <c r="AL11" s="96"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A12" s="33"/>
@@ -3657,53 +3606,35 @@
       <c r="G12" s="34"/>
       <c r="H12" s="36"/>
       <c r="I12" s="36"/>
-      <c r="J12" s="36"/>
-      <c r="K12" s="75"/>
-      <c r="L12" s="76"/>
-      <c r="M12" s="58"/>
-      <c r="N12" s="58"/>
-      <c r="O12" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P12" s="36">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="36">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R12" s="36">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S12" s="88">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="T12" s="85"/>
-      <c r="U12" s="85"/>
-      <c r="V12" s="85"/>
-      <c r="W12" s="85"/>
-      <c r="X12" s="85"/>
-      <c r="Y12" s="85"/>
-      <c r="Z12" s="85"/>
-      <c r="AA12" s="88"/>
-      <c r="AB12" s="88"/>
-      <c r="AC12" s="88"/>
-      <c r="AD12" s="88"/>
-      <c r="AE12" s="88"/>
-      <c r="AF12" s="88"/>
-      <c r="AG12" s="88"/>
-      <c r="AH12" s="88"/>
-      <c r="AI12" s="88"/>
-      <c r="AJ12" s="88"/>
-      <c r="AK12" s="85">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AL12" s="100"/>
+      <c r="J12" s="75"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="75"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="75"/>
+      <c r="P12" s="75"/>
+      <c r="Q12" s="75"/>
+      <c r="R12" s="75"/>
+      <c r="S12" s="36"/>
+      <c r="T12" s="36"/>
+      <c r="U12" s="36"/>
+      <c r="V12" s="36"/>
+      <c r="W12" s="36"/>
+      <c r="X12" s="36"/>
+      <c r="Y12" s="36"/>
+      <c r="Z12" s="36"/>
+      <c r="AA12" s="36"/>
+      <c r="AB12" s="36"/>
+      <c r="AC12" s="36"/>
+      <c r="AD12" s="36"/>
+      <c r="AE12" s="36"/>
+      <c r="AF12" s="36"/>
+      <c r="AG12" s="36"/>
+      <c r="AH12" s="36"/>
+      <c r="AI12" s="36"/>
+      <c r="AJ12" s="36"/>
+      <c r="AK12" s="36"/>
+      <c r="AL12" s="96"/>
     </row>
     <row r="13" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A13" s="33">
@@ -3717,56 +3648,53 @@
       <c r="G13" s="34"/>
       <c r="H13" s="36"/>
       <c r="I13" s="36"/>
-      <c r="J13" s="36"/>
-      <c r="K13" s="75"/>
-      <c r="L13" s="76"/>
+      <c r="J13" s="75">
+        <f t="shared" ref="J13:J15" si="0">H13+I13</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="36"/>
+      <c r="L13" s="75">
+        <f t="shared" ref="L13:L15" si="1">J13-K13</f>
+        <v>0</v>
+      </c>
       <c r="M13" s="36"/>
       <c r="N13" s="36"/>
-      <c r="O13" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P13" s="36">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q13" s="36">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R13" s="36">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S13" s="88">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="T13" s="85"/>
-      <c r="U13" s="85"/>
-      <c r="V13" s="85"/>
-      <c r="W13" s="85"/>
-      <c r="X13" s="85"/>
-      <c r="Y13" s="85"/>
-      <c r="Z13" s="36">
-        <f>SUM(AA13:AJ13)</f>
-        <v>0</v>
-      </c>
-      <c r="AA13" s="88"/>
-      <c r="AB13" s="88"/>
-      <c r="AC13" s="88"/>
-      <c r="AD13" s="88"/>
-      <c r="AE13" s="88"/>
-      <c r="AF13" s="88"/>
-      <c r="AG13" s="88"/>
-      <c r="AH13" s="88"/>
-      <c r="AI13" s="88"/>
-      <c r="AJ13" s="88"/>
-      <c r="AK13" s="85">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AL13" s="100"/>
+      <c r="O13" s="75">
+        <f t="shared" ref="O13:O15" si="2">L13-M13</f>
+        <v>0</v>
+      </c>
+      <c r="P13" s="75">
+        <f t="shared" ref="P13:P15" si="3">K13-N13</f>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="75">
+        <f t="shared" ref="Q13:Q15" si="4">M13+O13</f>
+        <v>0</v>
+      </c>
+      <c r="R13" s="75">
+        <f t="shared" ref="R13:R15" si="5">M13+N13+O13+P13</f>
+        <v>0</v>
+      </c>
+      <c r="S13" s="36"/>
+      <c r="T13" s="36"/>
+      <c r="U13" s="36"/>
+      <c r="V13" s="36"/>
+      <c r="W13" s="36"/>
+      <c r="X13" s="36"/>
+      <c r="Y13" s="36"/>
+      <c r="Z13" s="36"/>
+      <c r="AA13" s="36"/>
+      <c r="AB13" s="36"/>
+      <c r="AC13" s="36"/>
+      <c r="AD13" s="36"/>
+      <c r="AE13" s="36"/>
+      <c r="AF13" s="36"/>
+      <c r="AG13" s="36"/>
+      <c r="AH13" s="36"/>
+      <c r="AI13" s="36"/>
+      <c r="AJ13" s="36"/>
+      <c r="AK13" s="36"/>
+      <c r="AL13" s="96"/>
     </row>
     <row r="14" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A14" s="33">
@@ -3780,56 +3708,53 @@
       <c r="G14" s="34"/>
       <c r="H14" s="36"/>
       <c r="I14" s="36"/>
-      <c r="J14" s="36"/>
-      <c r="K14" s="75"/>
-      <c r="L14" s="76"/>
+      <c r="J14" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="36"/>
+      <c r="L14" s="75">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M14" s="36"/>
       <c r="N14" s="36"/>
-      <c r="O14" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P14" s="36">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="36">
+      <c r="O14" s="75">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R14" s="36">
+      <c r="P14" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S14" s="88">
+      <c r="Q14" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="T14" s="85"/>
-      <c r="U14" s="85"/>
-      <c r="V14" s="85"/>
-      <c r="W14" s="85"/>
-      <c r="X14" s="85"/>
-      <c r="Y14" s="85"/>
-      <c r="Z14" s="36">
-        <f t="shared" ref="Z13:Z16" si="6">SUM(AA14:AJ14)</f>
-        <v>0</v>
-      </c>
-      <c r="AA14" s="88"/>
-      <c r="AB14" s="88"/>
-      <c r="AC14" s="88"/>
-      <c r="AD14" s="88"/>
-      <c r="AE14" s="88"/>
-      <c r="AF14" s="88"/>
-      <c r="AG14" s="88"/>
-      <c r="AH14" s="88"/>
-      <c r="AI14" s="88"/>
-      <c r="AJ14" s="88"/>
-      <c r="AK14" s="85">
+      <c r="R14" s="75">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AL14" s="100"/>
+      <c r="S14" s="36"/>
+      <c r="T14" s="36"/>
+      <c r="U14" s="36"/>
+      <c r="V14" s="36"/>
+      <c r="W14" s="36"/>
+      <c r="X14" s="36"/>
+      <c r="Y14" s="36"/>
+      <c r="Z14" s="36"/>
+      <c r="AA14" s="36"/>
+      <c r="AB14" s="36"/>
+      <c r="AC14" s="36"/>
+      <c r="AD14" s="36"/>
+      <c r="AE14" s="36"/>
+      <c r="AF14" s="36"/>
+      <c r="AG14" s="36"/>
+      <c r="AH14" s="36"/>
+      <c r="AI14" s="36"/>
+      <c r="AJ14" s="36"/>
+      <c r="AK14" s="36"/>
+      <c r="AL14" s="96"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A15" s="33">
@@ -3843,56 +3768,53 @@
       <c r="G15" s="34"/>
       <c r="H15" s="36"/>
       <c r="I15" s="36"/>
-      <c r="J15" s="36"/>
-      <c r="K15" s="75"/>
-      <c r="L15" s="76"/>
+      <c r="J15" s="75">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K15" s="36"/>
+      <c r="L15" s="75">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="M15" s="36"/>
       <c r="N15" s="36"/>
-      <c r="O15" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P15" s="36">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="36">
+      <c r="O15" s="75">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="R15" s="36">
+      <c r="P15" s="75">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S15" s="88">
+      <c r="Q15" s="75">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="T15" s="85"/>
-      <c r="U15" s="85"/>
-      <c r="V15" s="85"/>
-      <c r="W15" s="85"/>
-      <c r="X15" s="85"/>
-      <c r="Y15" s="85"/>
-      <c r="Z15" s="36">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA15" s="88"/>
-      <c r="AB15" s="88"/>
-      <c r="AC15" s="88"/>
-      <c r="AD15" s="88"/>
-      <c r="AE15" s="88"/>
-      <c r="AF15" s="88"/>
-      <c r="AG15" s="88"/>
-      <c r="AH15" s="88"/>
-      <c r="AI15" s="88"/>
-      <c r="AJ15" s="88"/>
-      <c r="AK15" s="85">
+      <c r="R15" s="75">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="AL15" s="100"/>
+      <c r="S15" s="36"/>
+      <c r="T15" s="36"/>
+      <c r="U15" s="36"/>
+      <c r="V15" s="36"/>
+      <c r="W15" s="36"/>
+      <c r="X15" s="36"/>
+      <c r="Y15" s="36"/>
+      <c r="Z15" s="36"/>
+      <c r="AA15" s="36"/>
+      <c r="AB15" s="36"/>
+      <c r="AC15" s="36"/>
+      <c r="AD15" s="36"/>
+      <c r="AE15" s="36"/>
+      <c r="AF15" s="36"/>
+      <c r="AG15" s="36"/>
+      <c r="AH15" s="36"/>
+      <c r="AI15" s="36"/>
+      <c r="AJ15" s="36"/>
+      <c r="AK15" s="36"/>
+      <c r="AL15" s="96"/>
     </row>
     <row r="16" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A16" s="33"/>
@@ -3906,56 +3828,35 @@
       <c r="G16" s="40"/>
       <c r="H16" s="36"/>
       <c r="I16" s="36"/>
-      <c r="J16" s="36"/>
-      <c r="K16" s="75"/>
-      <c r="L16" s="76"/>
+      <c r="J16" s="75"/>
+      <c r="K16" s="36"/>
+      <c r="L16" s="75"/>
       <c r="M16" s="36"/>
       <c r="N16" s="36"/>
-      <c r="O16" s="36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P16" s="36">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="36">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="R16" s="36">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S16" s="88">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+      <c r="O16" s="75"/>
+      <c r="P16" s="75"/>
+      <c r="Q16" s="75"/>
+      <c r="R16" s="75"/>
+      <c r="S16" s="36"/>
       <c r="T16" s="36"/>
       <c r="U16" s="36"/>
       <c r="V16" s="36"/>
       <c r="W16" s="36"/>
       <c r="X16" s="36"/>
       <c r="Y16" s="36"/>
-      <c r="Z16" s="36">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="AA16" s="47"/>
-      <c r="AB16" s="85"/>
-      <c r="AC16" s="85"/>
-      <c r="AD16" s="85"/>
-      <c r="AE16" s="85"/>
-      <c r="AF16" s="85"/>
-      <c r="AG16" s="85"/>
-      <c r="AH16" s="85"/>
-      <c r="AI16" s="85"/>
-      <c r="AJ16" s="85"/>
-      <c r="AK16" s="85">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AL16" s="101"/>
+      <c r="Z16" s="36"/>
+      <c r="AA16" s="36"/>
+      <c r="AB16" s="36"/>
+      <c r="AC16" s="36"/>
+      <c r="AD16" s="36"/>
+      <c r="AE16" s="36"/>
+      <c r="AF16" s="36"/>
+      <c r="AG16" s="36"/>
+      <c r="AH16" s="36"/>
+      <c r="AI16" s="36"/>
+      <c r="AJ16" s="36"/>
+      <c r="AK16" s="36"/>
+      <c r="AL16" s="97"/>
     </row>
     <row r="17" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A17" s="41"/>
@@ -3964,139 +3865,130 @@
       <c r="D17" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="E17" s="44">
-        <f t="shared" ref="E17:L17" si="7">SUM(E12:E16)</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="44">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="44">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
       <c r="H17" s="44">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="H17:AK17" si="6">SUM(H12:H16)</f>
         <v>0</v>
       </c>
       <c r="I17" s="44">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="76">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="K17" s="44">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L17" s="44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L17" s="76">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M17" s="44">
-        <f t="shared" ref="M17:AK17" si="8">SUM(M12:M16)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="N17" s="44">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O17" s="44">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="P17" s="44">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="44">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="R17" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O17" s="76">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P17" s="76">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="76">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="R17" s="76">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="S17" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T17" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U17" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="V17" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="W17" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="X17" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Y17" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Z17" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AA17" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AB17" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AC17" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AD17" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AE17" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AF17" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AG17" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AH17" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AI17" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AJ17" s="44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="AK17" s="44">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="AL17" s="100"/>
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AL17" s="96"/>
     </row>
     <row r="18" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A18" s="33"/>
@@ -4110,53 +4002,35 @@
       <c r="G18" s="34"/>
       <c r="H18" s="36"/>
       <c r="I18" s="36"/>
-      <c r="J18" s="36"/>
-      <c r="K18" s="75"/>
-      <c r="L18" s="76"/>
+      <c r="J18" s="75"/>
+      <c r="K18" s="36"/>
+      <c r="L18" s="75"/>
       <c r="M18" s="36"/>
       <c r="N18" s="36"/>
-      <c r="O18" s="36">
-        <f t="shared" ref="O18:O22" si="9">L18-M18</f>
-        <v>0</v>
-      </c>
-      <c r="P18" s="36">
-        <f t="shared" ref="P18:P22" si="10">K18-N18</f>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="36">
-        <f t="shared" ref="Q18:Q22" si="11">M18+O18</f>
-        <v>0</v>
-      </c>
-      <c r="R18" s="36">
-        <f t="shared" ref="R18:R22" si="12">M18+N18+O18+P18</f>
-        <v>0</v>
-      </c>
-      <c r="S18" s="88">
-        <f t="shared" ref="S18:S22" si="13">SUM(T18:V18)</f>
-        <v>0</v>
-      </c>
-      <c r="T18" s="88"/>
-      <c r="U18" s="88"/>
-      <c r="V18" s="88"/>
-      <c r="W18" s="88"/>
-      <c r="X18" s="88"/>
-      <c r="Y18" s="88"/>
-      <c r="Z18" s="88"/>
-      <c r="AA18" s="88"/>
-      <c r="AB18" s="88"/>
-      <c r="AC18" s="88"/>
-      <c r="AD18" s="88"/>
-      <c r="AE18" s="88"/>
-      <c r="AF18" s="88"/>
-      <c r="AG18" s="88"/>
-      <c r="AH18" s="88"/>
-      <c r="AI18" s="88"/>
-      <c r="AJ18" s="88"/>
-      <c r="AK18" s="85">
-        <f t="shared" ref="AK18:AK22" si="14">AB18/1.17*0.17+AC18/1.16*0.16+AD18/1.11*0.11+AE18/1.1*0.1+AF18/1.09*0.09+AI18/1.03*0.03</f>
-        <v>0</v>
-      </c>
-      <c r="AL18" s="100"/>
+      <c r="O18" s="75"/>
+      <c r="P18" s="75"/>
+      <c r="Q18" s="75"/>
+      <c r="R18" s="75"/>
+      <c r="S18" s="36"/>
+      <c r="T18" s="36"/>
+      <c r="U18" s="36"/>
+      <c r="V18" s="36"/>
+      <c r="W18" s="36"/>
+      <c r="X18" s="36"/>
+      <c r="Y18" s="36"/>
+      <c r="Z18" s="36"/>
+      <c r="AA18" s="36"/>
+      <c r="AB18" s="36"/>
+      <c r="AC18" s="36"/>
+      <c r="AD18" s="36"/>
+      <c r="AE18" s="36"/>
+      <c r="AF18" s="36"/>
+      <c r="AG18" s="36"/>
+      <c r="AH18" s="36"/>
+      <c r="AI18" s="36"/>
+      <c r="AJ18" s="36"/>
+      <c r="AK18" s="36"/>
+      <c r="AL18" s="96"/>
     </row>
     <row r="19" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A19" s="33">
@@ -4170,56 +4044,53 @@
       <c r="G19" s="46"/>
       <c r="H19" s="36"/>
       <c r="I19" s="36"/>
-      <c r="J19" s="36"/>
-      <c r="K19" s="75"/>
-      <c r="L19" s="76"/>
+      <c r="J19" s="75">
+        <f t="shared" ref="J19:J21" si="7">H19+I19</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="36"/>
+      <c r="L19" s="75">
+        <f t="shared" ref="L19:L21" si="8">J19-K19</f>
+        <v>0</v>
+      </c>
       <c r="M19" s="36"/>
       <c r="N19" s="36"/>
-      <c r="O19" s="36">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="P19" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Q19" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="R19" s="36">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S19" s="88">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="T19" s="88"/>
-      <c r="U19" s="88"/>
-      <c r="V19" s="88"/>
-      <c r="W19" s="88"/>
-      <c r="X19" s="88"/>
-      <c r="Y19" s="88"/>
-      <c r="Z19" s="36">
-        <f t="shared" ref="Z19:Z21" si="15">SUM(AA19:AJ19)</f>
-        <v>0</v>
-      </c>
-      <c r="AA19" s="88"/>
-      <c r="AB19" s="88"/>
-      <c r="AC19" s="88"/>
-      <c r="AD19" s="88"/>
-      <c r="AE19" s="88"/>
-      <c r="AF19" s="88"/>
-      <c r="AG19" s="88"/>
-      <c r="AH19" s="88"/>
-      <c r="AI19" s="88"/>
-      <c r="AJ19" s="88"/>
-      <c r="AK19" s="85">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AL19" s="100"/>
+      <c r="O19" s="75">
+        <f t="shared" ref="O19:O21" si="9">L19-M19</f>
+        <v>0</v>
+      </c>
+      <c r="P19" s="75">
+        <f t="shared" ref="P19:P21" si="10">K19-N19</f>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="75">
+        <f t="shared" ref="Q19:Q21" si="11">M19+O19</f>
+        <v>0</v>
+      </c>
+      <c r="R19" s="75">
+        <f t="shared" ref="R19:R21" si="12">M19+N19+O19+P19</f>
+        <v>0</v>
+      </c>
+      <c r="S19" s="36"/>
+      <c r="T19" s="36"/>
+      <c r="U19" s="36"/>
+      <c r="V19" s="36"/>
+      <c r="W19" s="36"/>
+      <c r="X19" s="36"/>
+      <c r="Y19" s="36"/>
+      <c r="Z19" s="36"/>
+      <c r="AA19" s="36"/>
+      <c r="AB19" s="36"/>
+      <c r="AC19" s="36"/>
+      <c r="AD19" s="36"/>
+      <c r="AE19" s="36"/>
+      <c r="AF19" s="36"/>
+      <c r="AG19" s="36"/>
+      <c r="AH19" s="36"/>
+      <c r="AI19" s="36"/>
+      <c r="AJ19" s="36"/>
+      <c r="AK19" s="36"/>
+      <c r="AL19" s="96"/>
     </row>
     <row r="20" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A20" s="33">
@@ -4233,56 +4104,53 @@
       <c r="G20" s="47"/>
       <c r="H20" s="36"/>
       <c r="I20" s="36"/>
-      <c r="J20" s="36"/>
-      <c r="K20" s="75"/>
-      <c r="L20" s="76"/>
+      <c r="J20" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="36"/>
+      <c r="L20" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="M20" s="36"/>
       <c r="N20" s="36"/>
-      <c r="O20" s="36">
+      <c r="O20" s="75">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="P20" s="36">
+      <c r="P20" s="75">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="Q20" s="36">
+      <c r="Q20" s="75">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="R20" s="36">
+      <c r="R20" s="75">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="S20" s="88">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="T20" s="88"/>
-      <c r="U20" s="88"/>
-      <c r="V20" s="88"/>
-      <c r="W20" s="88"/>
-      <c r="X20" s="88"/>
-      <c r="Y20" s="88"/>
-      <c r="Z20" s="36">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AA20" s="88"/>
-      <c r="AB20" s="88"/>
-      <c r="AC20" s="88"/>
-      <c r="AD20" s="88"/>
-      <c r="AE20" s="88"/>
-      <c r="AF20" s="88"/>
-      <c r="AG20" s="88"/>
-      <c r="AH20" s="88"/>
-      <c r="AI20" s="88"/>
-      <c r="AJ20" s="88"/>
-      <c r="AK20" s="85">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AL20" s="100"/>
+      <c r="S20" s="36"/>
+      <c r="T20" s="36"/>
+      <c r="U20" s="36"/>
+      <c r="V20" s="36"/>
+      <c r="W20" s="36"/>
+      <c r="X20" s="36"/>
+      <c r="Y20" s="36"/>
+      <c r="Z20" s="36"/>
+      <c r="AA20" s="36"/>
+      <c r="AB20" s="36"/>
+      <c r="AC20" s="36"/>
+      <c r="AD20" s="36"/>
+      <c r="AE20" s="36"/>
+      <c r="AF20" s="36"/>
+      <c r="AG20" s="36"/>
+      <c r="AH20" s="36"/>
+      <c r="AI20" s="36"/>
+      <c r="AJ20" s="36"/>
+      <c r="AK20" s="36"/>
+      <c r="AL20" s="96"/>
     </row>
     <row r="21" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A21" s="33">
@@ -4296,56 +4164,53 @@
       <c r="G21" s="46"/>
       <c r="H21" s="36"/>
       <c r="I21" s="36"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="75"/>
-      <c r="L21" s="76"/>
+      <c r="J21" s="75">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="36"/>
+      <c r="L21" s="75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="M21" s="36"/>
       <c r="N21" s="36"/>
-      <c r="O21" s="36">
+      <c r="O21" s="75">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="P21" s="36">
+      <c r="P21" s="75">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="Q21" s="36">
+      <c r="Q21" s="75">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="R21" s="36">
+      <c r="R21" s="75">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="S21" s="88">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="T21" s="88"/>
-      <c r="U21" s="88"/>
-      <c r="V21" s="88"/>
-      <c r="W21" s="88"/>
-      <c r="X21" s="88"/>
-      <c r="Y21" s="88"/>
-      <c r="Z21" s="36">
-        <f t="shared" si="15"/>
-        <v>0</v>
-      </c>
-      <c r="AA21" s="88"/>
-      <c r="AB21" s="88"/>
-      <c r="AC21" s="88"/>
-      <c r="AD21" s="88"/>
-      <c r="AE21" s="88"/>
-      <c r="AF21" s="88"/>
-      <c r="AG21" s="88"/>
-      <c r="AH21" s="88"/>
-      <c r="AI21" s="88"/>
-      <c r="AJ21" s="88"/>
-      <c r="AK21" s="85">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AL21" s="100"/>
+      <c r="S21" s="36"/>
+      <c r="T21" s="36"/>
+      <c r="U21" s="36"/>
+      <c r="V21" s="36"/>
+      <c r="W21" s="36"/>
+      <c r="X21" s="36"/>
+      <c r="Y21" s="36"/>
+      <c r="Z21" s="36"/>
+      <c r="AA21" s="36"/>
+      <c r="AB21" s="36"/>
+      <c r="AC21" s="36"/>
+      <c r="AD21" s="36"/>
+      <c r="AE21" s="36"/>
+      <c r="AF21" s="36"/>
+      <c r="AG21" s="36"/>
+      <c r="AH21" s="36"/>
+      <c r="AI21" s="36"/>
+      <c r="AJ21" s="36"/>
+      <c r="AK21" s="36"/>
+      <c r="AL21" s="96"/>
     </row>
     <row r="22" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A22" s="33"/>
@@ -4359,53 +4224,35 @@
       <c r="G22" s="48"/>
       <c r="H22" s="36"/>
       <c r="I22" s="36"/>
-      <c r="J22" s="36"/>
-      <c r="K22" s="75"/>
-      <c r="L22" s="76"/>
+      <c r="J22" s="75"/>
+      <c r="K22" s="36"/>
+      <c r="L22" s="75"/>
       <c r="M22" s="36"/>
       <c r="N22" s="36"/>
-      <c r="O22" s="36">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="P22" s="36">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="36">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="R22" s="36">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S22" s="88">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
+      <c r="O22" s="75"/>
+      <c r="P22" s="75"/>
+      <c r="Q22" s="75"/>
+      <c r="R22" s="75"/>
+      <c r="S22" s="36"/>
       <c r="T22" s="36"/>
       <c r="U22" s="36"/>
       <c r="V22" s="36"/>
       <c r="W22" s="36"/>
       <c r="X22" s="36"/>
       <c r="Y22" s="36"/>
-      <c r="Z22" s="88"/>
-      <c r="AA22" s="88"/>
-      <c r="AB22" s="85"/>
-      <c r="AC22" s="85"/>
-      <c r="AD22" s="85"/>
-      <c r="AE22" s="85"/>
-      <c r="AF22" s="85"/>
-      <c r="AG22" s="85"/>
-      <c r="AH22" s="85"/>
-      <c r="AI22" s="85"/>
-      <c r="AJ22" s="85"/>
-      <c r="AK22" s="85">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AL22" s="101"/>
+      <c r="Z22" s="36"/>
+      <c r="AA22" s="36"/>
+      <c r="AB22" s="36"/>
+      <c r="AC22" s="36"/>
+      <c r="AD22" s="36"/>
+      <c r="AE22" s="36"/>
+      <c r="AF22" s="36"/>
+      <c r="AG22" s="36"/>
+      <c r="AH22" s="36"/>
+      <c r="AI22" s="36"/>
+      <c r="AJ22" s="36"/>
+      <c r="AK22" s="36"/>
+      <c r="AL22" s="97"/>
     </row>
     <row r="23" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A23" s="41"/>
@@ -4414,139 +4261,130 @@
       <c r="D23" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="E23" s="44">
-        <f t="shared" ref="E23:AK23" si="16">SUM(E18:E22)</f>
-        <v>0</v>
-      </c>
-      <c r="F23" s="44">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="G23" s="44">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
       <c r="H23" s="44">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="H23:AK23" si="13">SUM(H19:H22)</f>
         <v>0</v>
       </c>
       <c r="I23" s="44">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="J23" s="44">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="76">
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="K23" s="44">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="L23" s="44">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="L23" s="76">
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="M23" s="44">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="N23" s="44">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="O23" s="44">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="P23" s="44">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Q23" s="44">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="R23" s="44">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="O23" s="76">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="P23" s="76">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="76">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="R23" s="76">
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="S23" s="44">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="T23" s="44">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="U23" s="44">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="V23" s="44">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="W23" s="44">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="X23" s="44">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="Y23" s="44">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="Z23" s="44">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AA23" s="44">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AB23" s="44">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AC23" s="44">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AD23" s="44">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AE23" s="44">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AF23" s="44">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AG23" s="44">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AH23" s="44">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AI23" s="44">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AJ23" s="44">
-        <f t="shared" si="16"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AK23" s="44">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AL23" s="100"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AL23" s="96"/>
     </row>
     <row r="24" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A24" s="33"/>
@@ -4560,53 +4398,35 @@
       <c r="G24" s="34"/>
       <c r="H24" s="36"/>
       <c r="I24" s="36"/>
-      <c r="J24" s="36"/>
-      <c r="K24" s="75"/>
-      <c r="L24" s="76"/>
+      <c r="J24" s="75"/>
+      <c r="K24" s="36"/>
+      <c r="L24" s="75"/>
       <c r="M24" s="36"/>
       <c r="N24" s="36"/>
-      <c r="O24" s="36">
-        <f t="shared" ref="O24:O35" si="17">L24-M24</f>
-        <v>0</v>
-      </c>
-      <c r="P24" s="36">
-        <f t="shared" ref="P24:P35" si="18">K24-N24</f>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="36">
-        <f t="shared" ref="Q24:Q35" si="19">M24+O24</f>
-        <v>0</v>
-      </c>
-      <c r="R24" s="36">
-        <f t="shared" ref="R24:R35" si="20">M24+N24+O24+P24</f>
-        <v>0</v>
-      </c>
-      <c r="S24" s="88">
-        <f t="shared" ref="S24:S34" si="21">SUM(T24:V24)</f>
-        <v>0</v>
-      </c>
-      <c r="T24" s="88"/>
-      <c r="U24" s="88"/>
-      <c r="V24" s="88"/>
-      <c r="W24" s="88"/>
-      <c r="X24" s="88"/>
-      <c r="Y24" s="88"/>
-      <c r="Z24" s="88"/>
-      <c r="AA24" s="88"/>
-      <c r="AB24" s="96"/>
-      <c r="AC24" s="96"/>
-      <c r="AD24" s="96"/>
-      <c r="AE24" s="96"/>
-      <c r="AF24" s="96"/>
-      <c r="AG24" s="96"/>
-      <c r="AH24" s="96"/>
-      <c r="AI24" s="96"/>
-      <c r="AJ24" s="96"/>
-      <c r="AK24" s="85">
-        <f t="shared" ref="AK24:AK35" si="22">AB24/1.17*0.17+AC24/1.16*0.16+AD24/1.11*0.11+AE24/1.1*0.1+AF24/1.09*0.09+AI24/1.03*0.03</f>
-        <v>0</v>
-      </c>
-      <c r="AL24" s="102"/>
+      <c r="O24" s="75"/>
+      <c r="P24" s="75"/>
+      <c r="Q24" s="75"/>
+      <c r="R24" s="75"/>
+      <c r="S24" s="36"/>
+      <c r="T24" s="36"/>
+      <c r="U24" s="36"/>
+      <c r="V24" s="36"/>
+      <c r="W24" s="36"/>
+      <c r="X24" s="36"/>
+      <c r="Y24" s="36"/>
+      <c r="Z24" s="36"/>
+      <c r="AA24" s="36"/>
+      <c r="AB24" s="36"/>
+      <c r="AC24" s="36"/>
+      <c r="AD24" s="36"/>
+      <c r="AE24" s="36"/>
+      <c r="AF24" s="36"/>
+      <c r="AG24" s="36"/>
+      <c r="AH24" s="36"/>
+      <c r="AI24" s="36"/>
+      <c r="AJ24" s="36"/>
+      <c r="AK24" s="36"/>
+      <c r="AL24" s="98"/>
     </row>
     <row r="25" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A25" s="33"/>
@@ -4620,53 +4440,35 @@
       <c r="G25" s="34"/>
       <c r="H25" s="36"/>
       <c r="I25" s="36"/>
-      <c r="J25" s="36"/>
-      <c r="K25" s="75"/>
-      <c r="L25" s="76"/>
+      <c r="J25" s="75"/>
+      <c r="K25" s="36"/>
+      <c r="L25" s="75"/>
       <c r="M25" s="36"/>
       <c r="N25" s="36"/>
-      <c r="O25" s="36">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P25" s="36">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="36">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="R25" s="36">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="S25" s="88">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T25" s="88"/>
-      <c r="U25" s="88"/>
-      <c r="V25" s="88"/>
-      <c r="W25" s="88"/>
-      <c r="X25" s="88"/>
-      <c r="Y25" s="88"/>
-      <c r="Z25" s="88"/>
-      <c r="AA25" s="88"/>
-      <c r="AB25" s="96"/>
-      <c r="AC25" s="96"/>
-      <c r="AD25" s="96"/>
-      <c r="AE25" s="96"/>
-      <c r="AF25" s="96"/>
-      <c r="AG25" s="96"/>
-      <c r="AH25" s="96"/>
-      <c r="AI25" s="96"/>
-      <c r="AJ25" s="96"/>
-      <c r="AK25" s="85">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL25" s="102"/>
+      <c r="O25" s="75"/>
+      <c r="P25" s="75"/>
+      <c r="Q25" s="75"/>
+      <c r="R25" s="75"/>
+      <c r="S25" s="36"/>
+      <c r="T25" s="36"/>
+      <c r="U25" s="36"/>
+      <c r="V25" s="36"/>
+      <c r="W25" s="36"/>
+      <c r="X25" s="36"/>
+      <c r="Y25" s="36"/>
+      <c r="Z25" s="36"/>
+      <c r="AA25" s="36"/>
+      <c r="AB25" s="36"/>
+      <c r="AC25" s="36"/>
+      <c r="AD25" s="36"/>
+      <c r="AE25" s="36"/>
+      <c r="AF25" s="36"/>
+      <c r="AG25" s="36"/>
+      <c r="AH25" s="36"/>
+      <c r="AI25" s="36"/>
+      <c r="AJ25" s="36"/>
+      <c r="AK25" s="36"/>
+      <c r="AL25" s="98"/>
     </row>
     <row r="26" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A26" s="33">
@@ -4680,56 +4482,53 @@
       <c r="G26" s="47"/>
       <c r="H26" s="36"/>
       <c r="I26" s="36"/>
-      <c r="J26" s="36"/>
-      <c r="K26" s="75"/>
-      <c r="L26" s="76"/>
+      <c r="J26" s="75">
+        <f t="shared" ref="J26:J28" si="14">H26+I26</f>
+        <v>0</v>
+      </c>
+      <c r="K26" s="36"/>
+      <c r="L26" s="75">
+        <f t="shared" ref="L26:L28" si="15">J26-K26</f>
+        <v>0</v>
+      </c>
       <c r="M26" s="36"/>
       <c r="N26" s="36"/>
-      <c r="O26" s="36">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P26" s="36">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="36">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="R26" s="36">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="S26" s="88">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T26" s="88"/>
-      <c r="U26" s="88"/>
-      <c r="V26" s="88"/>
-      <c r="W26" s="88"/>
-      <c r="X26" s="88"/>
-      <c r="Y26" s="88"/>
-      <c r="Z26" s="36">
-        <f t="shared" ref="Z26:Z31" si="23">SUM(AA26:AJ26)</f>
-        <v>0</v>
-      </c>
-      <c r="AA26" s="88"/>
-      <c r="AB26" s="96"/>
-      <c r="AC26" s="96"/>
-      <c r="AD26" s="96"/>
-      <c r="AE26" s="96"/>
-      <c r="AF26" s="96"/>
-      <c r="AG26" s="96"/>
-      <c r="AH26" s="96"/>
-      <c r="AI26" s="96"/>
-      <c r="AJ26" s="96"/>
-      <c r="AK26" s="85">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL26" s="102"/>
+      <c r="O26" s="75">
+        <f t="shared" ref="O26:O28" si="16">L26-M26</f>
+        <v>0</v>
+      </c>
+      <c r="P26" s="75">
+        <f t="shared" ref="P26:P28" si="17">K26-N26</f>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="75">
+        <f t="shared" ref="Q26:Q32" si="18">M26+O26</f>
+        <v>0</v>
+      </c>
+      <c r="R26" s="75">
+        <f t="shared" ref="R26:R32" si="19">M26+N26+O26+P26</f>
+        <v>0</v>
+      </c>
+      <c r="S26" s="36"/>
+      <c r="T26" s="36"/>
+      <c r="U26" s="36"/>
+      <c r="V26" s="36"/>
+      <c r="W26" s="36"/>
+      <c r="X26" s="36"/>
+      <c r="Y26" s="36"/>
+      <c r="Z26" s="36"/>
+      <c r="AA26" s="36"/>
+      <c r="AB26" s="36"/>
+      <c r="AC26" s="36"/>
+      <c r="AD26" s="36"/>
+      <c r="AE26" s="36"/>
+      <c r="AF26" s="36"/>
+      <c r="AG26" s="36"/>
+      <c r="AH26" s="36"/>
+      <c r="AI26" s="36"/>
+      <c r="AJ26" s="36"/>
+      <c r="AK26" s="36"/>
+      <c r="AL26" s="98"/>
     </row>
     <row r="27" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A27" s="33">
@@ -4743,56 +4542,53 @@
       <c r="G27" s="47"/>
       <c r="H27" s="36"/>
       <c r="I27" s="36"/>
-      <c r="J27" s="36"/>
-      <c r="K27" s="75"/>
-      <c r="L27" s="76"/>
+      <c r="J27" s="75">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="K27" s="36"/>
+      <c r="L27" s="75">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="M27" s="36"/>
       <c r="N27" s="36"/>
-      <c r="O27" s="36">
+      <c r="O27" s="75">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="P27" s="75">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="P27" s="36">
+      <c r="Q27" s="75">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="Q27" s="36">
+      <c r="R27" s="75">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="R27" s="36">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="S27" s="88">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T27" s="88"/>
-      <c r="U27" s="88"/>
-      <c r="V27" s="88"/>
-      <c r="W27" s="88"/>
-      <c r="X27" s="88"/>
-      <c r="Y27" s="88"/>
-      <c r="Z27" s="36">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AA27" s="88"/>
-      <c r="AB27" s="96"/>
-      <c r="AC27" s="96"/>
-      <c r="AD27" s="96"/>
-      <c r="AE27" s="96"/>
-      <c r="AF27" s="96"/>
-      <c r="AG27" s="96"/>
-      <c r="AH27" s="96"/>
-      <c r="AI27" s="96"/>
-      <c r="AJ27" s="96"/>
-      <c r="AK27" s="85">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL27" s="102"/>
+      <c r="S27" s="36"/>
+      <c r="T27" s="36"/>
+      <c r="U27" s="36"/>
+      <c r="V27" s="36"/>
+      <c r="W27" s="36"/>
+      <c r="X27" s="36"/>
+      <c r="Y27" s="36"/>
+      <c r="Z27" s="36"/>
+      <c r="AA27" s="36"/>
+      <c r="AB27" s="36"/>
+      <c r="AC27" s="36"/>
+      <c r="AD27" s="36"/>
+      <c r="AE27" s="36"/>
+      <c r="AF27" s="36"/>
+      <c r="AG27" s="36"/>
+      <c r="AH27" s="36"/>
+      <c r="AI27" s="36"/>
+      <c r="AJ27" s="36"/>
+      <c r="AK27" s="36"/>
+      <c r="AL27" s="98"/>
     </row>
     <row r="28" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A28" s="33">
@@ -4806,56 +4602,53 @@
       <c r="G28" s="47"/>
       <c r="H28" s="36"/>
       <c r="I28" s="36"/>
-      <c r="J28" s="36"/>
-      <c r="K28" s="75"/>
-      <c r="L28" s="76"/>
+      <c r="J28" s="75">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="36"/>
+      <c r="L28" s="75">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="M28" s="36"/>
       <c r="N28" s="36"/>
-      <c r="O28" s="36">
+      <c r="O28" s="75">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="P28" s="75">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="P28" s="36">
+      <c r="Q28" s="75">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="Q28" s="36">
+      <c r="R28" s="75">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="R28" s="36">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="S28" s="88">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T28" s="88"/>
-      <c r="U28" s="88"/>
-      <c r="V28" s="88"/>
-      <c r="W28" s="88"/>
-      <c r="X28" s="88"/>
-      <c r="Y28" s="88"/>
-      <c r="Z28" s="36">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AA28" s="88"/>
-      <c r="AB28" s="96"/>
-      <c r="AC28" s="96"/>
-      <c r="AD28" s="96"/>
-      <c r="AE28" s="96"/>
-      <c r="AF28" s="96"/>
-      <c r="AG28" s="96"/>
-      <c r="AH28" s="96"/>
-      <c r="AI28" s="96"/>
-      <c r="AJ28" s="96"/>
-      <c r="AK28" s="85">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL28" s="102"/>
+      <c r="S28" s="36"/>
+      <c r="T28" s="36"/>
+      <c r="U28" s="36"/>
+      <c r="V28" s="36"/>
+      <c r="W28" s="36"/>
+      <c r="X28" s="36"/>
+      <c r="Y28" s="36"/>
+      <c r="Z28" s="36"/>
+      <c r="AA28" s="36"/>
+      <c r="AB28" s="36"/>
+      <c r="AC28" s="36"/>
+      <c r="AD28" s="36"/>
+      <c r="AE28" s="36"/>
+      <c r="AF28" s="36"/>
+      <c r="AG28" s="36"/>
+      <c r="AH28" s="36"/>
+      <c r="AI28" s="36"/>
+      <c r="AJ28" s="36"/>
+      <c r="AK28" s="36"/>
+      <c r="AL28" s="98"/>
     </row>
     <row r="29" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A29" s="33"/>
@@ -4869,56 +4662,41 @@
       <c r="G29" s="48"/>
       <c r="H29" s="36"/>
       <c r="I29" s="36"/>
-      <c r="J29" s="36"/>
-      <c r="K29" s="75"/>
-      <c r="L29" s="76"/>
+      <c r="J29" s="75"/>
+      <c r="K29" s="36"/>
+      <c r="L29" s="75"/>
       <c r="M29" s="36"/>
       <c r="N29" s="36"/>
-      <c r="O29" s="36">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P29" s="36">
+      <c r="O29" s="75"/>
+      <c r="P29" s="75"/>
+      <c r="Q29" s="75">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="Q29" s="36">
+      <c r="R29" s="75">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="R29" s="36">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="S29" s="88">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T29" s="88"/>
-      <c r="U29" s="88"/>
-      <c r="V29" s="88"/>
-      <c r="W29" s="88"/>
-      <c r="X29" s="88"/>
-      <c r="Y29" s="88"/>
-      <c r="Z29" s="36">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AA29" s="88"/>
-      <c r="AB29" s="96"/>
-      <c r="AC29" s="96"/>
-      <c r="AD29" s="96"/>
-      <c r="AE29" s="96"/>
-      <c r="AF29" s="96"/>
-      <c r="AG29" s="96"/>
-      <c r="AH29" s="96"/>
-      <c r="AI29" s="96"/>
-      <c r="AJ29" s="96"/>
-      <c r="AK29" s="85">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL29" s="102"/>
+      <c r="S29" s="36"/>
+      <c r="T29" s="36"/>
+      <c r="U29" s="36"/>
+      <c r="V29" s="36"/>
+      <c r="W29" s="36"/>
+      <c r="X29" s="36"/>
+      <c r="Y29" s="36"/>
+      <c r="Z29" s="36"/>
+      <c r="AA29" s="36"/>
+      <c r="AB29" s="36"/>
+      <c r="AC29" s="36"/>
+      <c r="AD29" s="36"/>
+      <c r="AE29" s="36"/>
+      <c r="AF29" s="36"/>
+      <c r="AG29" s="36"/>
+      <c r="AH29" s="36"/>
+      <c r="AI29" s="36"/>
+      <c r="AJ29" s="36"/>
+      <c r="AK29" s="36"/>
+      <c r="AL29" s="98"/>
     </row>
     <row r="30" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A30" s="33">
@@ -4934,56 +4712,53 @@
       <c r="G30" s="34"/>
       <c r="H30" s="36"/>
       <c r="I30" s="36"/>
-      <c r="J30" s="36"/>
-      <c r="K30" s="75"/>
-      <c r="L30" s="76"/>
+      <c r="J30" s="75">
+        <f t="shared" ref="J30:J32" si="20">H30+I30</f>
+        <v>0</v>
+      </c>
+      <c r="K30" s="36"/>
+      <c r="L30" s="75">
+        <f t="shared" ref="L30:L32" si="21">J30-K30</f>
+        <v>0</v>
+      </c>
       <c r="M30" s="36"/>
       <c r="N30" s="36"/>
-      <c r="O30" s="36">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P30" s="36">
+      <c r="O30" s="75">
+        <f t="shared" ref="O30:O32" si="22">L30-M30</f>
+        <v>0</v>
+      </c>
+      <c r="P30" s="75">
+        <f t="shared" ref="P30:P32" si="23">K30-N30</f>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="75">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="Q30" s="36">
+      <c r="R30" s="75">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="R30" s="36">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="S30" s="88">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="T30" s="88"/>
-      <c r="U30" s="88"/>
-      <c r="V30" s="88"/>
-      <c r="W30" s="88"/>
-      <c r="X30" s="88"/>
-      <c r="Y30" s="88"/>
-      <c r="Z30" s="36">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AA30" s="88"/>
-      <c r="AB30" s="96"/>
-      <c r="AC30" s="96"/>
-      <c r="AD30" s="96"/>
-      <c r="AE30" s="96"/>
-      <c r="AF30" s="96"/>
-      <c r="AG30" s="96"/>
-      <c r="AH30" s="96"/>
-      <c r="AI30" s="96"/>
-      <c r="AJ30" s="96"/>
-      <c r="AK30" s="85">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL30" s="102"/>
+      <c r="S30" s="36"/>
+      <c r="T30" s="36"/>
+      <c r="U30" s="36"/>
+      <c r="V30" s="36"/>
+      <c r="W30" s="36"/>
+      <c r="X30" s="36"/>
+      <c r="Y30" s="36"/>
+      <c r="Z30" s="36"/>
+      <c r="AA30" s="36"/>
+      <c r="AB30" s="36"/>
+      <c r="AC30" s="36"/>
+      <c r="AD30" s="36"/>
+      <c r="AE30" s="36"/>
+      <c r="AF30" s="36"/>
+      <c r="AG30" s="36"/>
+      <c r="AH30" s="36"/>
+      <c r="AI30" s="36"/>
+      <c r="AJ30" s="36"/>
+      <c r="AK30" s="36"/>
+      <c r="AL30" s="98"/>
     </row>
     <row r="31" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A31" s="33">
@@ -4999,56 +4774,53 @@
       <c r="G31" s="49"/>
       <c r="H31" s="50"/>
       <c r="I31" s="50"/>
-      <c r="J31" s="36"/>
-      <c r="K31" s="75"/>
-      <c r="L31" s="76"/>
+      <c r="J31" s="75">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="K31" s="50"/>
+      <c r="L31" s="75">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
       <c r="M31" s="50"/>
       <c r="N31" s="50"/>
-      <c r="O31" s="36">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="P31" s="36">
+      <c r="O31" s="75">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P31" s="75">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="75">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="Q31" s="36">
+      <c r="R31" s="75">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="R31" s="36">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="S31" s="88">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
+      <c r="S31" s="50"/>
       <c r="T31" s="50"/>
       <c r="U31" s="50"/>
       <c r="V31" s="50"/>
       <c r="W31" s="50"/>
       <c r="X31" s="50"/>
       <c r="Y31" s="50"/>
-      <c r="Z31" s="36">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
+      <c r="Z31" s="50"/>
       <c r="AA31" s="50"/>
-      <c r="AB31" s="97"/>
-      <c r="AC31" s="97"/>
-      <c r="AD31" s="97"/>
-      <c r="AE31" s="97"/>
-      <c r="AF31" s="97"/>
-      <c r="AG31" s="97"/>
-      <c r="AH31" s="97"/>
-      <c r="AI31" s="97"/>
-      <c r="AJ31" s="97"/>
-      <c r="AK31" s="85">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-      <c r="AL31" s="103"/>
+      <c r="AB31" s="50"/>
+      <c r="AC31" s="50"/>
+      <c r="AD31" s="50"/>
+      <c r="AE31" s="50"/>
+      <c r="AF31" s="50"/>
+      <c r="AG31" s="50"/>
+      <c r="AH31" s="50"/>
+      <c r="AI31" s="50"/>
+      <c r="AJ31" s="50"/>
+      <c r="AK31" s="50"/>
+      <c r="AL31" s="99"/>
     </row>
     <row r="32" s="1" customFormat="1" ht="26" spans="1:38">
       <c r="A32" s="33">
@@ -5064,35 +4836,53 @@
       <c r="G32" s="49"/>
       <c r="H32" s="50"/>
       <c r="I32" s="50"/>
-      <c r="J32" s="36"/>
-      <c r="K32" s="75"/>
-      <c r="L32" s="76"/>
+      <c r="J32" s="75">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="K32" s="50"/>
+      <c r="L32" s="75">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
       <c r="M32" s="50"/>
       <c r="N32" s="50"/>
-      <c r="O32" s="36"/>
-      <c r="P32" s="36"/>
-      <c r="Q32" s="36"/>
-      <c r="R32" s="36"/>
-      <c r="S32" s="88"/>
+      <c r="O32" s="75">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P32" s="75">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="Q32" s="75">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="R32" s="75">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="S32" s="50"/>
       <c r="T32" s="50"/>
       <c r="U32" s="50"/>
       <c r="V32" s="50"/>
       <c r="W32" s="50"/>
       <c r="X32" s="50"/>
       <c r="Y32" s="50"/>
-      <c r="Z32" s="36"/>
+      <c r="Z32" s="50"/>
       <c r="AA32" s="50"/>
-      <c r="AB32" s="97"/>
-      <c r="AC32" s="97"/>
-      <c r="AD32" s="97"/>
-      <c r="AE32" s="97"/>
-      <c r="AF32" s="97"/>
-      <c r="AG32" s="97"/>
-      <c r="AH32" s="97"/>
-      <c r="AI32" s="97"/>
-      <c r="AJ32" s="97"/>
-      <c r="AK32" s="85"/>
-      <c r="AL32" s="103"/>
+      <c r="AB32" s="50"/>
+      <c r="AC32" s="50"/>
+      <c r="AD32" s="50"/>
+      <c r="AE32" s="50"/>
+      <c r="AF32" s="50"/>
+      <c r="AG32" s="50"/>
+      <c r="AH32" s="50"/>
+      <c r="AI32" s="50"/>
+      <c r="AJ32" s="50"/>
+      <c r="AK32" s="50"/>
+      <c r="AL32" s="99"/>
     </row>
     <row r="33" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A33" s="33"/>
@@ -5106,53 +4896,35 @@
       <c r="G33" s="48"/>
       <c r="H33" s="36"/>
       <c r="I33" s="36"/>
-      <c r="J33" s="36"/>
-      <c r="K33" s="75"/>
-      <c r="L33" s="76"/>
+      <c r="J33" s="75"/>
+      <c r="K33" s="36"/>
+      <c r="L33" s="75"/>
       <c r="M33" s="36"/>
       <c r="N33" s="36"/>
-      <c r="O33" s="36">
-        <f>L33-M33</f>
-        <v>0</v>
-      </c>
-      <c r="P33" s="36">
-        <f>K33-N33</f>
-        <v>0</v>
-      </c>
-      <c r="Q33" s="36">
-        <f>M33+O33</f>
-        <v>0</v>
-      </c>
-      <c r="R33" s="36">
-        <f>M33+N33+O33+P33</f>
-        <v>0</v>
-      </c>
-      <c r="S33" s="88">
-        <f>SUM(T33:V33)</f>
-        <v>0</v>
-      </c>
-      <c r="T33" s="88"/>
-      <c r="U33" s="88"/>
-      <c r="V33" s="88"/>
-      <c r="W33" s="88"/>
-      <c r="X33" s="88"/>
-      <c r="Y33" s="88"/>
-      <c r="Z33" s="88"/>
-      <c r="AA33" s="88"/>
-      <c r="AB33" s="96"/>
-      <c r="AC33" s="96"/>
-      <c r="AD33" s="96"/>
-      <c r="AE33" s="96"/>
-      <c r="AF33" s="96"/>
-      <c r="AG33" s="96"/>
-      <c r="AH33" s="96"/>
-      <c r="AI33" s="96"/>
-      <c r="AJ33" s="96"/>
-      <c r="AK33" s="85">
-        <f>AB33/1.17*0.17+AC33/1.16*0.16+AD33/1.11*0.11+AE33/1.1*0.1+AF33/1.09*0.09+AI33/1.03*0.03</f>
-        <v>0</v>
-      </c>
-      <c r="AL33" s="102"/>
+      <c r="O33" s="75"/>
+      <c r="P33" s="75"/>
+      <c r="Q33" s="75"/>
+      <c r="R33" s="75"/>
+      <c r="S33" s="36"/>
+      <c r="T33" s="36"/>
+      <c r="U33" s="36"/>
+      <c r="V33" s="36"/>
+      <c r="W33" s="36"/>
+      <c r="X33" s="36"/>
+      <c r="Y33" s="36"/>
+      <c r="Z33" s="36"/>
+      <c r="AA33" s="36"/>
+      <c r="AB33" s="36"/>
+      <c r="AC33" s="36"/>
+      <c r="AD33" s="36"/>
+      <c r="AE33" s="36"/>
+      <c r="AF33" s="36"/>
+      <c r="AG33" s="36"/>
+      <c r="AH33" s="36"/>
+      <c r="AI33" s="36"/>
+      <c r="AJ33" s="36"/>
+      <c r="AK33" s="36"/>
+      <c r="AL33" s="98"/>
     </row>
     <row r="34" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A34" s="41"/>
@@ -5161,27 +4933,18 @@
       <c r="D34" s="43" t="s">
         <v>98</v>
       </c>
-      <c r="E34" s="44">
-        <f>SUM(E24:E33)</f>
-        <v>0</v>
-      </c>
-      <c r="F34" s="44">
-        <f t="shared" ref="E34:AK34" si="24">SUM(F24:F33)</f>
-        <v>0</v>
-      </c>
-      <c r="G34" s="44">
-        <f t="shared" si="24"/>
-        <v>0</v>
-      </c>
+      <c r="E34" s="44"/>
+      <c r="F34" s="44"/>
+      <c r="G34" s="44"/>
       <c r="H34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="H34:AK34" si="24">SUM(H25:H33)</f>
         <v>0</v>
       </c>
       <c r="I34" s="44">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="J34" s="44">
+      <c r="J34" s="76">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
@@ -5189,7 +4952,7 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="L34" s="44">
+      <c r="L34" s="76">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
@@ -5201,19 +4964,19 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="O34" s="44">
+      <c r="O34" s="76">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="P34" s="44">
+      <c r="P34" s="76">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="Q34" s="44">
+      <c r="Q34" s="76">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="R34" s="44">
+      <c r="R34" s="76">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
@@ -5293,7 +5056,7 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="AL34" s="100"/>
+      <c r="AL34" s="96"/>
     </row>
     <row r="35" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A35" s="33"/>
@@ -5307,58 +5070,35 @@
       <c r="G35" s="40"/>
       <c r="H35" s="36"/>
       <c r="I35" s="36"/>
-      <c r="J35" s="36"/>
-      <c r="K35" s="75">
-        <v>0</v>
-      </c>
-      <c r="L35" s="76">
-        <f t="shared" ref="L35:L37" si="25">J35-K35</f>
-        <v>0</v>
-      </c>
-      <c r="M35" s="58"/>
-      <c r="N35" s="58"/>
-      <c r="O35" s="36">
-        <f t="shared" ref="O35:O37" si="26">L35-M35</f>
-        <v>0</v>
-      </c>
-      <c r="P35" s="36">
-        <f t="shared" ref="P35:P37" si="27">K35-N35</f>
-        <v>0</v>
-      </c>
-      <c r="Q35" s="36">
-        <f t="shared" ref="Q35:Q37" si="28">M35+O35</f>
-        <v>0</v>
-      </c>
-      <c r="R35" s="36">
-        <f t="shared" ref="R35:R37" si="29">M35+N35+O35+P35</f>
-        <v>0</v>
-      </c>
-      <c r="S35" s="88">
-        <f t="shared" ref="S35:S37" si="30">SUM(T35:V35)</f>
-        <v>0</v>
-      </c>
-      <c r="T35" s="88"/>
-      <c r="U35" s="88"/>
-      <c r="V35" s="88"/>
-      <c r="W35" s="88"/>
-      <c r="X35" s="88"/>
-      <c r="Y35" s="88"/>
-      <c r="Z35" s="88"/>
-      <c r="AA35" s="88"/>
-      <c r="AB35" s="88"/>
-      <c r="AC35" s="88"/>
-      <c r="AD35" s="88"/>
-      <c r="AE35" s="88"/>
-      <c r="AF35" s="88"/>
-      <c r="AG35" s="88"/>
-      <c r="AH35" s="88"/>
-      <c r="AI35" s="88"/>
-      <c r="AJ35" s="88"/>
-      <c r="AK35" s="85">
-        <f t="shared" ref="AK35:AK37" si="31">AB35/1.17*0.17+AC35/1.16*0.16+AD35/1.11*0.11+AE35/1.1*0.1+AF35/1.09*0.09+AI35/1.03*0.03</f>
-        <v>0</v>
-      </c>
-      <c r="AL35" s="100"/>
+      <c r="J35" s="75"/>
+      <c r="K35" s="36"/>
+      <c r="L35" s="75"/>
+      <c r="M35" s="36"/>
+      <c r="N35" s="36"/>
+      <c r="O35" s="75"/>
+      <c r="P35" s="75"/>
+      <c r="Q35" s="75"/>
+      <c r="R35" s="75"/>
+      <c r="S35" s="36"/>
+      <c r="T35" s="36"/>
+      <c r="U35" s="36"/>
+      <c r="V35" s="36"/>
+      <c r="W35" s="36"/>
+      <c r="X35" s="36"/>
+      <c r="Y35" s="36"/>
+      <c r="Z35" s="36"/>
+      <c r="AA35" s="36"/>
+      <c r="AB35" s="36"/>
+      <c r="AC35" s="36"/>
+      <c r="AD35" s="36"/>
+      <c r="AE35" s="36"/>
+      <c r="AF35" s="36"/>
+      <c r="AG35" s="36"/>
+      <c r="AH35" s="36"/>
+      <c r="AI35" s="36"/>
+      <c r="AJ35" s="36"/>
+      <c r="AK35" s="36"/>
+      <c r="AL35" s="96"/>
     </row>
     <row r="36" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A36" s="33">
@@ -5372,64 +5112,53 @@
       <c r="G36" s="40"/>
       <c r="H36" s="36"/>
       <c r="I36" s="36"/>
-      <c r="J36" s="36">
-        <f t="shared" ref="J36:J44" si="32">H36+I36</f>
-        <v>0</v>
-      </c>
-      <c r="K36" s="75">
-        <v>0</v>
-      </c>
-      <c r="L36" s="76">
-        <f t="shared" si="25"/>
+      <c r="J36" s="75">
+        <f t="shared" ref="J36:J44" si="25">H36+I36</f>
+        <v>0</v>
+      </c>
+      <c r="K36" s="36"/>
+      <c r="L36" s="75">
+        <f t="shared" ref="L36:L44" si="26">J36-K36</f>
         <v>0</v>
       </c>
       <c r="M36" s="36"/>
       <c r="N36" s="36"/>
-      <c r="O36" s="36">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="P36" s="36">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="Q36" s="36">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="R36" s="36">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="S36" s="88">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="T36" s="88"/>
-      <c r="U36" s="88"/>
-      <c r="V36" s="88"/>
-      <c r="W36" s="88"/>
-      <c r="X36" s="88"/>
-      <c r="Y36" s="88"/>
-      <c r="Z36" s="36">
-        <f t="shared" ref="Z36:Z45" si="33">SUM(AA36:AJ36)</f>
-        <v>0</v>
-      </c>
-      <c r="AA36" s="88"/>
-      <c r="AB36" s="88"/>
-      <c r="AC36" s="88"/>
-      <c r="AD36" s="88"/>
-      <c r="AE36" s="88"/>
-      <c r="AF36" s="88"/>
-      <c r="AG36" s="88"/>
-      <c r="AH36" s="88"/>
-      <c r="AI36" s="88"/>
-      <c r="AJ36" s="88"/>
-      <c r="AK36" s="85">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="AL36" s="100"/>
+      <c r="O36" s="75">
+        <f t="shared" ref="O36:O44" si="27">L36-M36</f>
+        <v>0</v>
+      </c>
+      <c r="P36" s="75">
+        <f t="shared" ref="P36:P44" si="28">K36-N36</f>
+        <v>0</v>
+      </c>
+      <c r="Q36" s="75">
+        <f t="shared" ref="Q36:Q44" si="29">M36+O36</f>
+        <v>0</v>
+      </c>
+      <c r="R36" s="75">
+        <f t="shared" ref="R36:R44" si="30">M36+N36+O36+P36</f>
+        <v>0</v>
+      </c>
+      <c r="S36" s="36"/>
+      <c r="T36" s="36"/>
+      <c r="U36" s="36"/>
+      <c r="V36" s="36"/>
+      <c r="W36" s="36"/>
+      <c r="X36" s="36"/>
+      <c r="Y36" s="36"/>
+      <c r="Z36" s="36"/>
+      <c r="AA36" s="36"/>
+      <c r="AB36" s="36"/>
+      <c r="AC36" s="36"/>
+      <c r="AD36" s="36"/>
+      <c r="AE36" s="36"/>
+      <c r="AF36" s="36"/>
+      <c r="AG36" s="36"/>
+      <c r="AH36" s="36"/>
+      <c r="AI36" s="36"/>
+      <c r="AJ36" s="36"/>
+      <c r="AK36" s="36"/>
+      <c r="AL36" s="96"/>
     </row>
     <row r="37" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A37" s="33"/>
@@ -5443,58 +5172,35 @@
       <c r="G37" s="52"/>
       <c r="H37" s="36"/>
       <c r="I37" s="36"/>
-      <c r="J37" s="36"/>
-      <c r="K37" s="75">
-        <v>0</v>
-      </c>
-      <c r="L37" s="76">
-        <f t="shared" si="25"/>
-        <v>0</v>
-      </c>
-      <c r="M37" s="77"/>
-      <c r="N37" s="77"/>
-      <c r="O37" s="36">
-        <f t="shared" si="26"/>
-        <v>0</v>
-      </c>
-      <c r="P37" s="36">
-        <f t="shared" si="27"/>
-        <v>0</v>
-      </c>
-      <c r="Q37" s="36">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="R37" s="36">
-        <f t="shared" si="29"/>
-        <v>0</v>
-      </c>
-      <c r="S37" s="88">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="T37" s="77"/>
-      <c r="U37" s="77"/>
-      <c r="V37" s="77"/>
-      <c r="W37" s="77"/>
-      <c r="X37" s="77"/>
-      <c r="Y37" s="77"/>
-      <c r="Z37" s="77"/>
-      <c r="AA37" s="88"/>
-      <c r="AB37" s="85"/>
-      <c r="AC37" s="85"/>
-      <c r="AD37" s="85"/>
-      <c r="AE37" s="85"/>
-      <c r="AF37" s="85"/>
-      <c r="AG37" s="85"/>
-      <c r="AH37" s="85"/>
-      <c r="AI37" s="85"/>
-      <c r="AJ37" s="85"/>
-      <c r="AK37" s="85">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="AL37" s="101"/>
+      <c r="J37" s="75"/>
+      <c r="K37" s="36"/>
+      <c r="L37" s="75"/>
+      <c r="M37" s="36"/>
+      <c r="N37" s="36"/>
+      <c r="O37" s="75"/>
+      <c r="P37" s="75"/>
+      <c r="Q37" s="75"/>
+      <c r="R37" s="75"/>
+      <c r="S37" s="36"/>
+      <c r="T37" s="36"/>
+      <c r="U37" s="36"/>
+      <c r="V37" s="36"/>
+      <c r="W37" s="36"/>
+      <c r="X37" s="36"/>
+      <c r="Y37" s="36"/>
+      <c r="Z37" s="36"/>
+      <c r="AA37" s="36"/>
+      <c r="AB37" s="36"/>
+      <c r="AC37" s="36"/>
+      <c r="AD37" s="36"/>
+      <c r="AE37" s="36"/>
+      <c r="AF37" s="36"/>
+      <c r="AG37" s="36"/>
+      <c r="AH37" s="36"/>
+      <c r="AI37" s="36"/>
+      <c r="AJ37" s="36"/>
+      <c r="AK37" s="36"/>
+      <c r="AL37" s="97"/>
     </row>
     <row r="38" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A38" s="41"/>
@@ -5507,78 +5213,126 @@
       <c r="F38" s="54"/>
       <c r="G38" s="54"/>
       <c r="H38" s="44">
-        <f t="shared" ref="H38:S38" si="34">SUM(H36:H37)</f>
+        <f t="shared" ref="H38:AK38" si="31">SUM(H36:H37)</f>
         <v>0</v>
       </c>
       <c r="I38" s="44">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="J38" s="44">
-        <f t="shared" si="34"/>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="76">
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="K38" s="44">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="L38" s="78">
-        <f t="shared" si="34"/>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="L38" s="76">
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="M38" s="44">
-        <f t="shared" si="34"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="N38" s="44">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="O38" s="44">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="P38" s="44">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="Q38" s="44">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="R38" s="44">
-        <f t="shared" si="34"/>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="O38" s="76">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="P38" s="76">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="Q38" s="76">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="R38" s="76">
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="S38" s="44">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="T38" s="44"/>
-      <c r="U38" s="44"/>
-      <c r="V38" s="44"/>
-      <c r="W38" s="44"/>
-      <c r="X38" s="44"/>
-      <c r="Y38" s="44"/>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="T38" s="44">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="44">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="V38" s="44">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="W38" s="44">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="X38" s="44">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="Y38" s="44">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
       <c r="Z38" s="44">
-        <f>SUM(Z36:Z37)</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AA38" s="44">
-        <f>SUM(AA37:AA37)</f>
-        <v>0</v>
-      </c>
-      <c r="AB38" s="44"/>
-      <c r="AC38" s="44"/>
-      <c r="AD38" s="44"/>
-      <c r="AE38" s="44"/>
-      <c r="AF38" s="44"/>
-      <c r="AG38" s="44"/>
-      <c r="AH38" s="44"/>
-      <c r="AI38" s="44"/>
-      <c r="AJ38" s="44"/>
-      <c r="AK38" s="44"/>
-      <c r="AL38" s="100"/>
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AB38" s="44">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AC38" s="44">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AD38" s="44">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AE38" s="44">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AF38" s="44">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AG38" s="44">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AH38" s="44">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AI38" s="44">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AJ38" s="44">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AK38" s="44">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="AL38" s="96"/>
     </row>
     <row r="39" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A39" s="33"/>
@@ -5592,57 +5346,35 @@
       <c r="G39" s="40"/>
       <c r="H39" s="36"/>
       <c r="I39" s="36"/>
-      <c r="J39" s="58">
-        <v>0</v>
-      </c>
-      <c r="K39" s="75">
-        <v>0</v>
-      </c>
-      <c r="L39" s="76">
-        <f>J39-N39-P39</f>
-        <v>0</v>
-      </c>
-      <c r="M39" s="58"/>
-      <c r="N39" s="58"/>
-      <c r="O39" s="36">
-        <f t="shared" ref="O39:O45" si="35">L39-M39</f>
-        <v>0</v>
-      </c>
-      <c r="P39" s="36">
-        <f t="shared" ref="P39:P45" si="36">K39-N39</f>
-        <v>0</v>
-      </c>
-      <c r="Q39" s="36">
-        <f t="shared" ref="Q39:Q45" si="37">M39+O39</f>
-        <v>0</v>
-      </c>
-      <c r="R39" s="36">
-        <f t="shared" ref="R39:R45" si="38">M39+N39+O39+P39</f>
-        <v>0</v>
-      </c>
-      <c r="S39" s="88">
-        <f t="shared" ref="S39:S45" si="39">SUM(T39:V39)</f>
-        <v>0</v>
-      </c>
-      <c r="T39" s="88"/>
-      <c r="U39" s="88"/>
-      <c r="V39" s="88"/>
-      <c r="W39" s="88"/>
-      <c r="X39" s="88"/>
-      <c r="Y39" s="88"/>
-      <c r="Z39" s="88"/>
-      <c r="AA39" s="88"/>
-      <c r="AB39" s="88"/>
-      <c r="AC39" s="88"/>
-      <c r="AD39" s="88"/>
-      <c r="AE39" s="88"/>
-      <c r="AF39" s="88"/>
-      <c r="AG39" s="88"/>
-      <c r="AH39" s="88"/>
-      <c r="AI39" s="88"/>
-      <c r="AJ39" s="88"/>
-      <c r="AK39" s="85"/>
-      <c r="AL39" s="100"/>
+      <c r="J39" s="75"/>
+      <c r="K39" s="36"/>
+      <c r="L39" s="75"/>
+      <c r="M39" s="36"/>
+      <c r="N39" s="36"/>
+      <c r="O39" s="75"/>
+      <c r="P39" s="75"/>
+      <c r="Q39" s="75"/>
+      <c r="R39" s="75"/>
+      <c r="S39" s="36"/>
+      <c r="T39" s="36"/>
+      <c r="U39" s="36"/>
+      <c r="V39" s="36"/>
+      <c r="W39" s="36"/>
+      <c r="X39" s="36"/>
+      <c r="Y39" s="36"/>
+      <c r="Z39" s="36"/>
+      <c r="AA39" s="36"/>
+      <c r="AB39" s="36"/>
+      <c r="AC39" s="36"/>
+      <c r="AD39" s="36"/>
+      <c r="AE39" s="36"/>
+      <c r="AF39" s="36"/>
+      <c r="AG39" s="36"/>
+      <c r="AH39" s="36"/>
+      <c r="AI39" s="36"/>
+      <c r="AJ39" s="36"/>
+      <c r="AK39" s="36"/>
+      <c r="AL39" s="96"/>
     </row>
     <row r="40" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A40" s="33">
@@ -5656,61 +5388,53 @@
       <c r="G40" s="40"/>
       <c r="H40" s="36"/>
       <c r="I40" s="36"/>
-      <c r="J40" s="36">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="K40" s="75">
-        <v>0</v>
-      </c>
-      <c r="L40" s="76">
-        <f t="shared" ref="L40:L45" si="40">J40-K40</f>
-        <v>0</v>
-      </c>
-      <c r="M40" s="59"/>
-      <c r="N40" s="59"/>
-      <c r="O40" s="36">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="P40" s="36">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="Q40" s="36">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="R40" s="36">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="S40" s="88">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="T40" s="59"/>
-      <c r="U40" s="59"/>
-      <c r="V40" s="59"/>
-      <c r="W40" s="59"/>
-      <c r="X40" s="59"/>
-      <c r="Y40" s="59"/>
-      <c r="Z40" s="36">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AA40" s="88"/>
-      <c r="AB40" s="88"/>
-      <c r="AC40" s="88"/>
-      <c r="AD40" s="88"/>
-      <c r="AE40" s="88"/>
-      <c r="AF40" s="88"/>
-      <c r="AG40" s="88"/>
-      <c r="AH40" s="88"/>
-      <c r="AI40" s="88"/>
-      <c r="AJ40" s="88"/>
-      <c r="AK40" s="85"/>
-      <c r="AL40" s="100"/>
+      <c r="J40" s="75">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="K40" s="36"/>
+      <c r="L40" s="75">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="M40" s="36"/>
+      <c r="N40" s="36"/>
+      <c r="O40" s="75">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="P40" s="75">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="Q40" s="75">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="R40" s="75">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="36"/>
+      <c r="T40" s="36"/>
+      <c r="U40" s="36"/>
+      <c r="V40" s="36"/>
+      <c r="W40" s="36"/>
+      <c r="X40" s="36"/>
+      <c r="Y40" s="36"/>
+      <c r="Z40" s="36"/>
+      <c r="AA40" s="36"/>
+      <c r="AB40" s="36"/>
+      <c r="AC40" s="36"/>
+      <c r="AD40" s="36"/>
+      <c r="AE40" s="36"/>
+      <c r="AF40" s="36"/>
+      <c r="AG40" s="36"/>
+      <c r="AH40" s="36"/>
+      <c r="AI40" s="36"/>
+      <c r="AJ40" s="36"/>
+      <c r="AK40" s="36"/>
+      <c r="AL40" s="96"/>
     </row>
     <row r="41" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A41" s="33">
@@ -5724,61 +5448,53 @@
       <c r="G41" s="40"/>
       <c r="H41" s="36"/>
       <c r="I41" s="36"/>
-      <c r="J41" s="36">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="K41" s="75">
-        <v>0</v>
-      </c>
-      <c r="L41" s="76">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="M41" s="59"/>
-      <c r="N41" s="59"/>
-      <c r="O41" s="36">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="P41" s="36">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="Q41" s="36">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="R41" s="36">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="S41" s="88">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="T41" s="59"/>
-      <c r="U41" s="59"/>
-      <c r="V41" s="59"/>
-      <c r="W41" s="59"/>
-      <c r="X41" s="59"/>
-      <c r="Y41" s="59"/>
-      <c r="Z41" s="36">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AA41" s="88"/>
-      <c r="AB41" s="88"/>
-      <c r="AC41" s="88"/>
-      <c r="AD41" s="88"/>
-      <c r="AE41" s="88"/>
-      <c r="AF41" s="88"/>
-      <c r="AG41" s="88"/>
-      <c r="AH41" s="88"/>
-      <c r="AI41" s="88"/>
-      <c r="AJ41" s="88"/>
-      <c r="AK41" s="85"/>
-      <c r="AL41" s="100"/>
+      <c r="J41" s="75">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="K41" s="36"/>
+      <c r="L41" s="75">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="M41" s="36"/>
+      <c r="N41" s="36"/>
+      <c r="O41" s="75">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="P41" s="75">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="Q41" s="75">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="R41" s="75">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="S41" s="36"/>
+      <c r="T41" s="36"/>
+      <c r="U41" s="36"/>
+      <c r="V41" s="36"/>
+      <c r="W41" s="36"/>
+      <c r="X41" s="36"/>
+      <c r="Y41" s="36"/>
+      <c r="Z41" s="36"/>
+      <c r="AA41" s="36"/>
+      <c r="AB41" s="36"/>
+      <c r="AC41" s="36"/>
+      <c r="AD41" s="36"/>
+      <c r="AE41" s="36"/>
+      <c r="AF41" s="36"/>
+      <c r="AG41" s="36"/>
+      <c r="AH41" s="36"/>
+      <c r="AI41" s="36"/>
+      <c r="AJ41" s="36"/>
+      <c r="AK41" s="36"/>
+      <c r="AL41" s="96"/>
     </row>
     <row r="42" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A42" s="33">
@@ -5792,61 +5508,53 @@
       <c r="G42" s="40"/>
       <c r="H42" s="36"/>
       <c r="I42" s="36"/>
-      <c r="J42" s="36">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="K42" s="75">
-        <v>0</v>
-      </c>
-      <c r="L42" s="76">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="M42" s="59"/>
-      <c r="N42" s="59"/>
-      <c r="O42" s="36">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="P42" s="36">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="Q42" s="36">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="R42" s="36">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="S42" s="88">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="T42" s="59"/>
-      <c r="U42" s="59"/>
-      <c r="V42" s="59"/>
-      <c r="W42" s="59"/>
-      <c r="X42" s="59"/>
-      <c r="Y42" s="59"/>
-      <c r="Z42" s="36">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AA42" s="88"/>
-      <c r="AB42" s="88"/>
-      <c r="AC42" s="88"/>
-      <c r="AD42" s="88"/>
-      <c r="AE42" s="88"/>
-      <c r="AF42" s="88"/>
-      <c r="AG42" s="88"/>
-      <c r="AH42" s="88"/>
-      <c r="AI42" s="88"/>
-      <c r="AJ42" s="88"/>
-      <c r="AK42" s="85"/>
-      <c r="AL42" s="100"/>
+      <c r="J42" s="75">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="K42" s="36"/>
+      <c r="L42" s="75">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="M42" s="36"/>
+      <c r="N42" s="36"/>
+      <c r="O42" s="75">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="P42" s="75">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="Q42" s="75">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="R42" s="75">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="S42" s="36"/>
+      <c r="T42" s="36"/>
+      <c r="U42" s="36"/>
+      <c r="V42" s="36"/>
+      <c r="W42" s="36"/>
+      <c r="X42" s="36"/>
+      <c r="Y42" s="36"/>
+      <c r="Z42" s="36"/>
+      <c r="AA42" s="36"/>
+      <c r="AB42" s="36"/>
+      <c r="AC42" s="36"/>
+      <c r="AD42" s="36"/>
+      <c r="AE42" s="36"/>
+      <c r="AF42" s="36"/>
+      <c r="AG42" s="36"/>
+      <c r="AH42" s="36"/>
+      <c r="AI42" s="36"/>
+      <c r="AJ42" s="36"/>
+      <c r="AK42" s="36"/>
+      <c r="AL42" s="96"/>
     </row>
     <row r="43" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A43" s="33">
@@ -5860,61 +5568,53 @@
       <c r="G43" s="40"/>
       <c r="H43" s="36"/>
       <c r="I43" s="36"/>
-      <c r="J43" s="36">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="K43" s="75">
-        <v>0</v>
-      </c>
-      <c r="L43" s="76">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="M43" s="59"/>
-      <c r="N43" s="59"/>
-      <c r="O43" s="36">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="P43" s="36">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="Q43" s="36">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="R43" s="36">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="S43" s="88">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="T43" s="59"/>
-      <c r="U43" s="59"/>
-      <c r="V43" s="59"/>
-      <c r="W43" s="59"/>
-      <c r="X43" s="59"/>
-      <c r="Y43" s="59"/>
-      <c r="Z43" s="36">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AA43" s="88"/>
-      <c r="AB43" s="88"/>
-      <c r="AC43" s="88"/>
-      <c r="AD43" s="88"/>
-      <c r="AE43" s="88"/>
-      <c r="AF43" s="88"/>
-      <c r="AG43" s="88"/>
-      <c r="AH43" s="88"/>
-      <c r="AI43" s="88"/>
-      <c r="AJ43" s="88"/>
-      <c r="AK43" s="85"/>
-      <c r="AL43" s="100"/>
+      <c r="J43" s="75">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="K43" s="36"/>
+      <c r="L43" s="75">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="M43" s="36"/>
+      <c r="N43" s="36"/>
+      <c r="O43" s="75">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="P43" s="75">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="Q43" s="75">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="R43" s="75">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="36"/>
+      <c r="T43" s="36"/>
+      <c r="U43" s="36"/>
+      <c r="V43" s="36"/>
+      <c r="W43" s="36"/>
+      <c r="X43" s="36"/>
+      <c r="Y43" s="36"/>
+      <c r="Z43" s="36"/>
+      <c r="AA43" s="36"/>
+      <c r="AB43" s="36"/>
+      <c r="AC43" s="36"/>
+      <c r="AD43" s="36"/>
+      <c r="AE43" s="36"/>
+      <c r="AF43" s="36"/>
+      <c r="AG43" s="36"/>
+      <c r="AH43" s="36"/>
+      <c r="AI43" s="36"/>
+      <c r="AJ43" s="36"/>
+      <c r="AK43" s="36"/>
+      <c r="AL43" s="96"/>
     </row>
     <row r="44" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A44" s="33">
@@ -5928,63 +5628,53 @@
       <c r="G44" s="40"/>
       <c r="H44" s="36"/>
       <c r="I44" s="36"/>
-      <c r="J44" s="36">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="K44" s="75">
-        <v>0</v>
-      </c>
-      <c r="L44" s="76">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="M44" s="59"/>
-      <c r="N44" s="59">
-        <v>0</v>
-      </c>
-      <c r="O44" s="36">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="P44" s="36">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="Q44" s="36">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="R44" s="36">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="S44" s="88">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="T44" s="59"/>
-      <c r="U44" s="59"/>
-      <c r="V44" s="59"/>
-      <c r="W44" s="59"/>
-      <c r="X44" s="59"/>
-      <c r="Y44" s="59"/>
-      <c r="Z44" s="36">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AA44" s="88"/>
-      <c r="AB44" s="88"/>
-      <c r="AC44" s="88"/>
-      <c r="AD44" s="88"/>
-      <c r="AE44" s="88"/>
-      <c r="AF44" s="88"/>
-      <c r="AG44" s="88"/>
-      <c r="AH44" s="88"/>
-      <c r="AI44" s="88"/>
-      <c r="AJ44" s="88"/>
-      <c r="AK44" s="85"/>
-      <c r="AL44" s="100"/>
+      <c r="J44" s="75">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="K44" s="36"/>
+      <c r="L44" s="75">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="M44" s="36"/>
+      <c r="N44" s="36"/>
+      <c r="O44" s="75">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="P44" s="75">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="Q44" s="75">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="R44" s="75">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="S44" s="36"/>
+      <c r="T44" s="36"/>
+      <c r="U44" s="36"/>
+      <c r="V44" s="36"/>
+      <c r="W44" s="36"/>
+      <c r="X44" s="36"/>
+      <c r="Y44" s="36"/>
+      <c r="Z44" s="36"/>
+      <c r="AA44" s="36"/>
+      <c r="AB44" s="36"/>
+      <c r="AC44" s="36"/>
+      <c r="AD44" s="36"/>
+      <c r="AE44" s="36"/>
+      <c r="AF44" s="36"/>
+      <c r="AG44" s="36"/>
+      <c r="AH44" s="36"/>
+      <c r="AI44" s="36"/>
+      <c r="AJ44" s="36"/>
+      <c r="AK44" s="36"/>
+      <c r="AL44" s="96"/>
     </row>
     <row r="45" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A45" s="33"/>
@@ -5998,56 +5688,35 @@
       <c r="G45" s="40"/>
       <c r="H45" s="36"/>
       <c r="I45" s="36"/>
-      <c r="J45" s="58"/>
-      <c r="K45" s="75"/>
-      <c r="L45" s="76">
-        <f t="shared" si="40"/>
-        <v>0</v>
-      </c>
-      <c r="M45" s="59"/>
-      <c r="N45" s="59"/>
-      <c r="O45" s="36">
-        <f t="shared" si="35"/>
-        <v>0</v>
-      </c>
-      <c r="P45" s="36">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="Q45" s="36">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="R45" s="36">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="S45" s="88">
-        <f t="shared" si="39"/>
-        <v>0</v>
-      </c>
-      <c r="T45" s="59"/>
-      <c r="U45" s="59"/>
-      <c r="V45" s="59"/>
-      <c r="W45" s="59"/>
-      <c r="X45" s="59"/>
-      <c r="Y45" s="59"/>
-      <c r="Z45" s="36">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="AA45" s="88"/>
-      <c r="AB45" s="88"/>
-      <c r="AC45" s="88"/>
-      <c r="AD45" s="88"/>
-      <c r="AE45" s="88"/>
-      <c r="AF45" s="88"/>
-      <c r="AG45" s="88"/>
-      <c r="AH45" s="88"/>
-      <c r="AI45" s="88"/>
-      <c r="AJ45" s="88"/>
-      <c r="AK45" s="85"/>
-      <c r="AL45" s="100"/>
+      <c r="J45" s="75"/>
+      <c r="K45" s="36"/>
+      <c r="L45" s="75"/>
+      <c r="M45" s="36"/>
+      <c r="N45" s="36"/>
+      <c r="O45" s="75"/>
+      <c r="P45" s="75"/>
+      <c r="Q45" s="75"/>
+      <c r="R45" s="75"/>
+      <c r="S45" s="36"/>
+      <c r="T45" s="36"/>
+      <c r="U45" s="36"/>
+      <c r="V45" s="36"/>
+      <c r="W45" s="36"/>
+      <c r="X45" s="36"/>
+      <c r="Y45" s="36"/>
+      <c r="Z45" s="36"/>
+      <c r="AA45" s="36"/>
+      <c r="AB45" s="36"/>
+      <c r="AC45" s="36"/>
+      <c r="AD45" s="36"/>
+      <c r="AE45" s="36"/>
+      <c r="AF45" s="36"/>
+      <c r="AG45" s="36"/>
+      <c r="AH45" s="36"/>
+      <c r="AI45" s="36"/>
+      <c r="AJ45" s="36"/>
+      <c r="AK45" s="36"/>
+      <c r="AL45" s="96"/>
     </row>
     <row r="46" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A46" s="55"/>
@@ -6060,102 +5729,126 @@
       <c r="F46" s="57"/>
       <c r="G46" s="57"/>
       <c r="H46" s="44">
-        <f t="shared" ref="H46:L46" si="41">SUM(H39:H44)</f>
+        <f t="shared" ref="H46:AK46" si="32">SUM(H40:H45)</f>
         <v>0</v>
       </c>
       <c r="I46" s="44">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="J46" s="44">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="76">
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K46" s="44">
-        <f t="shared" si="41"/>
-        <v>0</v>
-      </c>
-      <c r="L46" s="78">
-        <f t="shared" si="41"/>
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="L46" s="76">
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="M46" s="44">
-        <f>SUM(M40:M44)</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="N46" s="44">
-        <f t="shared" ref="M46:P46" si="42">SUM(N40:N44)</f>
-        <v>0</v>
-      </c>
-      <c r="O46" s="44">
-        <f t="shared" ref="O46:O60" si="43">L46-M46</f>
-        <v>0</v>
-      </c>
-      <c r="P46" s="44">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="Q46" s="44">
-        <f t="shared" ref="Q46:Q60" si="44">M46+O46</f>
-        <v>0</v>
-      </c>
-      <c r="R46" s="44">
-        <f>SUM(R40:R44)</f>
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="O46" s="76">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="P46" s="76">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="Q46" s="76">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="R46" s="76">
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="S46" s="44">
-        <f>SUM(S40:S44)</f>
-        <v>0</v>
-      </c>
-      <c r="T46" s="44"/>
-      <c r="U46" s="44"/>
-      <c r="V46" s="44"/>
-      <c r="W46" s="44"/>
-      <c r="X46" s="44"/>
-      <c r="Y46" s="44"/>
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="U46" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="V46" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="W46" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="X46" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="Y46" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="Z46" s="44">
-        <f t="shared" ref="Z46:AF46" si="45">SUM(Z40:Z44)</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AA46" s="44">
-        <f t="shared" si="45"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AB46" s="44">
-        <f t="shared" si="45"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AC46" s="44">
-        <f t="shared" si="45"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AD46" s="44">
-        <f t="shared" si="45"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AE46" s="44">
-        <f t="shared" si="45"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AF46" s="44">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="AG46" s="44"/>
-      <c r="AH46" s="44"/>
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="AG46" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="AH46" s="44">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
       <c r="AI46" s="44">
-        <f t="shared" ref="AI46:AK46" si="46">SUM(AI40:AI44)</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AJ46" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AK46" s="44">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="AL46" s="100"/>
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="AL46" s="96"/>
     </row>
     <row r="47" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A47" s="33"/>
@@ -6168,58 +5861,36 @@
       <c r="F47" s="40"/>
       <c r="G47" s="40"/>
       <c r="H47" s="58"/>
-      <c r="I47" s="36"/>
-      <c r="J47" s="36">
-        <v>0</v>
-      </c>
-      <c r="K47" s="75">
-        <v>0</v>
-      </c>
-      <c r="L47" s="76">
-        <f>J47-N47-P47</f>
-        <v>0</v>
-      </c>
+      <c r="I47" s="58"/>
+      <c r="J47" s="76"/>
+      <c r="K47" s="58"/>
+      <c r="L47" s="76"/>
       <c r="M47" s="58"/>
       <c r="N47" s="58"/>
-      <c r="O47" s="36">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="P47" s="36">
-        <f t="shared" ref="P47:P60" si="47">K47-N47</f>
-        <v>0</v>
-      </c>
-      <c r="Q47" s="36">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="R47" s="36">
-        <f t="shared" ref="R47:R60" si="48">M47+N47+O47+P47</f>
-        <v>0</v>
-      </c>
-      <c r="S47" s="88">
-        <f t="shared" ref="S47:S60" si="49">SUM(T47:V47)</f>
-        <v>0</v>
-      </c>
-      <c r="T47" s="88"/>
-      <c r="U47" s="88"/>
-      <c r="V47" s="88"/>
-      <c r="W47" s="88"/>
-      <c r="X47" s="88"/>
-      <c r="Y47" s="88"/>
-      <c r="Z47" s="88"/>
-      <c r="AA47" s="88"/>
-      <c r="AB47" s="88"/>
-      <c r="AC47" s="88"/>
-      <c r="AD47" s="88"/>
-      <c r="AE47" s="88"/>
-      <c r="AF47" s="88"/>
-      <c r="AG47" s="88"/>
-      <c r="AH47" s="88"/>
-      <c r="AI47" s="88"/>
-      <c r="AJ47" s="88"/>
-      <c r="AK47" s="85"/>
-      <c r="AL47" s="100"/>
+      <c r="O47" s="76"/>
+      <c r="P47" s="76"/>
+      <c r="Q47" s="76"/>
+      <c r="R47" s="76"/>
+      <c r="S47" s="58"/>
+      <c r="T47" s="58"/>
+      <c r="U47" s="58"/>
+      <c r="V47" s="58"/>
+      <c r="W47" s="58"/>
+      <c r="X47" s="58"/>
+      <c r="Y47" s="58"/>
+      <c r="Z47" s="58"/>
+      <c r="AA47" s="58"/>
+      <c r="AB47" s="58"/>
+      <c r="AC47" s="58"/>
+      <c r="AD47" s="58"/>
+      <c r="AE47" s="58"/>
+      <c r="AF47" s="58"/>
+      <c r="AG47" s="58"/>
+      <c r="AH47" s="58"/>
+      <c r="AI47" s="58"/>
+      <c r="AJ47" s="58"/>
+      <c r="AK47" s="58"/>
+      <c r="AL47" s="96"/>
     </row>
     <row r="48" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A48" s="33">
@@ -6232,62 +5903,54 @@
       <c r="F48" s="40"/>
       <c r="G48" s="40"/>
       <c r="H48" s="59"/>
-      <c r="I48" s="36"/>
-      <c r="J48" s="59">
-        <f t="shared" ref="J48:J59" si="50">H48+I48</f>
-        <v>0</v>
-      </c>
-      <c r="K48" s="75">
-        <v>0</v>
-      </c>
-      <c r="L48" s="76">
-        <f t="shared" ref="L48:L59" si="51">J48-K48</f>
+      <c r="I48" s="59"/>
+      <c r="J48" s="75">
+        <f t="shared" ref="J48:J59" si="33">H48+I48</f>
+        <v>0</v>
+      </c>
+      <c r="K48" s="59"/>
+      <c r="L48" s="75">
+        <f t="shared" ref="L48:L59" si="34">J48-K48</f>
         <v>0</v>
       </c>
       <c r="M48" s="59"/>
       <c r="N48" s="59"/>
-      <c r="O48" s="36">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="P48" s="36">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="Q48" s="36">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="R48" s="36">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="S48" s="88">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
+      <c r="O48" s="75">
+        <f t="shared" ref="O48:O59" si="35">L48-M48</f>
+        <v>0</v>
+      </c>
+      <c r="P48" s="75">
+        <f t="shared" ref="P48:P59" si="36">K48-N48</f>
+        <v>0</v>
+      </c>
+      <c r="Q48" s="75">
+        <f t="shared" ref="Q48:Q59" si="37">M48+O48</f>
+        <v>0</v>
+      </c>
+      <c r="R48" s="75">
+        <f t="shared" ref="R48:R59" si="38">M48+N48+O48+P48</f>
+        <v>0</v>
+      </c>
+      <c r="S48" s="59"/>
       <c r="T48" s="59"/>
       <c r="U48" s="59"/>
       <c r="V48" s="59"/>
       <c r="W48" s="59"/>
       <c r="X48" s="59"/>
       <c r="Y48" s="59"/>
-      <c r="Z48" s="36">
-        <f t="shared" ref="Z48:Z59" si="52">SUM(AA48:AJ48)</f>
-        <v>0</v>
-      </c>
-      <c r="AA48" s="88"/>
-      <c r="AB48" s="88"/>
-      <c r="AC48" s="88"/>
-      <c r="AD48" s="88"/>
-      <c r="AE48" s="88"/>
-      <c r="AF48" s="88"/>
-      <c r="AG48" s="88"/>
-      <c r="AH48" s="88"/>
-      <c r="AI48" s="88"/>
-      <c r="AJ48" s="88"/>
-      <c r="AK48" s="85"/>
-      <c r="AL48" s="100"/>
+      <c r="Z48" s="59"/>
+      <c r="AA48" s="59"/>
+      <c r="AB48" s="59"/>
+      <c r="AC48" s="59"/>
+      <c r="AD48" s="59"/>
+      <c r="AE48" s="59"/>
+      <c r="AF48" s="59"/>
+      <c r="AG48" s="59"/>
+      <c r="AH48" s="59"/>
+      <c r="AI48" s="59"/>
+      <c r="AJ48" s="59"/>
+      <c r="AK48" s="59"/>
+      <c r="AL48" s="96"/>
     </row>
     <row r="49" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A49" s="33">
@@ -6300,62 +5963,54 @@
       <c r="F49" s="40"/>
       <c r="G49" s="40"/>
       <c r="H49" s="59"/>
-      <c r="I49" s="36"/>
-      <c r="J49" s="59">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="K49" s="75">
-        <v>0</v>
-      </c>
-      <c r="L49" s="76">
-        <f t="shared" si="51"/>
+      <c r="I49" s="59"/>
+      <c r="J49" s="75">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="K49" s="59"/>
+      <c r="L49" s="75">
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M49" s="59"/>
       <c r="N49" s="59"/>
-      <c r="O49" s="36">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="P49" s="36">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="Q49" s="36">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="R49" s="36">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="S49" s="88">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
+      <c r="O49" s="75">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="P49" s="75">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="Q49" s="75">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="R49" s="75">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="59"/>
       <c r="T49" s="59"/>
       <c r="U49" s="59"/>
       <c r="V49" s="59"/>
       <c r="W49" s="59"/>
       <c r="X49" s="59"/>
       <c r="Y49" s="59"/>
-      <c r="Z49" s="36">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="AA49" s="88"/>
-      <c r="AB49" s="88"/>
-      <c r="AC49" s="88"/>
-      <c r="AD49" s="88"/>
-      <c r="AE49" s="88"/>
-      <c r="AF49" s="88"/>
-      <c r="AG49" s="88"/>
-      <c r="AH49" s="88"/>
-      <c r="AI49" s="88"/>
-      <c r="AJ49" s="88"/>
-      <c r="AK49" s="85"/>
-      <c r="AL49" s="100"/>
+      <c r="Z49" s="59"/>
+      <c r="AA49" s="59"/>
+      <c r="AB49" s="59"/>
+      <c r="AC49" s="59"/>
+      <c r="AD49" s="59"/>
+      <c r="AE49" s="59"/>
+      <c r="AF49" s="59"/>
+      <c r="AG49" s="59"/>
+      <c r="AH49" s="59"/>
+      <c r="AI49" s="59"/>
+      <c r="AJ49" s="59"/>
+      <c r="AK49" s="59"/>
+      <c r="AL49" s="96"/>
     </row>
     <row r="50" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A50" s="33">
@@ -6368,62 +6023,54 @@
       <c r="F50" s="40"/>
       <c r="G50" s="40"/>
       <c r="H50" s="59"/>
-      <c r="I50" s="36"/>
-      <c r="J50" s="59">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="K50" s="75">
-        <v>0</v>
-      </c>
-      <c r="L50" s="76">
-        <f t="shared" si="51"/>
+      <c r="I50" s="59"/>
+      <c r="J50" s="75">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="K50" s="59"/>
+      <c r="L50" s="75">
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M50" s="59"/>
-      <c r="N50" s="36"/>
-      <c r="O50" s="36">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="P50" s="36">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="Q50" s="36">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="R50" s="36">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="S50" s="88">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
+      <c r="N50" s="59"/>
+      <c r="O50" s="75">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="P50" s="75">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="Q50" s="75">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="R50" s="75">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="59"/>
       <c r="T50" s="59"/>
       <c r="U50" s="59"/>
       <c r="V50" s="59"/>
       <c r="W50" s="59"/>
       <c r="X50" s="59"/>
       <c r="Y50" s="59"/>
-      <c r="Z50" s="36">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="AA50" s="88"/>
-      <c r="AB50" s="88"/>
-      <c r="AC50" s="88"/>
-      <c r="AD50" s="88"/>
-      <c r="AE50" s="88"/>
-      <c r="AF50" s="88"/>
-      <c r="AG50" s="88"/>
-      <c r="AH50" s="88"/>
-      <c r="AI50" s="88"/>
-      <c r="AJ50" s="88"/>
-      <c r="AK50" s="85"/>
-      <c r="AL50" s="100"/>
+      <c r="Z50" s="59"/>
+      <c r="AA50" s="59"/>
+      <c r="AB50" s="59"/>
+      <c r="AC50" s="59"/>
+      <c r="AD50" s="59"/>
+      <c r="AE50" s="59"/>
+      <c r="AF50" s="59"/>
+      <c r="AG50" s="59"/>
+      <c r="AH50" s="59"/>
+      <c r="AI50" s="59"/>
+      <c r="AJ50" s="59"/>
+      <c r="AK50" s="59"/>
+      <c r="AL50" s="96"/>
     </row>
     <row r="51" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A51" s="33">
@@ -6436,62 +6083,54 @@
       <c r="F51" s="40"/>
       <c r="G51" s="40"/>
       <c r="H51" s="59"/>
-      <c r="I51" s="36"/>
-      <c r="J51" s="59">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="K51" s="75">
-        <v>0</v>
-      </c>
-      <c r="L51" s="76">
-        <f t="shared" si="51"/>
+      <c r="I51" s="59"/>
+      <c r="J51" s="75">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="K51" s="59"/>
+      <c r="L51" s="75">
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M51" s="59"/>
       <c r="N51" s="59"/>
-      <c r="O51" s="36">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="P51" s="36">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="Q51" s="36">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="R51" s="36">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="S51" s="88">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
+      <c r="O51" s="75">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="P51" s="75">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="Q51" s="75">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="R51" s="75">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="59"/>
       <c r="T51" s="59"/>
       <c r="U51" s="59"/>
       <c r="V51" s="59"/>
       <c r="W51" s="59"/>
       <c r="X51" s="59"/>
       <c r="Y51" s="59"/>
-      <c r="Z51" s="36">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="AA51" s="88"/>
-      <c r="AB51" s="88"/>
-      <c r="AC51" s="88"/>
-      <c r="AD51" s="88"/>
-      <c r="AE51" s="88"/>
-      <c r="AF51" s="88"/>
-      <c r="AG51" s="88"/>
-      <c r="AH51" s="88"/>
-      <c r="AI51" s="88"/>
-      <c r="AJ51" s="88"/>
-      <c r="AK51" s="85"/>
-      <c r="AL51" s="100"/>
+      <c r="Z51" s="59"/>
+      <c r="AA51" s="59"/>
+      <c r="AB51" s="59"/>
+      <c r="AC51" s="59"/>
+      <c r="AD51" s="59"/>
+      <c r="AE51" s="59"/>
+      <c r="AF51" s="59"/>
+      <c r="AG51" s="59"/>
+      <c r="AH51" s="59"/>
+      <c r="AI51" s="59"/>
+      <c r="AJ51" s="59"/>
+      <c r="AK51" s="59"/>
+      <c r="AL51" s="96"/>
     </row>
     <row r="52" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A52" s="33">
@@ -6504,62 +6143,54 @@
       <c r="F52" s="40"/>
       <c r="G52" s="40"/>
       <c r="H52" s="59"/>
-      <c r="I52" s="36"/>
-      <c r="J52" s="59">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="K52" s="75">
-        <v>0</v>
-      </c>
-      <c r="L52" s="76">
-        <f t="shared" si="51"/>
+      <c r="I52" s="59"/>
+      <c r="J52" s="75">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="K52" s="59"/>
+      <c r="L52" s="75">
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M52" s="59"/>
       <c r="N52" s="59"/>
-      <c r="O52" s="36">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="P52" s="36">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="Q52" s="36">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="R52" s="36">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="S52" s="88">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
+      <c r="O52" s="75">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="P52" s="75">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="Q52" s="75">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="R52" s="75">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="59"/>
       <c r="T52" s="59"/>
       <c r="U52" s="59"/>
       <c r="V52" s="59"/>
       <c r="W52" s="59"/>
       <c r="X52" s="59"/>
       <c r="Y52" s="59"/>
-      <c r="Z52" s="36">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="AA52" s="88"/>
-      <c r="AB52" s="88"/>
-      <c r="AC52" s="88"/>
-      <c r="AD52" s="88"/>
-      <c r="AE52" s="88"/>
-      <c r="AF52" s="88"/>
-      <c r="AG52" s="88"/>
-      <c r="AH52" s="88"/>
-      <c r="AI52" s="88"/>
-      <c r="AJ52" s="88"/>
-      <c r="AK52" s="85"/>
-      <c r="AL52" s="100"/>
+      <c r="Z52" s="59"/>
+      <c r="AA52" s="59"/>
+      <c r="AB52" s="59"/>
+      <c r="AC52" s="59"/>
+      <c r="AD52" s="59"/>
+      <c r="AE52" s="59"/>
+      <c r="AF52" s="59"/>
+      <c r="AG52" s="59"/>
+      <c r="AH52" s="59"/>
+      <c r="AI52" s="59"/>
+      <c r="AJ52" s="59"/>
+      <c r="AK52" s="59"/>
+      <c r="AL52" s="96"/>
     </row>
     <row r="53" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A53" s="33">
@@ -6572,62 +6203,54 @@
       <c r="F53" s="40"/>
       <c r="G53" s="40"/>
       <c r="H53" s="59"/>
-      <c r="I53" s="36"/>
-      <c r="J53" s="59">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="K53" s="75">
-        <v>0</v>
-      </c>
-      <c r="L53" s="76">
-        <f t="shared" si="51"/>
+      <c r="I53" s="59"/>
+      <c r="J53" s="75">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="K53" s="59"/>
+      <c r="L53" s="75">
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M53" s="59"/>
       <c r="N53" s="59"/>
-      <c r="O53" s="36">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="P53" s="36">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="Q53" s="36">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="R53" s="36">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="S53" s="88">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
+      <c r="O53" s="75">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="P53" s="75">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="Q53" s="75">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="R53" s="75">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="59"/>
       <c r="T53" s="59"/>
       <c r="U53" s="59"/>
       <c r="V53" s="59"/>
       <c r="W53" s="59"/>
       <c r="X53" s="59"/>
       <c r="Y53" s="59"/>
-      <c r="Z53" s="36">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="AA53" s="88"/>
-      <c r="AB53" s="88"/>
-      <c r="AC53" s="88"/>
-      <c r="AD53" s="88"/>
-      <c r="AE53" s="88"/>
-      <c r="AF53" s="88"/>
-      <c r="AG53" s="88"/>
-      <c r="AH53" s="88"/>
-      <c r="AI53" s="88"/>
-      <c r="AJ53" s="88"/>
-      <c r="AK53" s="85"/>
-      <c r="AL53" s="100"/>
+      <c r="Z53" s="59"/>
+      <c r="AA53" s="59"/>
+      <c r="AB53" s="59"/>
+      <c r="AC53" s="59"/>
+      <c r="AD53" s="59"/>
+      <c r="AE53" s="59"/>
+      <c r="AF53" s="59"/>
+      <c r="AG53" s="59"/>
+      <c r="AH53" s="59"/>
+      <c r="AI53" s="59"/>
+      <c r="AJ53" s="59"/>
+      <c r="AK53" s="59"/>
+      <c r="AL53" s="96"/>
     </row>
     <row r="54" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A54" s="33">
@@ -6640,62 +6263,54 @@
       <c r="F54" s="40"/>
       <c r="G54" s="40"/>
       <c r="H54" s="59"/>
-      <c r="I54" s="36"/>
-      <c r="J54" s="59">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="K54" s="75">
-        <v>0</v>
-      </c>
-      <c r="L54" s="76">
-        <f t="shared" si="51"/>
+      <c r="I54" s="59"/>
+      <c r="J54" s="75">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="59"/>
+      <c r="L54" s="75">
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M54" s="59"/>
       <c r="N54" s="59"/>
-      <c r="O54" s="36">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="P54" s="36">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="Q54" s="36">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="R54" s="36">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="S54" s="88">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
+      <c r="O54" s="75">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="P54" s="75">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="Q54" s="75">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="R54" s="75">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="59"/>
       <c r="T54" s="59"/>
       <c r="U54" s="59"/>
       <c r="V54" s="59"/>
       <c r="W54" s="59"/>
       <c r="X54" s="59"/>
       <c r="Y54" s="59"/>
-      <c r="Z54" s="36">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="AA54" s="88"/>
-      <c r="AB54" s="88"/>
-      <c r="AC54" s="88"/>
-      <c r="AD54" s="88"/>
-      <c r="AE54" s="88"/>
-      <c r="AF54" s="88"/>
-      <c r="AG54" s="88"/>
-      <c r="AH54" s="88"/>
-      <c r="AI54" s="88"/>
-      <c r="AJ54" s="88"/>
-      <c r="AK54" s="85"/>
-      <c r="AL54" s="100"/>
+      <c r="Z54" s="59"/>
+      <c r="AA54" s="59"/>
+      <c r="AB54" s="59"/>
+      <c r="AC54" s="59"/>
+      <c r="AD54" s="59"/>
+      <c r="AE54" s="59"/>
+      <c r="AF54" s="59"/>
+      <c r="AG54" s="59"/>
+      <c r="AH54" s="59"/>
+      <c r="AI54" s="59"/>
+      <c r="AJ54" s="59"/>
+      <c r="AK54" s="59"/>
+      <c r="AL54" s="96"/>
     </row>
     <row r="55" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A55" s="33">
@@ -6708,62 +6323,54 @@
       <c r="F55" s="40"/>
       <c r="G55" s="40"/>
       <c r="H55" s="59"/>
-      <c r="I55" s="36"/>
-      <c r="J55" s="59">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="K55" s="75">
-        <v>0</v>
-      </c>
-      <c r="L55" s="76">
-        <f t="shared" si="51"/>
+      <c r="I55" s="59"/>
+      <c r="J55" s="75">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="59"/>
+      <c r="L55" s="75">
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M55" s="59"/>
-      <c r="N55" s="36"/>
-      <c r="O55" s="36">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="P55" s="36">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="Q55" s="36">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="R55" s="36">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="S55" s="88">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
+      <c r="N55" s="59"/>
+      <c r="O55" s="75">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="P55" s="75">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="Q55" s="75">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="R55" s="75">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="59"/>
       <c r="T55" s="59"/>
       <c r="U55" s="59"/>
       <c r="V55" s="59"/>
       <c r="W55" s="59"/>
       <c r="X55" s="59"/>
       <c r="Y55" s="59"/>
-      <c r="Z55" s="36">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="AA55" s="88"/>
-      <c r="AB55" s="88"/>
-      <c r="AC55" s="88"/>
-      <c r="AD55" s="88"/>
-      <c r="AE55" s="88"/>
-      <c r="AF55" s="88"/>
-      <c r="AG55" s="88"/>
-      <c r="AH55" s="88"/>
-      <c r="AI55" s="88"/>
-      <c r="AJ55" s="88"/>
-      <c r="AK55" s="85"/>
-      <c r="AL55" s="100"/>
+      <c r="Z55" s="59"/>
+      <c r="AA55" s="59"/>
+      <c r="AB55" s="59"/>
+      <c r="AC55" s="59"/>
+      <c r="AD55" s="59"/>
+      <c r="AE55" s="59"/>
+      <c r="AF55" s="59"/>
+      <c r="AG55" s="59"/>
+      <c r="AH55" s="59"/>
+      <c r="AI55" s="59"/>
+      <c r="AJ55" s="59"/>
+      <c r="AK55" s="59"/>
+      <c r="AL55" s="96"/>
     </row>
     <row r="56" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A56" s="33">
@@ -6776,62 +6383,54 @@
       <c r="F56" s="40"/>
       <c r="G56" s="40"/>
       <c r="H56" s="59"/>
-      <c r="I56" s="36"/>
-      <c r="J56" s="59">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="K56" s="75">
-        <v>0</v>
-      </c>
-      <c r="L56" s="76">
-        <f t="shared" si="51"/>
+      <c r="I56" s="59"/>
+      <c r="J56" s="75">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="59"/>
+      <c r="L56" s="75">
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M56" s="59"/>
       <c r="N56" s="59"/>
-      <c r="O56" s="36">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="P56" s="36">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="Q56" s="36">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="R56" s="36">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="S56" s="88">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
+      <c r="O56" s="75">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="P56" s="75">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="Q56" s="75">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="R56" s="75">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="59"/>
       <c r="T56" s="59"/>
       <c r="U56" s="59"/>
       <c r="V56" s="59"/>
       <c r="W56" s="59"/>
       <c r="X56" s="59"/>
       <c r="Y56" s="59"/>
-      <c r="Z56" s="36">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="AA56" s="88"/>
-      <c r="AB56" s="88"/>
-      <c r="AC56" s="88"/>
-      <c r="AD56" s="88"/>
-      <c r="AE56" s="88"/>
-      <c r="AF56" s="88"/>
-      <c r="AG56" s="88"/>
-      <c r="AH56" s="88"/>
-      <c r="AI56" s="88"/>
-      <c r="AJ56" s="88"/>
-      <c r="AK56" s="85"/>
-      <c r="AL56" s="100"/>
+      <c r="Z56" s="59"/>
+      <c r="AA56" s="59"/>
+      <c r="AB56" s="59"/>
+      <c r="AC56" s="59"/>
+      <c r="AD56" s="59"/>
+      <c r="AE56" s="59"/>
+      <c r="AF56" s="59"/>
+      <c r="AG56" s="59"/>
+      <c r="AH56" s="59"/>
+      <c r="AI56" s="59"/>
+      <c r="AJ56" s="59"/>
+      <c r="AK56" s="59"/>
+      <c r="AL56" s="96"/>
     </row>
     <row r="57" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A57" s="33">
@@ -6844,62 +6443,54 @@
       <c r="F57" s="40"/>
       <c r="G57" s="40"/>
       <c r="H57" s="59"/>
-      <c r="I57" s="36"/>
-      <c r="J57" s="59">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="K57" s="75">
-        <v>0</v>
-      </c>
-      <c r="L57" s="76">
-        <f t="shared" si="51"/>
+      <c r="I57" s="59"/>
+      <c r="J57" s="75">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="59"/>
+      <c r="L57" s="75">
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M57" s="59"/>
-      <c r="N57" s="36"/>
-      <c r="O57" s="36">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="P57" s="36">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="Q57" s="36">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="R57" s="36">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="S57" s="88">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
+      <c r="N57" s="59"/>
+      <c r="O57" s="75">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="P57" s="75">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="Q57" s="75">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="R57" s="75">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="59"/>
       <c r="T57" s="59"/>
       <c r="U57" s="59"/>
       <c r="V57" s="59"/>
       <c r="W57" s="59"/>
       <c r="X57" s="59"/>
       <c r="Y57" s="59"/>
-      <c r="Z57" s="36">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="AA57" s="88"/>
-      <c r="AB57" s="88"/>
-      <c r="AC57" s="88"/>
-      <c r="AD57" s="88"/>
-      <c r="AE57" s="88"/>
-      <c r="AF57" s="88"/>
-      <c r="AG57" s="88"/>
-      <c r="AH57" s="88"/>
-      <c r="AI57" s="88"/>
-      <c r="AJ57" s="88"/>
-      <c r="AK57" s="85"/>
-      <c r="AL57" s="100"/>
+      <c r="Z57" s="59"/>
+      <c r="AA57" s="59"/>
+      <c r="AB57" s="59"/>
+      <c r="AC57" s="59"/>
+      <c r="AD57" s="59"/>
+      <c r="AE57" s="59"/>
+      <c r="AF57" s="59"/>
+      <c r="AG57" s="59"/>
+      <c r="AH57" s="59"/>
+      <c r="AI57" s="59"/>
+      <c r="AJ57" s="59"/>
+      <c r="AK57" s="59"/>
+      <c r="AL57" s="96"/>
     </row>
     <row r="58" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A58" s="33">
@@ -6912,62 +6503,54 @@
       <c r="F58" s="40"/>
       <c r="G58" s="40"/>
       <c r="H58" s="59"/>
-      <c r="I58" s="36"/>
-      <c r="J58" s="59">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="K58" s="75">
-        <v>0</v>
-      </c>
-      <c r="L58" s="76">
-        <f t="shared" si="51"/>
+      <c r="I58" s="59"/>
+      <c r="J58" s="75">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="59"/>
+      <c r="L58" s="75">
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M58" s="59"/>
-      <c r="N58" s="36"/>
-      <c r="O58" s="36">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="P58" s="36">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="Q58" s="36">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="R58" s="36">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="S58" s="88">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
+      <c r="N58" s="59"/>
+      <c r="O58" s="75">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="P58" s="75">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="Q58" s="75">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="R58" s="75">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="59"/>
       <c r="T58" s="59"/>
       <c r="U58" s="59"/>
       <c r="V58" s="59"/>
       <c r="W58" s="59"/>
       <c r="X58" s="59"/>
       <c r="Y58" s="59"/>
-      <c r="Z58" s="36">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="AA58" s="88"/>
-      <c r="AB58" s="88"/>
-      <c r="AC58" s="88"/>
-      <c r="AD58" s="88"/>
-      <c r="AE58" s="88"/>
-      <c r="AF58" s="88"/>
-      <c r="AG58" s="88"/>
-      <c r="AH58" s="88"/>
-      <c r="AI58" s="88"/>
-      <c r="AJ58" s="88"/>
-      <c r="AK58" s="85"/>
-      <c r="AL58" s="100"/>
+      <c r="Z58" s="59"/>
+      <c r="AA58" s="59"/>
+      <c r="AB58" s="59"/>
+      <c r="AC58" s="59"/>
+      <c r="AD58" s="59"/>
+      <c r="AE58" s="59"/>
+      <c r="AF58" s="59"/>
+      <c r="AG58" s="59"/>
+      <c r="AH58" s="59"/>
+      <c r="AI58" s="59"/>
+      <c r="AJ58" s="59"/>
+      <c r="AK58" s="59"/>
+      <c r="AL58" s="96"/>
     </row>
     <row r="59" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A59" s="33">
@@ -6980,60 +6563,54 @@
       <c r="F59" s="40"/>
       <c r="G59" s="40"/>
       <c r="H59" s="59"/>
-      <c r="I59" s="36"/>
-      <c r="J59" s="59">
-        <f t="shared" si="50"/>
-        <v>0</v>
-      </c>
-      <c r="K59" s="75"/>
-      <c r="L59" s="76">
-        <f t="shared" si="51"/>
+      <c r="I59" s="59"/>
+      <c r="J59" s="75">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="59"/>
+      <c r="L59" s="75">
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="M59" s="59"/>
-      <c r="N59" s="36"/>
-      <c r="O59" s="36">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="P59" s="36">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="Q59" s="36">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="R59" s="36">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="S59" s="88">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
+      <c r="N59" s="59"/>
+      <c r="O59" s="75">
+        <f t="shared" si="35"/>
+        <v>0</v>
+      </c>
+      <c r="P59" s="75">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="Q59" s="75">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
+      <c r="R59" s="75">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="59"/>
       <c r="T59" s="59"/>
       <c r="U59" s="59"/>
       <c r="V59" s="59"/>
       <c r="W59" s="59"/>
       <c r="X59" s="59"/>
       <c r="Y59" s="59"/>
-      <c r="Z59" s="36">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="AA59" s="88"/>
-      <c r="AB59" s="85"/>
-      <c r="AC59" s="85"/>
-      <c r="AD59" s="85"/>
-      <c r="AE59" s="85"/>
-      <c r="AF59" s="85"/>
-      <c r="AG59" s="85"/>
-      <c r="AH59" s="85"/>
-      <c r="AI59" s="85"/>
-      <c r="AJ59" s="85"/>
-      <c r="AK59" s="85"/>
-      <c r="AL59" s="101"/>
+      <c r="Z59" s="59"/>
+      <c r="AA59" s="59"/>
+      <c r="AB59" s="59"/>
+      <c r="AC59" s="59"/>
+      <c r="AD59" s="59"/>
+      <c r="AE59" s="59"/>
+      <c r="AF59" s="59"/>
+      <c r="AG59" s="59"/>
+      <c r="AH59" s="59"/>
+      <c r="AI59" s="59"/>
+      <c r="AJ59" s="59"/>
+      <c r="AK59" s="59"/>
+      <c r="AL59" s="97"/>
     </row>
     <row r="60" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A60" s="33"/>
@@ -7046,32 +6623,17 @@
       <c r="F60" s="40"/>
       <c r="G60" s="40"/>
       <c r="H60" s="59"/>
-      <c r="I60" s="36"/>
-      <c r="J60" s="59"/>
-      <c r="K60" s="75"/>
-      <c r="L60" s="76"/>
+      <c r="I60" s="59"/>
+      <c r="J60" s="77"/>
+      <c r="K60" s="59"/>
+      <c r="L60" s="77"/>
       <c r="M60" s="59"/>
-      <c r="N60" s="36"/>
-      <c r="O60" s="36">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="P60" s="36">
-        <f t="shared" si="47"/>
-        <v>0</v>
-      </c>
-      <c r="Q60" s="36">
-        <f t="shared" si="44"/>
-        <v>0</v>
-      </c>
-      <c r="R60" s="36">
-        <f t="shared" si="48"/>
-        <v>0</v>
-      </c>
-      <c r="S60" s="88">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
+      <c r="N60" s="59"/>
+      <c r="O60" s="77"/>
+      <c r="P60" s="77"/>
+      <c r="Q60" s="77"/>
+      <c r="R60" s="77"/>
+      <c r="S60" s="59"/>
       <c r="T60" s="59"/>
       <c r="U60" s="59"/>
       <c r="V60" s="59"/>
@@ -7079,18 +6641,18 @@
       <c r="X60" s="59"/>
       <c r="Y60" s="59"/>
       <c r="Z60" s="59"/>
-      <c r="AA60" s="88"/>
-      <c r="AB60" s="85"/>
-      <c r="AC60" s="85"/>
-      <c r="AD60" s="85"/>
-      <c r="AE60" s="85"/>
-      <c r="AF60" s="85"/>
-      <c r="AG60" s="85"/>
-      <c r="AH60" s="85"/>
-      <c r="AI60" s="85"/>
-      <c r="AJ60" s="85"/>
-      <c r="AK60" s="85"/>
-      <c r="AL60" s="101"/>
+      <c r="AA60" s="59"/>
+      <c r="AB60" s="59"/>
+      <c r="AC60" s="59"/>
+      <c r="AD60" s="59"/>
+      <c r="AE60" s="59"/>
+      <c r="AF60" s="59"/>
+      <c r="AG60" s="59"/>
+      <c r="AH60" s="59"/>
+      <c r="AI60" s="59"/>
+      <c r="AJ60" s="59"/>
+      <c r="AK60" s="59"/>
+      <c r="AL60" s="97"/>
     </row>
     <row r="61" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A61" s="55"/>
@@ -7103,102 +6665,126 @@
       <c r="F61" s="57"/>
       <c r="G61" s="57"/>
       <c r="H61" s="44">
-        <f t="shared" ref="H61:S61" si="53">SUM(H47:H59)</f>
+        <f t="shared" ref="H61:AK61" si="39">SUM(H48:H60)</f>
         <v>0</v>
       </c>
       <c r="I61" s="44">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="J61" s="44">
-        <f t="shared" si="53"/>
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="J61" s="76">
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="K61" s="44">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="L61" s="78">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="M61" s="78">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="N61" s="78">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="O61" s="78">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="P61" s="78">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="Q61" s="78">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="R61" s="78">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="S61" s="78">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
-      <c r="T61" s="78"/>
-      <c r="U61" s="78"/>
-      <c r="V61" s="78"/>
-      <c r="W61" s="78"/>
-      <c r="X61" s="78"/>
-      <c r="Y61" s="78"/>
-      <c r="Z61" s="78">
-        <f t="shared" ref="Z61:AF61" si="54">SUM(Z47:Z59)</f>
-        <v>0</v>
-      </c>
-      <c r="AA61" s="78">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="AB61" s="78">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="AC61" s="78">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="AD61" s="78">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="AE61" s="78">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="AF61" s="78">
-        <f t="shared" si="54"/>
-        <v>0</v>
-      </c>
-      <c r="AG61" s="78"/>
-      <c r="AH61" s="78"/>
-      <c r="AI61" s="78">
-        <f t="shared" ref="AI61:AK61" si="55">SUM(AI47:AI59)</f>
-        <v>0</v>
-      </c>
-      <c r="AJ61" s="78">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
-      <c r="AK61" s="78">
-        <f t="shared" si="55"/>
-        <v>0</v>
-      </c>
-      <c r="AL61" s="101"/>
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="L61" s="76">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="M61" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="N61" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="O61" s="76">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="P61" s="76">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="Q61" s="76">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="R61" s="76">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="S61" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="T61" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="U61" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="V61" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="W61" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="X61" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="Y61" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="Z61" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="AA61" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="AB61" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="AC61" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="AD61" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="AE61" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="AF61" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="AG61" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="AH61" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="AI61" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="AJ61" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="AK61" s="44">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="AL61" s="97"/>
     </row>
     <row r="62" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A62" s="33"/>
@@ -7212,55 +6798,35 @@
       <c r="G62" s="40"/>
       <c r="H62" s="36"/>
       <c r="I62" s="36"/>
-      <c r="J62" s="58">
-        <v>0</v>
-      </c>
-      <c r="K62" s="79"/>
-      <c r="L62" s="76">
-        <f>J62-N62-P62</f>
-        <v>0</v>
-      </c>
+      <c r="J62" s="75"/>
+      <c r="K62" s="36"/>
+      <c r="L62" s="75"/>
       <c r="M62" s="36"/>
       <c r="N62" s="36"/>
-      <c r="O62" s="36">
-        <f t="shared" ref="O62:O66" si="56">L62-M62</f>
-        <v>0</v>
-      </c>
-      <c r="P62" s="36">
-        <f t="shared" ref="P62:P66" si="57">K62-N62</f>
-        <v>0</v>
-      </c>
-      <c r="Q62" s="36">
-        <f t="shared" ref="Q62:Q66" si="58">M62+O62</f>
-        <v>0</v>
-      </c>
-      <c r="R62" s="36">
-        <f t="shared" ref="R62:R66" si="59">M62+N62+O62+P62</f>
-        <v>0</v>
-      </c>
-      <c r="S62" s="88">
-        <f t="shared" ref="S62:S66" si="60">SUM(T62:V62)</f>
-        <v>0</v>
-      </c>
-      <c r="T62" s="59"/>
-      <c r="U62" s="59"/>
-      <c r="V62" s="59"/>
-      <c r="W62" s="59"/>
-      <c r="X62" s="59"/>
-      <c r="Y62" s="59"/>
-      <c r="Z62" s="77"/>
-      <c r="AA62" s="88"/>
-      <c r="AB62" s="85"/>
-      <c r="AC62" s="85"/>
-      <c r="AD62" s="85"/>
-      <c r="AE62" s="85"/>
-      <c r="AF62" s="85"/>
-      <c r="AG62" s="85"/>
-      <c r="AH62" s="85"/>
-      <c r="AI62" s="85"/>
-      <c r="AJ62" s="85"/>
-      <c r="AK62" s="85"/>
-      <c r="AL62" s="101"/>
+      <c r="O62" s="75"/>
+      <c r="P62" s="75"/>
+      <c r="Q62" s="75"/>
+      <c r="R62" s="75"/>
+      <c r="S62" s="36"/>
+      <c r="T62" s="36"/>
+      <c r="U62" s="36"/>
+      <c r="V62" s="36"/>
+      <c r="W62" s="36"/>
+      <c r="X62" s="36"/>
+      <c r="Y62" s="36"/>
+      <c r="Z62" s="36"/>
+      <c r="AA62" s="36"/>
+      <c r="AB62" s="36"/>
+      <c r="AC62" s="36"/>
+      <c r="AD62" s="36"/>
+      <c r="AE62" s="36"/>
+      <c r="AF62" s="36"/>
+      <c r="AG62" s="36"/>
+      <c r="AH62" s="36"/>
+      <c r="AI62" s="36"/>
+      <c r="AJ62" s="36"/>
+      <c r="AK62" s="36"/>
+      <c r="AL62" s="97"/>
     </row>
     <row r="63" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A63" s="33">
@@ -7274,56 +6840,53 @@
       <c r="G63" s="40"/>
       <c r="H63" s="36"/>
       <c r="I63" s="36"/>
-      <c r="J63" s="58">
-        <f t="shared" ref="J63:J66" si="61">H63+I63</f>
+      <c r="J63" s="75">
+        <f t="shared" ref="J63:J66" si="40">H63+I63</f>
         <v>0</v>
       </c>
       <c r="K63" s="36"/>
-      <c r="L63" s="76">
-        <f t="shared" ref="L63:L67" si="62">J63-K63</f>
+      <c r="L63" s="75">
+        <f t="shared" ref="L63:L66" si="41">J63-K63</f>
         <v>0</v>
       </c>
       <c r="M63" s="36"/>
       <c r="N63" s="36"/>
-      <c r="O63" s="36">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="P63" s="36">
-        <f t="shared" si="57"/>
-        <v>0</v>
-      </c>
-      <c r="Q63" s="36">
-        <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-      <c r="R63" s="36">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="S63" s="88">
-        <f t="shared" si="60"/>
-        <v>0</v>
-      </c>
-      <c r="T63" s="88"/>
-      <c r="U63" s="88"/>
-      <c r="V63" s="88"/>
-      <c r="W63" s="88"/>
-      <c r="X63" s="88"/>
-      <c r="Y63" s="88"/>
-      <c r="Z63" s="88"/>
-      <c r="AA63" s="88"/>
-      <c r="AB63" s="85"/>
-      <c r="AC63" s="85"/>
-      <c r="AD63" s="85"/>
-      <c r="AE63" s="85"/>
-      <c r="AF63" s="85"/>
-      <c r="AG63" s="85"/>
-      <c r="AH63" s="85"/>
-      <c r="AI63" s="85"/>
-      <c r="AJ63" s="85"/>
-      <c r="AK63" s="85"/>
-      <c r="AL63" s="101"/>
+      <c r="O63" s="75">
+        <f t="shared" ref="O63:O66" si="42">L63-M63</f>
+        <v>0</v>
+      </c>
+      <c r="P63" s="75">
+        <f t="shared" ref="P63:P66" si="43">K63-N63</f>
+        <v>0</v>
+      </c>
+      <c r="Q63" s="75">
+        <f t="shared" ref="Q63:Q66" si="44">M63+O63</f>
+        <v>0</v>
+      </c>
+      <c r="R63" s="75">
+        <f t="shared" ref="R63:R66" si="45">M63+N63+O63+P63</f>
+        <v>0</v>
+      </c>
+      <c r="S63" s="36"/>
+      <c r="T63" s="36"/>
+      <c r="U63" s="36"/>
+      <c r="V63" s="36"/>
+      <c r="W63" s="36"/>
+      <c r="X63" s="36"/>
+      <c r="Y63" s="36"/>
+      <c r="Z63" s="36"/>
+      <c r="AA63" s="36"/>
+      <c r="AB63" s="36"/>
+      <c r="AC63" s="36"/>
+      <c r="AD63" s="36"/>
+      <c r="AE63" s="36"/>
+      <c r="AF63" s="36"/>
+      <c r="AG63" s="36"/>
+      <c r="AH63" s="36"/>
+      <c r="AI63" s="36"/>
+      <c r="AJ63" s="36"/>
+      <c r="AK63" s="36"/>
+      <c r="AL63" s="97"/>
     </row>
     <row r="64" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A64" s="33">
@@ -7337,56 +6900,53 @@
       <c r="G64" s="40"/>
       <c r="H64" s="36"/>
       <c r="I64" s="36"/>
-      <c r="J64" s="58">
-        <f t="shared" si="61"/>
+      <c r="J64" s="75">
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="K64" s="36"/>
-      <c r="L64" s="76">
-        <f t="shared" si="62"/>
+      <c r="L64" s="75">
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="M64" s="36"/>
       <c r="N64" s="36"/>
-      <c r="O64" s="36">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="P64" s="36">
-        <f t="shared" si="57"/>
-        <v>0</v>
-      </c>
-      <c r="Q64" s="36">
-        <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-      <c r="R64" s="36">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="S64" s="88">
-        <f t="shared" si="60"/>
-        <v>0</v>
-      </c>
-      <c r="T64" s="88"/>
-      <c r="U64" s="88"/>
-      <c r="V64" s="88"/>
-      <c r="W64" s="88"/>
-      <c r="X64" s="88"/>
-      <c r="Y64" s="88"/>
-      <c r="Z64" s="88"/>
-      <c r="AA64" s="88"/>
-      <c r="AB64" s="85"/>
-      <c r="AC64" s="85"/>
-      <c r="AD64" s="85"/>
-      <c r="AE64" s="85"/>
-      <c r="AF64" s="85"/>
-      <c r="AG64" s="85"/>
-      <c r="AH64" s="85"/>
-      <c r="AI64" s="85"/>
-      <c r="AJ64" s="85"/>
-      <c r="AK64" s="85"/>
-      <c r="AL64" s="101"/>
+      <c r="O64" s="75">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="P64" s="75">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="Q64" s="75">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="R64" s="75">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="S64" s="36"/>
+      <c r="T64" s="36"/>
+      <c r="U64" s="36"/>
+      <c r="V64" s="36"/>
+      <c r="W64" s="36"/>
+      <c r="X64" s="36"/>
+      <c r="Y64" s="36"/>
+      <c r="Z64" s="36"/>
+      <c r="AA64" s="36"/>
+      <c r="AB64" s="36"/>
+      <c r="AC64" s="36"/>
+      <c r="AD64" s="36"/>
+      <c r="AE64" s="36"/>
+      <c r="AF64" s="36"/>
+      <c r="AG64" s="36"/>
+      <c r="AH64" s="36"/>
+      <c r="AI64" s="36"/>
+      <c r="AJ64" s="36"/>
+      <c r="AK64" s="36"/>
+      <c r="AL64" s="97"/>
     </row>
     <row r="65" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A65" s="33">
@@ -7400,56 +6960,53 @@
       <c r="G65" s="40"/>
       <c r="H65" s="36"/>
       <c r="I65" s="36"/>
-      <c r="J65" s="58">
-        <f t="shared" si="61"/>
+      <c r="J65" s="75">
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="K65" s="36"/>
-      <c r="L65" s="76">
-        <f t="shared" si="62"/>
+      <c r="L65" s="75">
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="M65" s="36"/>
       <c r="N65" s="36"/>
-      <c r="O65" s="36">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="P65" s="36">
-        <f t="shared" si="57"/>
-        <v>0</v>
-      </c>
-      <c r="Q65" s="36">
-        <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-      <c r="R65" s="36">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="S65" s="88">
-        <f t="shared" si="60"/>
-        <v>0</v>
-      </c>
-      <c r="T65" s="88"/>
-      <c r="U65" s="88"/>
-      <c r="V65" s="88"/>
-      <c r="W65" s="88"/>
-      <c r="X65" s="88"/>
-      <c r="Y65" s="88"/>
-      <c r="Z65" s="88"/>
-      <c r="AA65" s="88"/>
-      <c r="AB65" s="85"/>
-      <c r="AC65" s="85"/>
-      <c r="AD65" s="85"/>
-      <c r="AE65" s="85"/>
-      <c r="AF65" s="85"/>
-      <c r="AG65" s="85"/>
-      <c r="AH65" s="85"/>
-      <c r="AI65" s="85"/>
-      <c r="AJ65" s="85"/>
-      <c r="AK65" s="85"/>
-      <c r="AL65" s="101"/>
+      <c r="O65" s="75">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="P65" s="75">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="Q65" s="75">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="R65" s="75">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="S65" s="36"/>
+      <c r="T65" s="36"/>
+      <c r="U65" s="36"/>
+      <c r="V65" s="36"/>
+      <c r="W65" s="36"/>
+      <c r="X65" s="36"/>
+      <c r="Y65" s="36"/>
+      <c r="Z65" s="36"/>
+      <c r="AA65" s="36"/>
+      <c r="AB65" s="36"/>
+      <c r="AC65" s="36"/>
+      <c r="AD65" s="36"/>
+      <c r="AE65" s="36"/>
+      <c r="AF65" s="36"/>
+      <c r="AG65" s="36"/>
+      <c r="AH65" s="36"/>
+      <c r="AI65" s="36"/>
+      <c r="AJ65" s="36"/>
+      <c r="AK65" s="36"/>
+      <c r="AL65" s="97"/>
     </row>
     <row r="66" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A66" s="33">
@@ -7463,56 +7020,53 @@
       <c r="G66" s="40"/>
       <c r="H66" s="36"/>
       <c r="I66" s="36"/>
-      <c r="J66" s="58">
-        <f t="shared" si="61"/>
+      <c r="J66" s="75">
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="K66" s="36"/>
-      <c r="L66" s="76">
-        <f t="shared" si="62"/>
+      <c r="L66" s="75">
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="M66" s="36"/>
       <c r="N66" s="36"/>
-      <c r="O66" s="36">
-        <f t="shared" si="56"/>
-        <v>0</v>
-      </c>
-      <c r="P66" s="36">
-        <f t="shared" si="57"/>
-        <v>0</v>
-      </c>
-      <c r="Q66" s="36">
-        <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-      <c r="R66" s="36">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="S66" s="88">
-        <f t="shared" si="60"/>
-        <v>0</v>
-      </c>
-      <c r="T66" s="88"/>
-      <c r="U66" s="88"/>
-      <c r="V66" s="88"/>
-      <c r="W66" s="88"/>
-      <c r="X66" s="88"/>
-      <c r="Y66" s="88"/>
-      <c r="Z66" s="88"/>
-      <c r="AA66" s="88"/>
-      <c r="AB66" s="85"/>
-      <c r="AC66" s="85"/>
-      <c r="AD66" s="85"/>
-      <c r="AE66" s="85"/>
-      <c r="AF66" s="85"/>
-      <c r="AG66" s="85"/>
-      <c r="AH66" s="85"/>
-      <c r="AI66" s="85"/>
-      <c r="AJ66" s="85"/>
-      <c r="AK66" s="85"/>
-      <c r="AL66" s="101"/>
+      <c r="O66" s="75">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="P66" s="75">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="Q66" s="75">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="R66" s="75">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="S66" s="36"/>
+      <c r="T66" s="36"/>
+      <c r="U66" s="36"/>
+      <c r="V66" s="36"/>
+      <c r="W66" s="36"/>
+      <c r="X66" s="36"/>
+      <c r="Y66" s="36"/>
+      <c r="Z66" s="36"/>
+      <c r="AA66" s="36"/>
+      <c r="AB66" s="36"/>
+      <c r="AC66" s="36"/>
+      <c r="AD66" s="36"/>
+      <c r="AE66" s="36"/>
+      <c r="AF66" s="36"/>
+      <c r="AG66" s="36"/>
+      <c r="AH66" s="36"/>
+      <c r="AI66" s="36"/>
+      <c r="AJ66" s="36"/>
+      <c r="AK66" s="36"/>
+      <c r="AL66" s="97"/>
     </row>
     <row r="67" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A67" s="55"/>
@@ -7525,94 +7079,123 @@
       <c r="F67" s="53"/>
       <c r="G67" s="53"/>
       <c r="H67" s="44">
-        <f>SUM(H62)</f>
+        <f t="shared" ref="H67:AK67" si="46">SUM(H63:H66)</f>
         <v>0</v>
       </c>
       <c r="I67" s="44">
-        <f>SUM(I62)</f>
-        <v>0</v>
-      </c>
-      <c r="J67" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="J67" s="76">
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="K67" s="44">
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="L67" s="76">
-        <f t="shared" si="62"/>
-        <v>0</v>
-      </c>
-      <c r="M67" s="78">
-        <f>SUM(M49:M61)</f>
-        <v>0</v>
-      </c>
-      <c r="N67" s="78">
-        <f>SUM(N49:N61)</f>
-        <v>0</v>
-      </c>
-      <c r="O67" s="78">
-        <f t="shared" ref="O67:S67" si="63">SUM(O49:O61)</f>
-        <v>0</v>
-      </c>
-      <c r="P67" s="78">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="Q67" s="78">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="R67" s="78">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="S67" s="78">
-        <f t="shared" si="63"/>
-        <v>0</v>
-      </c>
-      <c r="T67" s="124"/>
-      <c r="U67" s="124"/>
-      <c r="V67" s="124"/>
-      <c r="W67" s="124"/>
-      <c r="X67" s="124"/>
-      <c r="Y67" s="124"/>
-      <c r="Z67" s="124"/>
-      <c r="AA67" s="124">
-        <f t="shared" ref="AA67:AF67" si="64">SUM(AA62)</f>
-        <v>0</v>
-      </c>
-      <c r="AB67" s="124">
-        <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="AC67" s="124">
-        <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="AD67" s="124">
-        <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="AE67" s="124">
-        <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="AF67" s="124">
-        <f t="shared" si="64"/>
-        <v>0</v>
-      </c>
-      <c r="AG67" s="124"/>
-      <c r="AH67" s="124"/>
-      <c r="AI67" s="124">
-        <f t="shared" ref="AI67:AK67" si="65">SUM(AI62)</f>
-        <v>0</v>
-      </c>
-      <c r="AJ67" s="124">
-        <f t="shared" si="65"/>
-        <v>0</v>
-      </c>
-      <c r="AK67" s="124">
-        <f t="shared" si="65"/>
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="M67" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="N67" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="O67" s="76">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="P67" s="76">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="Q67" s="76">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="R67" s="76">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="S67" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="T67" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="U67" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="V67" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="W67" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="X67" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="Y67" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="Z67" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="AA67" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="AB67" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="AC67" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="AD67" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="AE67" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="AF67" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="AG67" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="AH67" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="AI67" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="AJ67" s="44">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="AK67" s="44">
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="AL67" s="151"/>
@@ -7628,99 +7211,123 @@
       <c r="F68" s="57"/>
       <c r="G68" s="57"/>
       <c r="H68" s="44">
-        <f t="shared" ref="H68:S68" si="66">H17+H23+H34+H38+H46+H61+H67</f>
+        <f t="shared" ref="H68:AK68" si="47">H17+H23+H34+H38+H46+H61+H67</f>
         <v>0</v>
       </c>
       <c r="I68" s="44">
-        <f t="shared" si="66"/>
-        <v>0</v>
-      </c>
-      <c r="J68" s="44">
-        <f t="shared" si="66"/>
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="J68" s="76">
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="K68" s="44">
-        <f t="shared" si="66"/>
-        <v>0</v>
-      </c>
-      <c r="L68" s="78">
-        <f t="shared" si="66"/>
-        <v>0</v>
-      </c>
-      <c r="M68" s="124">
-        <f>M17+M23+M34+M38+M46+M61+M67</f>
-        <v>0</v>
-      </c>
-      <c r="N68" s="124">
-        <f t="shared" si="66"/>
-        <v>0</v>
-      </c>
-      <c r="O68" s="124">
-        <f t="shared" si="66"/>
-        <v>0</v>
-      </c>
-      <c r="P68" s="124">
-        <f t="shared" si="66"/>
-        <v>0</v>
-      </c>
-      <c r="Q68" s="124">
-        <f t="shared" si="66"/>
-        <v>0</v>
-      </c>
-      <c r="R68" s="124">
-        <f t="shared" si="66"/>
-        <v>0</v>
-      </c>
-      <c r="S68" s="124">
-        <f t="shared" si="66"/>
-        <v>0</v>
-      </c>
-      <c r="T68" s="124"/>
-      <c r="U68" s="124"/>
-      <c r="V68" s="124"/>
-      <c r="W68" s="124"/>
-      <c r="X68" s="124"/>
-      <c r="Y68" s="124"/>
-      <c r="Z68" s="124">
-        <f t="shared" ref="Z68:AF68" si="67">Z17+Z23+Z34+Z38+Z46+Z61+Z67</f>
-        <v>0</v>
-      </c>
-      <c r="AA68" s="124">
-        <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AB68" s="124">
-        <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AC68" s="124">
-        <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AD68" s="124">
-        <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AE68" s="124">
-        <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AF68" s="124">
-        <f t="shared" si="67"/>
-        <v>0</v>
-      </c>
-      <c r="AG68" s="124"/>
-      <c r="AH68" s="124"/>
-      <c r="AI68" s="124">
-        <f t="shared" ref="AI68:AK68" si="68">AI17+AI23+AI34+AI38+AI46+AI61+AI67</f>
-        <v>0</v>
-      </c>
-      <c r="AJ68" s="124">
-        <f t="shared" si="68"/>
-        <v>0</v>
-      </c>
-      <c r="AK68" s="124">
-        <f t="shared" si="68"/>
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="L68" s="76">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="M68" s="44">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="N68" s="44">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="O68" s="76">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="P68" s="76">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="Q68" s="76">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="R68" s="76">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="S68" s="44">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="T68" s="44">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="U68" s="44">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="V68" s="44">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="W68" s="44">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="X68" s="44">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="Y68" s="44">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="Z68" s="44">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="AA68" s="44">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="AB68" s="44">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="AC68" s="44">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="AD68" s="44">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="AE68" s="44">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="AF68" s="44">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="AG68" s="44">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="AH68" s="44">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="AI68" s="44">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="AJ68" s="44">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
+      <c r="AK68" s="44">
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AL68" s="151"/>
@@ -7732,52 +7339,52 @@
       <c r="D69" s="45" t="s">
         <v>108</v>
       </c>
-      <c r="E69" s="104" t="s">
+      <c r="E69" s="100" t="s">
         <v>109</v>
       </c>
-      <c r="F69" s="104"/>
-      <c r="G69" s="104"/>
+      <c r="F69" s="100"/>
+      <c r="G69" s="100"/>
       <c r="H69" s="58"/>
       <c r="I69" s="58"/>
-      <c r="J69" s="58">
-        <f t="shared" ref="J69:J75" si="69">H69+I69</f>
+      <c r="J69" s="76">
+        <f t="shared" ref="J69:J76" si="48">H69+I69</f>
         <v>0</v>
       </c>
       <c r="K69" s="58"/>
-      <c r="L69" s="76">
-        <f t="shared" ref="L69:L75" si="70">J69-K69</f>
+      <c r="L69" s="120">
+        <f t="shared" ref="L69:L75" si="49">J69-K69</f>
         <v>0</v>
       </c>
       <c r="M69" s="36"/>
       <c r="N69" s="36"/>
-      <c r="O69" s="36">
-        <f t="shared" ref="O69:O72" si="71">L69-M69</f>
-        <v>0</v>
-      </c>
-      <c r="P69" s="36">
-        <f t="shared" ref="P69:P72" si="72">K69-N69</f>
-        <v>0</v>
-      </c>
-      <c r="Q69" s="36">
-        <f t="shared" ref="Q69:Q72" si="73">M69+O69</f>
-        <v>0</v>
-      </c>
-      <c r="R69" s="36">
-        <f t="shared" ref="R69:R72" si="74">M69+N69+O69+P69</f>
-        <v>0</v>
-      </c>
-      <c r="S69" s="88">
-        <f t="shared" ref="S69:S72" si="75">SUM(T69:V69)</f>
-        <v>0</v>
-      </c>
-      <c r="T69" s="88"/>
-      <c r="U69" s="88"/>
-      <c r="V69" s="88"/>
-      <c r="W69" s="88"/>
-      <c r="X69" s="88"/>
-      <c r="Y69" s="88"/>
-      <c r="Z69" s="88"/>
-      <c r="AA69" s="88">
+      <c r="O69" s="75">
+        <f>L69-M69</f>
+        <v>0</v>
+      </c>
+      <c r="P69" s="75">
+        <f t="shared" ref="P69:P72" si="50">K69-N69</f>
+        <v>0</v>
+      </c>
+      <c r="Q69" s="75">
+        <f t="shared" ref="Q69:Q72" si="51">M69+O69</f>
+        <v>0</v>
+      </c>
+      <c r="R69" s="75">
+        <f t="shared" ref="R69:R72" si="52">M69+N69+O69+P69</f>
+        <v>0</v>
+      </c>
+      <c r="S69" s="141">
+        <f t="shared" ref="S69:S72" si="53">SUM(T69:V69)</f>
+        <v>0</v>
+      </c>
+      <c r="T69" s="141"/>
+      <c r="U69" s="141"/>
+      <c r="V69" s="141"/>
+      <c r="W69" s="141"/>
+      <c r="X69" s="141"/>
+      <c r="Y69" s="141"/>
+      <c r="Z69" s="141"/>
+      <c r="AA69" s="141">
         <f>Q69-S69</f>
         <v>0</v>
       </c>
@@ -7790,7 +7397,7 @@
       <c r="AH69" s="144"/>
       <c r="AI69" s="144"/>
       <c r="AJ69" s="144"/>
-      <c r="AK69" s="85"/>
+      <c r="AK69" s="83"/>
       <c r="AL69" s="151"/>
     </row>
     <row r="70" s="1" customFormat="1" ht="14" spans="1:38">
@@ -7805,56 +7412,56 @@
       <c r="G70" s="40"/>
       <c r="H70" s="58"/>
       <c r="I70" s="58"/>
-      <c r="J70" s="58">
-        <f t="shared" si="69"/>
+      <c r="J70" s="76">
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="K70" s="58"/>
-      <c r="L70" s="76">
-        <f t="shared" si="70"/>
+      <c r="L70" s="120">
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="M70" s="36"/>
       <c r="N70" s="36"/>
-      <c r="O70" s="36">
-        <f t="shared" si="71"/>
-        <v>0</v>
-      </c>
-      <c r="P70" s="36">
-        <f t="shared" si="72"/>
-        <v>0</v>
-      </c>
-      <c r="Q70" s="36">
-        <f t="shared" si="73"/>
-        <v>0</v>
-      </c>
-      <c r="R70" s="36">
-        <f t="shared" si="74"/>
-        <v>0</v>
-      </c>
-      <c r="S70" s="88">
-        <f t="shared" si="75"/>
-        <v>0</v>
-      </c>
-      <c r="T70" s="88"/>
-      <c r="U70" s="88"/>
-      <c r="V70" s="88"/>
-      <c r="W70" s="88"/>
-      <c r="X70" s="88"/>
-      <c r="Y70" s="88"/>
-      <c r="Z70" s="88"/>
-      <c r="AA70" s="88"/>
-      <c r="AB70" s="85"/>
-      <c r="AC70" s="85"/>
-      <c r="AD70" s="85"/>
-      <c r="AE70" s="85"/>
-      <c r="AF70" s="85"/>
-      <c r="AG70" s="85"/>
-      <c r="AH70" s="85"/>
-      <c r="AI70" s="85"/>
-      <c r="AJ70" s="85"/>
-      <c r="AK70" s="85"/>
-      <c r="AL70" s="101"/>
+      <c r="O70" s="75">
+        <f t="shared" ref="O69:O72" si="54">L70-M70</f>
+        <v>0</v>
+      </c>
+      <c r="P70" s="75">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Q70" s="75">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="R70" s="75">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="S70" s="141">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="T70" s="141"/>
+      <c r="U70" s="141"/>
+      <c r="V70" s="141"/>
+      <c r="W70" s="141"/>
+      <c r="X70" s="141"/>
+      <c r="Y70" s="141"/>
+      <c r="Z70" s="141"/>
+      <c r="AA70" s="141"/>
+      <c r="AB70" s="83"/>
+      <c r="AC70" s="83"/>
+      <c r="AD70" s="83"/>
+      <c r="AE70" s="83"/>
+      <c r="AF70" s="83"/>
+      <c r="AG70" s="83"/>
+      <c r="AH70" s="83"/>
+      <c r="AI70" s="83"/>
+      <c r="AJ70" s="83"/>
+      <c r="AK70" s="83"/>
+      <c r="AL70" s="97"/>
     </row>
     <row r="71" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A71" s="33"/>
@@ -7868,56 +7475,56 @@
       <c r="G71" s="40"/>
       <c r="H71" s="36"/>
       <c r="I71" s="36"/>
-      <c r="J71" s="58">
-        <f t="shared" si="69"/>
+      <c r="J71" s="76">
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="K71" s="36"/>
-      <c r="L71" s="76">
-        <f t="shared" si="70"/>
+      <c r="L71" s="120">
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="M71" s="36"/>
       <c r="N71" s="36"/>
-      <c r="O71" s="36">
-        <f t="shared" si="71"/>
-        <v>0</v>
-      </c>
-      <c r="P71" s="36">
-        <f t="shared" si="72"/>
-        <v>0</v>
-      </c>
-      <c r="Q71" s="36">
-        <f t="shared" si="73"/>
-        <v>0</v>
-      </c>
-      <c r="R71" s="36">
-        <f t="shared" si="74"/>
-        <v>0</v>
-      </c>
-      <c r="S71" s="88">
-        <f t="shared" si="75"/>
-        <v>0</v>
-      </c>
-      <c r="T71" s="88"/>
-      <c r="U71" s="88"/>
-      <c r="V71" s="88"/>
-      <c r="W71" s="88"/>
-      <c r="X71" s="88"/>
-      <c r="Y71" s="88"/>
-      <c r="Z71" s="88"/>
-      <c r="AA71" s="88"/>
-      <c r="AB71" s="85"/>
-      <c r="AC71" s="85"/>
-      <c r="AD71" s="85"/>
-      <c r="AE71" s="85"/>
-      <c r="AF71" s="85"/>
-      <c r="AG71" s="85"/>
-      <c r="AH71" s="85"/>
-      <c r="AI71" s="85"/>
-      <c r="AJ71" s="85"/>
-      <c r="AK71" s="85"/>
-      <c r="AL71" s="101"/>
+      <c r="O71" s="75">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="P71" s="75">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Q71" s="75">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="R71" s="75">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="S71" s="141">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="T71" s="141"/>
+      <c r="U71" s="141"/>
+      <c r="V71" s="141"/>
+      <c r="W71" s="141"/>
+      <c r="X71" s="141"/>
+      <c r="Y71" s="141"/>
+      <c r="Z71" s="141"/>
+      <c r="AA71" s="141"/>
+      <c r="AB71" s="83"/>
+      <c r="AC71" s="83"/>
+      <c r="AD71" s="83"/>
+      <c r="AE71" s="83"/>
+      <c r="AF71" s="83"/>
+      <c r="AG71" s="83"/>
+      <c r="AH71" s="83"/>
+      <c r="AI71" s="83"/>
+      <c r="AJ71" s="83"/>
+      <c r="AK71" s="83"/>
+      <c r="AL71" s="97"/>
     </row>
     <row r="72" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A72" s="33"/>
@@ -7931,56 +7538,56 @@
       <c r="G72" s="40"/>
       <c r="H72" s="36"/>
       <c r="I72" s="36"/>
-      <c r="J72" s="58">
-        <f t="shared" si="69"/>
+      <c r="J72" s="76">
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="K72" s="36"/>
-      <c r="L72" s="76">
-        <f t="shared" si="70"/>
+      <c r="L72" s="120">
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="M72" s="36"/>
       <c r="N72" s="36"/>
-      <c r="O72" s="36">
-        <f t="shared" si="71"/>
-        <v>0</v>
-      </c>
-      <c r="P72" s="36">
-        <f t="shared" si="72"/>
-        <v>0</v>
-      </c>
-      <c r="Q72" s="36">
-        <f t="shared" si="73"/>
-        <v>0</v>
-      </c>
-      <c r="R72" s="36">
-        <f t="shared" si="74"/>
-        <v>0</v>
-      </c>
-      <c r="S72" s="88">
-        <f t="shared" si="75"/>
-        <v>0</v>
-      </c>
-      <c r="T72" s="88"/>
-      <c r="U72" s="88"/>
-      <c r="V72" s="88"/>
-      <c r="W72" s="88"/>
-      <c r="X72" s="88"/>
-      <c r="Y72" s="88"/>
-      <c r="Z72" s="88"/>
-      <c r="AA72" s="88"/>
-      <c r="AB72" s="85"/>
-      <c r="AC72" s="85"/>
-      <c r="AD72" s="85"/>
-      <c r="AE72" s="85"/>
-      <c r="AF72" s="85"/>
-      <c r="AG72" s="85"/>
-      <c r="AH72" s="85"/>
-      <c r="AI72" s="85"/>
-      <c r="AJ72" s="85"/>
-      <c r="AK72" s="85"/>
-      <c r="AL72" s="101"/>
+      <c r="O72" s="75">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="P72" s="75">
+        <f t="shared" si="50"/>
+        <v>0</v>
+      </c>
+      <c r="Q72" s="75">
+        <f t="shared" si="51"/>
+        <v>0</v>
+      </c>
+      <c r="R72" s="75">
+        <f t="shared" si="52"/>
+        <v>0</v>
+      </c>
+      <c r="S72" s="141">
+        <f t="shared" si="53"/>
+        <v>0</v>
+      </c>
+      <c r="T72" s="141"/>
+      <c r="U72" s="141"/>
+      <c r="V72" s="141"/>
+      <c r="W72" s="141"/>
+      <c r="X72" s="141"/>
+      <c r="Y72" s="141"/>
+      <c r="Z72" s="141"/>
+      <c r="AA72" s="141"/>
+      <c r="AB72" s="83"/>
+      <c r="AC72" s="83"/>
+      <c r="AD72" s="83"/>
+      <c r="AE72" s="83"/>
+      <c r="AF72" s="83"/>
+      <c r="AG72" s="83"/>
+      <c r="AH72" s="83"/>
+      <c r="AI72" s="83"/>
+      <c r="AJ72" s="83"/>
+      <c r="AK72" s="83"/>
+      <c r="AL72" s="97"/>
     </row>
     <row r="73" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A73" s="55"/>
@@ -7994,113 +7601,113 @@
       <c r="G73" s="57"/>
       <c r="H73" s="44"/>
       <c r="I73" s="44"/>
-      <c r="J73" s="44">
-        <f t="shared" si="69"/>
+      <c r="J73" s="76">
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="K73" s="44"/>
-      <c r="L73" s="78">
-        <f t="shared" si="70"/>
-        <v>0</v>
-      </c>
-      <c r="M73" s="124">
-        <f t="shared" ref="M73:AK73" si="76">SUM(M74:M76)</f>
-        <v>0</v>
-      </c>
-      <c r="N73" s="124">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
-      <c r="O73" s="124">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
-      <c r="P73" s="124">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
-      <c r="Q73" s="124">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
-      <c r="R73" s="124">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
-      <c r="S73" s="124">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
-      <c r="T73" s="124">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
-      <c r="U73" s="124">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
-      <c r="V73" s="124">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
-      <c r="W73" s="124">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
-      <c r="X73" s="124">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
-      <c r="Y73" s="124">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
-      <c r="Z73" s="124">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
-      <c r="AA73" s="124">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
-      <c r="AB73" s="124">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
-      <c r="AC73" s="124">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
-      <c r="AD73" s="124">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
-      <c r="AE73" s="124">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
-      <c r="AF73" s="124">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
-      <c r="AG73" s="124">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
-      <c r="AH73" s="124">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
-      <c r="AI73" s="124">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
-      <c r="AJ73" s="124">
-        <f t="shared" si="76"/>
-        <v>0</v>
-      </c>
-      <c r="AK73" s="124">
-        <f t="shared" si="76"/>
+      <c r="L73" s="121">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="M73" s="122">
+        <f t="shared" ref="M73:AK73" si="55">SUM(M74:M76)</f>
+        <v>0</v>
+      </c>
+      <c r="N73" s="122">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="O73" s="76">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="P73" s="76">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="Q73" s="76">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="R73" s="76">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="S73" s="122">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="T73" s="122">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="U73" s="122">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="V73" s="122">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="W73" s="122">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="X73" s="122">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="Y73" s="122">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="Z73" s="122">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="AA73" s="122">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="AB73" s="122">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="AC73" s="122">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="AD73" s="122">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="AE73" s="122">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="AF73" s="122">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="AG73" s="122">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="AH73" s="122">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="AI73" s="122">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="AJ73" s="122">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="AK73" s="122">
+        <f t="shared" si="55"/>
         <v>0</v>
       </c>
       <c r="AL73" s="151"/>
@@ -8117,56 +7724,56 @@
       <c r="G74" s="40"/>
       <c r="H74" s="36"/>
       <c r="I74" s="36"/>
-      <c r="J74" s="58">
-        <f t="shared" si="69"/>
+      <c r="J74" s="76">
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="K74" s="36"/>
-      <c r="L74" s="76">
-        <f t="shared" si="70"/>
+      <c r="L74" s="120">
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="M74" s="36"/>
       <c r="N74" s="36"/>
-      <c r="O74" s="36">
-        <f t="shared" ref="O74:O76" si="77">L74-M74</f>
-        <v>0</v>
-      </c>
-      <c r="P74" s="36">
-        <f t="shared" ref="P74:P76" si="78">K74-N74</f>
-        <v>0</v>
-      </c>
-      <c r="Q74" s="36">
-        <f t="shared" ref="Q74:Q76" si="79">M74+O74</f>
-        <v>0</v>
-      </c>
-      <c r="R74" s="36">
-        <f t="shared" ref="R74:R76" si="80">M74+N74+O74+P74</f>
-        <v>0</v>
-      </c>
-      <c r="S74" s="88">
-        <f t="shared" ref="S74:S76" si="81">SUM(T74:V74)</f>
-        <v>0</v>
-      </c>
-      <c r="T74" s="88"/>
-      <c r="U74" s="88"/>
-      <c r="V74" s="88"/>
-      <c r="W74" s="88"/>
-      <c r="X74" s="88"/>
-      <c r="Y74" s="88"/>
-      <c r="Z74" s="88"/>
-      <c r="AA74" s="88"/>
-      <c r="AB74" s="85"/>
-      <c r="AC74" s="85"/>
-      <c r="AD74" s="85"/>
-      <c r="AE74" s="85"/>
-      <c r="AF74" s="85"/>
-      <c r="AG74" s="85"/>
-      <c r="AH74" s="85"/>
-      <c r="AI74" s="85"/>
-      <c r="AJ74" s="85"/>
-      <c r="AK74" s="85"/>
-      <c r="AL74" s="101"/>
+      <c r="O74" s="75">
+        <f t="shared" ref="O74:O76" si="56">L74-M74</f>
+        <v>0</v>
+      </c>
+      <c r="P74" s="75">
+        <f t="shared" ref="P74:P76" si="57">K74-N74</f>
+        <v>0</v>
+      </c>
+      <c r="Q74" s="75">
+        <f t="shared" ref="Q74:Q76" si="58">M74+O74</f>
+        <v>0</v>
+      </c>
+      <c r="R74" s="75">
+        <f t="shared" ref="R74:R76" si="59">M74+N74+O74+P74</f>
+        <v>0</v>
+      </c>
+      <c r="S74" s="141">
+        <f t="shared" ref="S74:S76" si="60">SUM(T74:V74)</f>
+        <v>0</v>
+      </c>
+      <c r="T74" s="141"/>
+      <c r="U74" s="141"/>
+      <c r="V74" s="141"/>
+      <c r="W74" s="141"/>
+      <c r="X74" s="141"/>
+      <c r="Y74" s="141"/>
+      <c r="Z74" s="141"/>
+      <c r="AA74" s="141"/>
+      <c r="AB74" s="83"/>
+      <c r="AC74" s="83"/>
+      <c r="AD74" s="83"/>
+      <c r="AE74" s="83"/>
+      <c r="AF74" s="83"/>
+      <c r="AG74" s="83"/>
+      <c r="AH74" s="83"/>
+      <c r="AI74" s="83"/>
+      <c r="AJ74" s="83"/>
+      <c r="AK74" s="83"/>
+      <c r="AL74" s="97"/>
     </row>
     <row r="75" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A75" s="33">
@@ -8180,50 +7787,53 @@
       <c r="G75" s="40"/>
       <c r="H75" s="36"/>
       <c r="I75" s="36"/>
-      <c r="J75" s="58"/>
+      <c r="J75" s="76">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
       <c r="K75" s="36"/>
-      <c r="L75" s="76"/>
+      <c r="L75" s="120"/>
       <c r="M75" s="36"/>
       <c r="N75" s="36"/>
-      <c r="O75" s="36">
-        <f t="shared" si="77"/>
-        <v>0</v>
-      </c>
-      <c r="P75" s="36">
-        <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="Q75" s="36">
-        <f t="shared" si="79"/>
-        <v>0</v>
-      </c>
-      <c r="R75" s="36">
-        <f t="shared" si="80"/>
-        <v>0</v>
-      </c>
-      <c r="S75" s="88">
-        <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="T75" s="88"/>
-      <c r="U75" s="88"/>
-      <c r="V75" s="88"/>
-      <c r="W75" s="88"/>
-      <c r="X75" s="88"/>
-      <c r="Y75" s="88"/>
-      <c r="Z75" s="88"/>
-      <c r="AA75" s="88"/>
-      <c r="AB75" s="85"/>
-      <c r="AC75" s="85"/>
-      <c r="AD75" s="85"/>
-      <c r="AE75" s="85"/>
-      <c r="AF75" s="85"/>
-      <c r="AG75" s="85"/>
-      <c r="AH75" s="85"/>
-      <c r="AI75" s="85"/>
-      <c r="AJ75" s="85"/>
-      <c r="AK75" s="85"/>
-      <c r="AL75" s="101"/>
+      <c r="O75" s="75">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="P75" s="75">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="Q75" s="75">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="R75" s="75">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="S75" s="141">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="T75" s="141"/>
+      <c r="U75" s="141"/>
+      <c r="V75" s="141"/>
+      <c r="W75" s="141"/>
+      <c r="X75" s="141"/>
+      <c r="Y75" s="141"/>
+      <c r="Z75" s="141"/>
+      <c r="AA75" s="141"/>
+      <c r="AB75" s="83"/>
+      <c r="AC75" s="83"/>
+      <c r="AD75" s="83"/>
+      <c r="AE75" s="83"/>
+      <c r="AF75" s="83"/>
+      <c r="AG75" s="83"/>
+      <c r="AH75" s="83"/>
+      <c r="AI75" s="83"/>
+      <c r="AJ75" s="83"/>
+      <c r="AK75" s="83"/>
+      <c r="AL75" s="97"/>
     </row>
     <row r="76" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A76" s="33">
@@ -8237,50 +7847,53 @@
       <c r="G76" s="40"/>
       <c r="H76" s="36"/>
       <c r="I76" s="36"/>
-      <c r="J76" s="58"/>
+      <c r="J76" s="76">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
       <c r="K76" s="36"/>
-      <c r="L76" s="76"/>
+      <c r="L76" s="120"/>
       <c r="M76" s="36"/>
       <c r="N76" s="36"/>
-      <c r="O76" s="36">
-        <f t="shared" si="77"/>
-        <v>0</v>
-      </c>
-      <c r="P76" s="36">
-        <f t="shared" si="78"/>
-        <v>0</v>
-      </c>
-      <c r="Q76" s="36">
-        <f t="shared" si="79"/>
-        <v>0</v>
-      </c>
-      <c r="R76" s="36">
-        <f t="shared" si="80"/>
-        <v>0</v>
-      </c>
-      <c r="S76" s="88">
-        <f t="shared" si="81"/>
-        <v>0</v>
-      </c>
-      <c r="T76" s="88"/>
-      <c r="U76" s="88"/>
-      <c r="V76" s="88"/>
-      <c r="W76" s="88"/>
-      <c r="X76" s="88"/>
-      <c r="Y76" s="88"/>
-      <c r="Z76" s="88"/>
-      <c r="AA76" s="88"/>
-      <c r="AB76" s="85"/>
-      <c r="AC76" s="85"/>
-      <c r="AD76" s="85"/>
-      <c r="AE76" s="85"/>
-      <c r="AF76" s="85"/>
-      <c r="AG76" s="85"/>
-      <c r="AH76" s="85"/>
-      <c r="AI76" s="85"/>
-      <c r="AJ76" s="85"/>
-      <c r="AK76" s="85"/>
-      <c r="AL76" s="101"/>
+      <c r="O76" s="75">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="P76" s="75">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
+      <c r="Q76" s="75">
+        <f t="shared" si="58"/>
+        <v>0</v>
+      </c>
+      <c r="R76" s="75">
+        <f t="shared" si="59"/>
+        <v>0</v>
+      </c>
+      <c r="S76" s="141">
+        <f t="shared" si="60"/>
+        <v>0</v>
+      </c>
+      <c r="T76" s="141"/>
+      <c r="U76" s="141"/>
+      <c r="V76" s="141"/>
+      <c r="W76" s="141"/>
+      <c r="X76" s="141"/>
+      <c r="Y76" s="141"/>
+      <c r="Z76" s="141"/>
+      <c r="AA76" s="141"/>
+      <c r="AB76" s="83"/>
+      <c r="AC76" s="83"/>
+      <c r="AD76" s="83"/>
+      <c r="AE76" s="83"/>
+      <c r="AF76" s="83"/>
+      <c r="AG76" s="83"/>
+      <c r="AH76" s="83"/>
+      <c r="AI76" s="83"/>
+      <c r="AJ76" s="83"/>
+      <c r="AK76" s="83"/>
+      <c r="AL76" s="97"/>
     </row>
     <row r="77" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A77" s="41"/>
@@ -8300,7 +7913,7 @@
         <f>I68+I69+I70+I71+#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="J77" s="125" t="e">
+      <c r="J77" s="123" t="e">
         <f>J68+J69+J70+J71+#REF!</f>
         <v>#REF!</v>
       </c>
@@ -8308,49 +7921,49 @@
         <f>K68+K69+K70+K71+#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="L77" s="126" t="e">
+      <c r="L77" s="124" t="e">
         <f>L68+L69+L70+L71+#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="M77" s="126">
+      <c r="M77" s="124">
         <f>M68+M69+M70+M71</f>
         <v>0</v>
       </c>
-      <c r="N77" s="126">
-        <f t="shared" ref="M77:S77" si="82">N68+N69+N70+N71</f>
-        <v>0</v>
-      </c>
-      <c r="O77" s="126">
-        <f t="shared" si="82"/>
-        <v>0</v>
-      </c>
-      <c r="P77" s="126">
-        <f t="shared" si="82"/>
-        <v>0</v>
-      </c>
-      <c r="Q77" s="126">
-        <f t="shared" si="82"/>
-        <v>0</v>
-      </c>
-      <c r="R77" s="126">
-        <f t="shared" si="82"/>
-        <v>0</v>
-      </c>
-      <c r="S77" s="124">
-        <f t="shared" si="82"/>
-        <v>0</v>
-      </c>
-      <c r="T77" s="124"/>
-      <c r="U77" s="124"/>
-      <c r="V77" s="124"/>
-      <c r="W77" s="124"/>
-      <c r="X77" s="124"/>
-      <c r="Y77" s="124"/>
-      <c r="Z77" s="124">
+      <c r="N77" s="124">
+        <f t="shared" ref="M77:S77" si="61">N68+N69+N70+N71</f>
+        <v>0</v>
+      </c>
+      <c r="O77" s="125">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="P77" s="124">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="Q77" s="124">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="R77" s="124">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="S77" s="122">
+        <f t="shared" si="61"/>
+        <v>0</v>
+      </c>
+      <c r="T77" s="122"/>
+      <c r="U77" s="122"/>
+      <c r="V77" s="122"/>
+      <c r="W77" s="122"/>
+      <c r="X77" s="122"/>
+      <c r="Y77" s="122"/>
+      <c r="Z77" s="122">
         <f>Z68+Z69+Z70+Z71</f>
         <v>0</v>
       </c>
-      <c r="AA77" s="124">
+      <c r="AA77" s="122">
         <f>AA68+AA69+AA70+AA71</f>
         <v>0</v>
       </c>
@@ -8380,39 +7993,39 @@
       <c r="G78" s="54"/>
       <c r="H78" s="44"/>
       <c r="I78" s="44"/>
-      <c r="J78" s="125">
+      <c r="J78" s="123">
         <f>H78+I78</f>
         <v>0</v>
       </c>
       <c r="K78" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="L78" s="126" t="s">
+      <c r="L78" s="124" t="s">
         <v>117</v>
       </c>
-      <c r="M78" s="126"/>
-      <c r="N78" s="126">
+      <c r="M78" s="124"/>
+      <c r="N78" s="124">
         <f>N6-N77</f>
         <v>0</v>
       </c>
-      <c r="O78" s="126"/>
-      <c r="P78" s="126"/>
-      <c r="Q78" s="126" t="s">
+      <c r="O78" s="125"/>
+      <c r="P78" s="124"/>
+      <c r="Q78" s="124" t="s">
         <v>117</v>
       </c>
-      <c r="R78" s="126">
+      <c r="R78" s="124">
         <f>N78+P78</f>
         <v>0</v>
       </c>
-      <c r="S78" s="124"/>
-      <c r="T78" s="124"/>
-      <c r="U78" s="124"/>
-      <c r="V78" s="124"/>
-      <c r="W78" s="124"/>
-      <c r="X78" s="124"/>
-      <c r="Y78" s="124"/>
-      <c r="Z78" s="124"/>
-      <c r="AA78" s="124"/>
+      <c r="S78" s="122"/>
+      <c r="T78" s="122"/>
+      <c r="U78" s="122"/>
+      <c r="V78" s="122"/>
+      <c r="W78" s="122"/>
+      <c r="X78" s="122"/>
+      <c r="Y78" s="122"/>
+      <c r="Z78" s="122"/>
+      <c r="AA78" s="122"/>
       <c r="AB78" s="145"/>
       <c r="AC78" s="145"/>
       <c r="AD78" s="145"/>
@@ -8439,39 +8052,39 @@
       <c r="G79" s="54"/>
       <c r="H79" s="44"/>
       <c r="I79" s="44"/>
-      <c r="J79" s="125">
+      <c r="J79" s="123">
         <f>H79+I79</f>
         <v>0</v>
       </c>
       <c r="K79" s="44"/>
-      <c r="L79" s="126">
+      <c r="L79" s="124">
         <f>J79</f>
         <v>0</v>
       </c>
-      <c r="M79" s="126"/>
-      <c r="N79" s="126"/>
-      <c r="O79" s="126">
+      <c r="M79" s="124"/>
+      <c r="N79" s="124"/>
+      <c r="O79" s="125">
         <f>L79-M79</f>
         <v>0</v>
       </c>
-      <c r="P79" s="126"/>
-      <c r="Q79" s="126">
+      <c r="P79" s="124"/>
+      <c r="Q79" s="124">
         <f>M79+O79</f>
         <v>0</v>
       </c>
-      <c r="R79" s="126">
+      <c r="R79" s="124">
         <f>Q79</f>
         <v>0</v>
       </c>
-      <c r="S79" s="124"/>
-      <c r="T79" s="124"/>
-      <c r="U79" s="124"/>
-      <c r="V79" s="124"/>
-      <c r="W79" s="124"/>
-      <c r="X79" s="124"/>
-      <c r="Y79" s="124"/>
-      <c r="Z79" s="124"/>
-      <c r="AA79" s="124"/>
+      <c r="S79" s="122"/>
+      <c r="T79" s="122"/>
+      <c r="U79" s="122"/>
+      <c r="V79" s="122"/>
+      <c r="W79" s="122"/>
+      <c r="X79" s="122"/>
+      <c r="Y79" s="122"/>
+      <c r="Z79" s="122"/>
+      <c r="AA79" s="122"/>
       <c r="AB79" s="145"/>
       <c r="AC79" s="145"/>
       <c r="AD79" s="145"/>
@@ -8496,27 +8109,27 @@
       <c r="G80" s="54"/>
       <c r="H80" s="44"/>
       <c r="I80" s="44"/>
-      <c r="J80" s="125" t="e">
+      <c r="J80" s="123" t="e">
         <f>J6-J77-J78-J79</f>
         <v>#REF!</v>
       </c>
       <c r="K80" s="44"/>
-      <c r="L80" s="126"/>
-      <c r="M80" s="126"/>
-      <c r="N80" s="126"/>
-      <c r="O80" s="126"/>
-      <c r="P80" s="126"/>
-      <c r="Q80" s="126"/>
-      <c r="R80" s="126"/>
-      <c r="S80" s="124"/>
-      <c r="T80" s="124"/>
-      <c r="U80" s="124"/>
-      <c r="V80" s="124"/>
-      <c r="W80" s="124"/>
-      <c r="X80" s="124"/>
-      <c r="Y80" s="124"/>
-      <c r="Z80" s="124"/>
-      <c r="AA80" s="124"/>
+      <c r="L80" s="124"/>
+      <c r="M80" s="124"/>
+      <c r="N80" s="124"/>
+      <c r="O80" s="125"/>
+      <c r="P80" s="124"/>
+      <c r="Q80" s="124"/>
+      <c r="R80" s="124"/>
+      <c r="S80" s="122"/>
+      <c r="T80" s="122"/>
+      <c r="U80" s="122"/>
+      <c r="V80" s="122"/>
+      <c r="W80" s="122"/>
+      <c r="X80" s="122"/>
+      <c r="Y80" s="122"/>
+      <c r="Z80" s="122"/>
+      <c r="AA80" s="122"/>
       <c r="AB80" s="145"/>
       <c r="AC80" s="145"/>
       <c r="AD80" s="145"/>
@@ -8530,38 +8143,38 @@
       <c r="AL80" s="153"/>
     </row>
     <row r="81" s="3" customFormat="1" ht="14" spans="1:38">
-      <c r="A81" s="105"/>
-      <c r="B81" s="106"/>
-      <c r="C81" s="106"/>
-      <c r="D81" s="107" t="s">
+      <c r="A81" s="101"/>
+      <c r="B81" s="102"/>
+      <c r="C81" s="102"/>
+      <c r="D81" s="103" t="s">
         <v>121</v>
       </c>
-      <c r="E81" s="108"/>
-      <c r="F81" s="108"/>
-      <c r="G81" s="108"/>
-      <c r="H81" s="109"/>
-      <c r="I81" s="109"/>
-      <c r="J81" s="109" t="e">
-        <f t="shared" ref="J81:M81" si="83">J80/J6</f>
+      <c r="E81" s="104"/>
+      <c r="F81" s="104"/>
+      <c r="G81" s="104"/>
+      <c r="H81" s="105"/>
+      <c r="I81" s="105"/>
+      <c r="J81" s="105" t="e">
+        <f t="shared" ref="J81:M81" si="62">J80/J6</f>
         <v>#REF!</v>
       </c>
-      <c r="K81" s="109"/>
-      <c r="L81" s="127" t="e">
-        <f t="shared" si="83"/>
+      <c r="K81" s="105"/>
+      <c r="L81" s="126" t="e">
+        <f t="shared" si="62"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M81" s="127" t="e">
-        <f t="shared" si="83"/>
+      <c r="M81" s="126" t="e">
+        <f t="shared" si="62"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N81" s="127"/>
-      <c r="O81" s="127"/>
-      <c r="P81" s="127"/>
-      <c r="Q81" s="127" t="e">
+      <c r="N81" s="126"/>
+      <c r="O81" s="126"/>
+      <c r="P81" s="126"/>
+      <c r="Q81" s="126" t="e">
         <f>Q80/Q6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="R81" s="127" t="e">
+      <c r="R81" s="126" t="e">
         <f>R80/R6</f>
         <v>#DIV/0!</v>
       </c>
@@ -8587,37 +8200,37 @@
       <c r="AL81" s="155"/>
     </row>
     <row r="82" ht="14" spans="1:38">
-      <c r="A82" s="110"/>
-      <c r="B82" s="111"/>
-      <c r="C82" s="111"/>
-      <c r="D82" s="112"/>
-      <c r="E82" s="113"/>
-      <c r="F82" s="113"/>
-      <c r="G82" s="113"/>
-      <c r="H82" s="114"/>
-      <c r="I82" s="114"/>
-      <c r="J82" s="128" t="s">
+      <c r="A82" s="106"/>
+      <c r="B82" s="107"/>
+      <c r="C82" s="107"/>
+      <c r="D82" s="108"/>
+      <c r="E82" s="109"/>
+      <c r="F82" s="109"/>
+      <c r="G82" s="109"/>
+      <c r="H82" s="110"/>
+      <c r="I82" s="110"/>
+      <c r="J82" s="127" t="s">
         <v>122</v>
       </c>
-      <c r="K82" s="129"/>
-      <c r="L82" s="130" t="s">
+      <c r="K82" s="128"/>
+      <c r="L82" s="129" t="s">
         <v>123</v>
       </c>
-      <c r="M82" s="131"/>
-      <c r="N82" s="131"/>
-      <c r="O82" s="131"/>
-      <c r="P82" s="131"/>
-      <c r="Q82" s="131"/>
-      <c r="R82" s="131"/>
-      <c r="S82" s="131"/>
-      <c r="T82" s="131"/>
-      <c r="U82" s="131"/>
-      <c r="V82" s="131"/>
-      <c r="W82" s="131"/>
-      <c r="X82" s="131"/>
-      <c r="Y82" s="131"/>
+      <c r="M82" s="130"/>
+      <c r="N82" s="130"/>
+      <c r="O82" s="130"/>
+      <c r="P82" s="130"/>
+      <c r="Q82" s="130"/>
+      <c r="R82" s="130"/>
+      <c r="S82" s="130"/>
+      <c r="T82" s="130"/>
+      <c r="U82" s="130"/>
+      <c r="V82" s="130"/>
+      <c r="W82" s="130"/>
+      <c r="X82" s="130"/>
+      <c r="Y82" s="130"/>
       <c r="Z82" s="147"/>
-      <c r="AA82" s="89"/>
+      <c r="AA82" s="86"/>
       <c r="AB82" s="148"/>
       <c r="AC82" s="148"/>
       <c r="AD82" s="148"/>
@@ -8631,33 +8244,33 @@
       <c r="AL82" s="156"/>
     </row>
     <row r="83" ht="14" spans="1:38">
-      <c r="A83" s="110"/>
-      <c r="B83" s="111"/>
-      <c r="C83" s="111"/>
-      <c r="D83" s="112"/>
-      <c r="E83" s="113"/>
-      <c r="F83" s="113"/>
-      <c r="G83" s="113"/>
-      <c r="H83" s="114"/>
-      <c r="I83" s="114"/>
-      <c r="J83" s="132"/>
-      <c r="K83" s="114"/>
-      <c r="L83" s="133"/>
-      <c r="M83" s="131"/>
-      <c r="N83" s="131"/>
-      <c r="O83" s="131"/>
-      <c r="P83" s="131"/>
-      <c r="Q83" s="131"/>
-      <c r="R83" s="131"/>
-      <c r="S83" s="131"/>
-      <c r="T83" s="131"/>
-      <c r="U83" s="131"/>
-      <c r="V83" s="131"/>
-      <c r="W83" s="131"/>
-      <c r="X83" s="131"/>
-      <c r="Y83" s="131"/>
+      <c r="A83" s="106"/>
+      <c r="B83" s="107"/>
+      <c r="C83" s="107"/>
+      <c r="D83" s="108"/>
+      <c r="E83" s="109"/>
+      <c r="F83" s="109"/>
+      <c r="G83" s="109"/>
+      <c r="H83" s="110"/>
+      <c r="I83" s="110"/>
+      <c r="J83" s="131"/>
+      <c r="K83" s="110"/>
+      <c r="L83" s="132"/>
+      <c r="M83" s="130"/>
+      <c r="N83" s="130"/>
+      <c r="O83" s="130"/>
+      <c r="P83" s="130"/>
+      <c r="Q83" s="130"/>
+      <c r="R83" s="130"/>
+      <c r="S83" s="130"/>
+      <c r="T83" s="130"/>
+      <c r="U83" s="130"/>
+      <c r="V83" s="130"/>
+      <c r="W83" s="130"/>
+      <c r="X83" s="130"/>
+      <c r="Y83" s="130"/>
       <c r="Z83" s="147"/>
-      <c r="AA83" s="89"/>
+      <c r="AA83" s="86"/>
       <c r="AB83" s="148"/>
       <c r="AC83" s="148"/>
       <c r="AD83" s="148"/>
@@ -8671,24 +8284,24 @@
       <c r="AL83" s="156"/>
     </row>
     <row r="84" spans="1:38">
-      <c r="A84" s="115"/>
-      <c r="B84" s="116"/>
-      <c r="C84" s="116"/>
-      <c r="D84" s="117"/>
-      <c r="E84" s="118"/>
-      <c r="F84" s="118"/>
-      <c r="G84" s="118"/>
-      <c r="H84" s="119"/>
-      <c r="I84" s="119"/>
-      <c r="J84" s="134"/>
-      <c r="K84" s="135"/>
-      <c r="L84" s="135"/>
-      <c r="M84" s="136"/>
-      <c r="N84" s="137"/>
-      <c r="O84" s="137"/>
-      <c r="P84" s="138"/>
-      <c r="Q84" s="138"/>
-      <c r="R84" s="137"/>
+      <c r="A84" s="111"/>
+      <c r="B84" s="112"/>
+      <c r="C84" s="112"/>
+      <c r="D84" s="113"/>
+      <c r="E84" s="114"/>
+      <c r="F84" s="114"/>
+      <c r="G84" s="114"/>
+      <c r="H84" s="115"/>
+      <c r="I84" s="115"/>
+      <c r="J84" s="133"/>
+      <c r="K84" s="134"/>
+      <c r="L84" s="134"/>
+      <c r="M84" s="135"/>
+      <c r="N84" s="136"/>
+      <c r="O84" s="136"/>
+      <c r="P84" s="137"/>
+      <c r="Q84" s="137"/>
+      <c r="R84" s="136"/>
       <c r="S84" s="143"/>
       <c r="T84" s="143"/>
       <c r="U84" s="143"/>
@@ -8696,7 +8309,7 @@
       <c r="W84" s="143"/>
       <c r="X84" s="143"/>
       <c r="Y84" s="143"/>
-      <c r="Z84" s="141"/>
+      <c r="Z84" s="140"/>
       <c r="AA84" s="149"/>
       <c r="AD84" s="150"/>
       <c r="AE84" s="150"/>
@@ -8706,27 +8319,27 @@
       <c r="AI84" s="150"/>
       <c r="AJ84" s="150"/>
       <c r="AK84" s="150"/>
-      <c r="AL84" s="121"/>
+      <c r="AL84" s="117"/>
     </row>
     <row r="85" spans="1:38">
-      <c r="A85" s="120"/>
-      <c r="B85" s="121"/>
-      <c r="C85" s="121"/>
-      <c r="D85" s="121"/>
-      <c r="E85" s="122"/>
-      <c r="F85" s="122"/>
-      <c r="G85" s="122"/>
-      <c r="H85" s="122"/>
-      <c r="I85" s="122"/>
-      <c r="J85" s="122"/>
-      <c r="K85" s="139"/>
-      <c r="L85" s="122"/>
-      <c r="M85" s="140"/>
-      <c r="N85" s="140"/>
-      <c r="O85" s="140"/>
-      <c r="P85" s="140"/>
-      <c r="Q85" s="140"/>
-      <c r="R85" s="140"/>
+      <c r="A85" s="116"/>
+      <c r="B85" s="117"/>
+      <c r="C85" s="117"/>
+      <c r="D85" s="117"/>
+      <c r="E85" s="118"/>
+      <c r="F85" s="118"/>
+      <c r="G85" s="118"/>
+      <c r="H85" s="118"/>
+      <c r="I85" s="118"/>
+      <c r="J85" s="118"/>
+      <c r="K85" s="138"/>
+      <c r="L85" s="118"/>
+      <c r="M85" s="139"/>
+      <c r="N85" s="139"/>
+      <c r="O85" s="139"/>
+      <c r="P85" s="139"/>
+      <c r="Q85" s="139"/>
+      <c r="R85" s="139"/>
       <c r="S85" s="143"/>
       <c r="T85" s="143"/>
       <c r="U85" s="143"/>
@@ -8734,7 +8347,7 @@
       <c r="W85" s="143"/>
       <c r="X85" s="143"/>
       <c r="Y85" s="143"/>
-      <c r="Z85" s="140"/>
+      <c r="Z85" s="139"/>
       <c r="AA85" s="150"/>
       <c r="AB85" s="150"/>
       <c r="AC85" s="150"/>
@@ -8746,27 +8359,27 @@
       <c r="AI85" s="150"/>
       <c r="AJ85" s="150"/>
       <c r="AK85" s="150"/>
-      <c r="AL85" s="121"/>
+      <c r="AL85" s="117"/>
     </row>
     <row r="86" spans="1:38">
-      <c r="A86" s="120"/>
-      <c r="B86" s="121"/>
-      <c r="C86" s="121"/>
-      <c r="D86" s="121"/>
-      <c r="E86" s="122"/>
-      <c r="F86" s="122"/>
-      <c r="G86" s="122"/>
-      <c r="H86" s="122"/>
-      <c r="I86" s="122"/>
-      <c r="J86" s="122"/>
-      <c r="K86" s="139"/>
-      <c r="L86" s="122"/>
-      <c r="M86" s="140"/>
-      <c r="N86" s="140"/>
-      <c r="O86" s="140"/>
-      <c r="P86" s="140"/>
-      <c r="Q86" s="140"/>
-      <c r="R86" s="140"/>
+      <c r="A86" s="116"/>
+      <c r="B86" s="117"/>
+      <c r="C86" s="117"/>
+      <c r="D86" s="117"/>
+      <c r="E86" s="118"/>
+      <c r="F86" s="118"/>
+      <c r="G86" s="118"/>
+      <c r="H86" s="118"/>
+      <c r="I86" s="118"/>
+      <c r="J86" s="118"/>
+      <c r="K86" s="138"/>
+      <c r="L86" s="118"/>
+      <c r="M86" s="139"/>
+      <c r="N86" s="139"/>
+      <c r="O86" s="139"/>
+      <c r="P86" s="139"/>
+      <c r="Q86" s="139"/>
+      <c r="R86" s="139"/>
       <c r="S86" s="143"/>
       <c r="T86" s="143"/>
       <c r="U86" s="143"/>
@@ -8774,7 +8387,7 @@
       <c r="W86" s="143"/>
       <c r="X86" s="143"/>
       <c r="Y86" s="143"/>
-      <c r="Z86" s="140"/>
+      <c r="Z86" s="139"/>
       <c r="AA86" s="150"/>
       <c r="AB86" s="150"/>
       <c r="AC86" s="150"/>
@@ -8786,27 +8399,27 @@
       <c r="AI86" s="150"/>
       <c r="AJ86" s="150"/>
       <c r="AK86" s="150"/>
-      <c r="AL86" s="121"/>
+      <c r="AL86" s="117"/>
     </row>
     <row r="87" spans="1:38">
-      <c r="A87" s="120"/>
-      <c r="B87" s="121"/>
-      <c r="C87" s="121"/>
-      <c r="D87" s="121"/>
-      <c r="E87" s="123"/>
-      <c r="F87" s="123"/>
-      <c r="G87" s="123"/>
-      <c r="H87" s="122"/>
-      <c r="I87" s="122"/>
-      <c r="J87" s="122"/>
-      <c r="K87" s="123"/>
-      <c r="L87" s="122"/>
-      <c r="M87" s="140"/>
-      <c r="N87" s="141"/>
-      <c r="O87" s="140"/>
-      <c r="P87" s="140"/>
-      <c r="Q87" s="140"/>
-      <c r="R87" s="137"/>
+      <c r="A87" s="116"/>
+      <c r="B87" s="117"/>
+      <c r="C87" s="117"/>
+      <c r="D87" s="117"/>
+      <c r="E87" s="119"/>
+      <c r="F87" s="119"/>
+      <c r="G87" s="119"/>
+      <c r="H87" s="118"/>
+      <c r="I87" s="118"/>
+      <c r="J87" s="118"/>
+      <c r="K87" s="119"/>
+      <c r="L87" s="118"/>
+      <c r="M87" s="139"/>
+      <c r="N87" s="140"/>
+      <c r="O87" s="139"/>
+      <c r="P87" s="139"/>
+      <c r="Q87" s="139"/>
+      <c r="R87" s="136"/>
       <c r="S87" s="143"/>
       <c r="T87" s="143"/>
       <c r="U87" s="143"/>
@@ -8814,7 +8427,7 @@
       <c r="W87" s="143"/>
       <c r="X87" s="143"/>
       <c r="Y87" s="143"/>
-      <c r="Z87" s="140"/>
+      <c r="Z87" s="139"/>
       <c r="AA87" s="150"/>
       <c r="AB87" s="150"/>
       <c r="AC87" s="150"/>
@@ -8826,7 +8439,7 @@
       <c r="AI87" s="150"/>
       <c r="AJ87" s="150"/>
       <c r="AK87" s="150"/>
-      <c r="AL87" s="121"/>
+      <c r="AL87" s="117"/>
     </row>
   </sheetData>
   <mergeCells count="58">

--- a/项目效益审核表.xlsx
+++ b/项目效益审核表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="22190" windowHeight="9760"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="AL8" s="28"/>
     </row>
-    <row r="9" spans="1:38">
+    <row r="9" ht="14" spans="1:38">
       <c r="A9" s="30"/>
       <c r="B9" s="20"/>
       <c r="C9" s="20"/>
@@ -7373,10 +7373,7 @@
         <f t="shared" ref="R69:R72" si="52">M69+N69+O69+P69</f>
         <v>0</v>
       </c>
-      <c r="S69" s="141">
-        <f t="shared" ref="S69:S72" si="53">SUM(T69:V69)</f>
-        <v>0</v>
-      </c>
+      <c r="S69" s="141"/>
       <c r="T69" s="141"/>
       <c r="U69" s="141"/>
       <c r="V69" s="141"/>
@@ -7424,7 +7421,7 @@
       <c r="M70" s="36"/>
       <c r="N70" s="36"/>
       <c r="O70" s="75">
-        <f t="shared" ref="O69:O72" si="54">L70-M70</f>
+        <f t="shared" ref="O69:O72" si="53">L70-M70</f>
         <v>0</v>
       </c>
       <c r="P70" s="75">
@@ -7439,10 +7436,7 @@
         <f t="shared" si="52"/>
         <v>0</v>
       </c>
-      <c r="S70" s="141">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
+      <c r="S70" s="141"/>
       <c r="T70" s="141"/>
       <c r="U70" s="141"/>
       <c r="V70" s="141"/>
@@ -7487,7 +7481,7 @@
       <c r="M71" s="36"/>
       <c r="N71" s="36"/>
       <c r="O71" s="75">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="P71" s="75">
@@ -7502,10 +7496,7 @@
         <f t="shared" si="52"/>
         <v>0</v>
       </c>
-      <c r="S71" s="141">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
+      <c r="S71" s="141"/>
       <c r="T71" s="141"/>
       <c r="U71" s="141"/>
       <c r="V71" s="141"/>
@@ -7550,7 +7541,7 @@
       <c r="M72" s="36"/>
       <c r="N72" s="36"/>
       <c r="O72" s="75">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="P72" s="75">
@@ -7565,10 +7556,7 @@
         <f t="shared" si="52"/>
         <v>0</v>
       </c>
-      <c r="S72" s="141">
-        <f t="shared" si="53"/>
-        <v>0</v>
-      </c>
+      <c r="S72" s="141"/>
       <c r="T72" s="141"/>
       <c r="U72" s="141"/>
       <c r="V72" s="141"/>
@@ -7611,103 +7599,103 @@
         <v>0</v>
       </c>
       <c r="M73" s="122">
-        <f t="shared" ref="M73:AK73" si="55">SUM(M74:M76)</f>
+        <f t="shared" ref="M73:AK73" si="54">SUM(M74:M76)</f>
         <v>0</v>
       </c>
       <c r="N73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="O73" s="76">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="P73" s="76">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="Q73" s="76">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="R73" s="76">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="S73" s="122">
-        <f t="shared" si="55"/>
+        <f>SUM(S74:S76)</f>
         <v>0</v>
       </c>
       <c r="T73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="U73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="V73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="W73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="X73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="Y73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="Z73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AA73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AB73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AC73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AD73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AE73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AF73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AG73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AH73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AI73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AJ73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AK73" s="122">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="AL73" s="151"/>
@@ -7736,25 +7724,22 @@
       <c r="M74" s="36"/>
       <c r="N74" s="36"/>
       <c r="O74" s="75">
-        <f t="shared" ref="O74:O76" si="56">L74-M74</f>
+        <f t="shared" ref="O74:O76" si="55">L74-M74</f>
         <v>0</v>
       </c>
       <c r="P74" s="75">
-        <f t="shared" ref="P74:P76" si="57">K74-N74</f>
+        <f t="shared" ref="P74:P76" si="56">K74-N74</f>
         <v>0</v>
       </c>
       <c r="Q74" s="75">
-        <f t="shared" ref="Q74:Q76" si="58">M74+O74</f>
+        <f t="shared" ref="Q74:Q76" si="57">M74+O74</f>
         <v>0</v>
       </c>
       <c r="R74" s="75">
-        <f t="shared" ref="R74:R76" si="59">M74+N74+O74+P74</f>
-        <v>0</v>
-      </c>
-      <c r="S74" s="141">
-        <f t="shared" ref="S74:S76" si="60">SUM(T74:V74)</f>
-        <v>0</v>
-      </c>
+        <f t="shared" ref="R74:R76" si="58">M74+N74+O74+P74</f>
+        <v>0</v>
+      </c>
+      <c r="S74" s="141"/>
       <c r="T74" s="141"/>
       <c r="U74" s="141"/>
       <c r="V74" s="141"/>
@@ -7796,25 +7781,22 @@
       <c r="M75" s="36"/>
       <c r="N75" s="36"/>
       <c r="O75" s="75">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="P75" s="75">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="P75" s="75">
+      <c r="Q75" s="75">
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="Q75" s="75">
+      <c r="R75" s="75">
         <f t="shared" si="58"/>
         <v>0</v>
       </c>
-      <c r="R75" s="75">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="S75" s="141">
-        <f t="shared" si="60"/>
-        <v>0</v>
-      </c>
+      <c r="S75" s="141"/>
       <c r="T75" s="141"/>
       <c r="U75" s="141"/>
       <c r="V75" s="141"/>
@@ -7856,25 +7838,22 @@
       <c r="M76" s="36"/>
       <c r="N76" s="36"/>
       <c r="O76" s="75">
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="P76" s="75">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="P76" s="75">
+      <c r="Q76" s="75">
         <f t="shared" si="57"/>
         <v>0</v>
       </c>
-      <c r="Q76" s="75">
+      <c r="R76" s="75">
         <f t="shared" si="58"/>
         <v>0</v>
       </c>
-      <c r="R76" s="75">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="S76" s="141">
-        <f t="shared" si="60"/>
-        <v>0</v>
-      </c>
+      <c r="S76" s="141"/>
       <c r="T76" s="141"/>
       <c r="U76" s="141"/>
       <c r="V76" s="141"/>
@@ -7930,27 +7909,27 @@
         <v>0</v>
       </c>
       <c r="N77" s="124">
-        <f t="shared" ref="M77:S77" si="61">N68+N69+N70+N71</f>
+        <f t="shared" ref="M77:S77" si="59">N68+N69+N70+N71</f>
         <v>0</v>
       </c>
       <c r="O77" s="125">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="P77" s="124">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="Q77" s="124">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="R77" s="124">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="S77" s="122">
-        <f t="shared" si="61"/>
+        <f>S68+S69+S70+S71</f>
         <v>0</v>
       </c>
       <c r="T77" s="122"/>
@@ -8155,16 +8134,16 @@
       <c r="H81" s="105"/>
       <c r="I81" s="105"/>
       <c r="J81" s="105" t="e">
-        <f t="shared" ref="J81:M81" si="62">J80/J6</f>
+        <f t="shared" ref="J81:M81" si="60">J80/J6</f>
         <v>#REF!</v>
       </c>
       <c r="K81" s="105"/>
       <c r="L81" s="126" t="e">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M81" s="126" t="e">
-        <f t="shared" si="62"/>
+        <f t="shared" si="60"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N81" s="126"/>

--- a/项目效益审核表.xlsx
+++ b/项目效益审核表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22190" windowHeight="9760"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -512,7 +512,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="124">
   <si>
     <t xml:space="preserve">            项目效益审核表               单位：元</t>
   </si>
@@ -868,7 +868,7 @@
     <t>八、研发费用</t>
   </si>
   <si>
-    <t>九、成本及费用合计（三+四+五+六+七）</t>
+    <t>九、成本及费用合计（三+四+五+六+七+八）</t>
   </si>
   <si>
     <t>十、增值税实际税负（按财务数据）</t>
@@ -2281,11 +2281,11 @@
     <xf numFmtId="43" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="43" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2856,9 +2856,9 @@
     <col min="2" max="2" width="21.8181818181818" style="5" customWidth="1"/>
     <col min="3" max="3" width="16.7636363636364" style="5" customWidth="1"/>
     <col min="4" max="4" width="37.7545454545455" style="5" customWidth="1"/>
-    <col min="5" max="5" width="35.0545454545455" style="5" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="20" style="5" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="19.1909090909091" style="5" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="35.0545454545455" style="5" customWidth="1"/>
+    <col min="6" max="6" width="20" style="5" customWidth="1"/>
+    <col min="7" max="7" width="19.1909090909091" style="5" customWidth="1"/>
     <col min="8" max="8" width="20.9090909090909" style="5" customWidth="1"/>
     <col min="9" max="9" width="25.2545454545455" style="5" customWidth="1"/>
     <col min="10" max="11" width="20.9090909090909" style="5" customWidth="1"/>
@@ -3215,7 +3215,10 @@
         <f>M6+N6+O6+P6</f>
         <v>0</v>
       </c>
-      <c r="S6" s="83"/>
+      <c r="S6" s="83">
+        <f>SUM(T6+U6+V6)</f>
+        <v>0</v>
+      </c>
       <c r="T6" s="83"/>
       <c r="U6" s="83"/>
       <c r="V6" s="83"/>
@@ -3242,7 +3245,7 @@
       </c>
       <c r="AL6" s="21"/>
     </row>
-    <row r="7" ht="14" spans="1:38">
+    <row r="7" spans="1:38">
       <c r="A7" s="13"/>
       <c r="B7" s="14" t="s">
         <v>48</v>
@@ -3615,11 +3618,17 @@
       <c r="P12" s="75"/>
       <c r="Q12" s="75"/>
       <c r="R12" s="75"/>
-      <c r="S12" s="36"/>
+      <c r="S12" s="36">
+        <f t="shared" ref="S12:S15" si="0">SUM(T12:V12)</f>
+        <v>0</v>
+      </c>
       <c r="T12" s="36"/>
       <c r="U12" s="36"/>
       <c r="V12" s="36"/>
-      <c r="W12" s="36"/>
+      <c r="W12" s="36">
+        <f t="shared" ref="W12:W15" si="1">SUM(X12:Y12)</f>
+        <v>0</v>
+      </c>
       <c r="X12" s="36"/>
       <c r="Y12" s="36"/>
       <c r="Z12" s="36"/>
@@ -3649,37 +3658,43 @@
       <c r="H13" s="36"/>
       <c r="I13" s="36"/>
       <c r="J13" s="75">
-        <f t="shared" ref="J13:J15" si="0">H13+I13</f>
+        <f t="shared" ref="J13:J15" si="2">H13+I13</f>
         <v>0</v>
       </c>
       <c r="K13" s="36"/>
       <c r="L13" s="75">
-        <f t="shared" ref="L13:L15" si="1">J13-K13</f>
+        <f t="shared" ref="L13:L15" si="3">J13-K13</f>
         <v>0</v>
       </c>
       <c r="M13" s="36"/>
       <c r="N13" s="36"/>
       <c r="O13" s="75">
-        <f t="shared" ref="O13:O15" si="2">L13-M13</f>
+        <f t="shared" ref="O13:O15" si="4">L13-M13</f>
         <v>0</v>
       </c>
       <c r="P13" s="75">
-        <f t="shared" ref="P13:P15" si="3">K13-N13</f>
+        <f t="shared" ref="P13:P15" si="5">K13-N13</f>
         <v>0</v>
       </c>
       <c r="Q13" s="75">
-        <f t="shared" ref="Q13:Q15" si="4">M13+O13</f>
+        <f t="shared" ref="Q13:Q15" si="6">M13+O13</f>
         <v>0</v>
       </c>
       <c r="R13" s="75">
-        <f t="shared" ref="R13:R15" si="5">M13+N13+O13+P13</f>
-        <v>0</v>
-      </c>
-      <c r="S13" s="36"/>
+        <f t="shared" ref="R13:R15" si="7">M13+N13+O13+P13</f>
+        <v>0</v>
+      </c>
+      <c r="S13" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="T13" s="36"/>
       <c r="U13" s="36"/>
       <c r="V13" s="36"/>
-      <c r="W13" s="36"/>
+      <c r="W13" s="36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="X13" s="36"/>
       <c r="Y13" s="36"/>
       <c r="Z13" s="36"/>
@@ -3709,37 +3724,43 @@
       <c r="H14" s="36"/>
       <c r="I14" s="36"/>
       <c r="J14" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K14" s="36"/>
       <c r="L14" s="75">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M14" s="36"/>
       <c r="N14" s="36"/>
       <c r="O14" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P14" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q14" s="75">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R14" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S14" s="36"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S14" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="T14" s="36"/>
       <c r="U14" s="36"/>
       <c r="V14" s="36"/>
-      <c r="W14" s="36"/>
+      <c r="W14" s="36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="X14" s="36"/>
       <c r="Y14" s="36"/>
       <c r="Z14" s="36"/>
@@ -3769,37 +3790,43 @@
       <c r="H15" s="36"/>
       <c r="I15" s="36"/>
       <c r="J15" s="75">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K15" s="36"/>
       <c r="L15" s="75">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M15" s="36"/>
       <c r="N15" s="36"/>
       <c r="O15" s="75">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P15" s="75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="Q15" s="75">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="R15" s="75">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S15" s="36"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S15" s="36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="T15" s="36"/>
       <c r="U15" s="36"/>
       <c r="V15" s="36"/>
-      <c r="W15" s="36"/>
+      <c r="W15" s="36">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="X15" s="36"/>
       <c r="Y15" s="36"/>
       <c r="Z15" s="36"/>
@@ -3869,123 +3896,123 @@
       <c r="F17" s="44"/>
       <c r="G17" s="44"/>
       <c r="H17" s="44">
-        <f t="shared" ref="H17:AK17" si="6">SUM(H12:H16)</f>
+        <f t="shared" ref="H17:AK17" si="8">SUM(H12:H16)</f>
         <v>0</v>
       </c>
       <c r="I17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J17" s="76">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="L17" s="76">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="M17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="N17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O17" s="76">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="P17" s="76">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Q17" s="76">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="R17" s="76">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="S17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="V17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="W17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="X17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Y17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="Z17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AA17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AB17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AC17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AD17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AF17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AG17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AH17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AI17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AJ17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AK17" s="44">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AL17" s="96"/>
@@ -4045,37 +4072,43 @@
       <c r="H19" s="36"/>
       <c r="I19" s="36"/>
       <c r="J19" s="75">
-        <f t="shared" ref="J19:J21" si="7">H19+I19</f>
+        <f t="shared" ref="J19:J21" si="9">H19+I19</f>
         <v>0</v>
       </c>
       <c r="K19" s="36"/>
       <c r="L19" s="75">
-        <f t="shared" ref="L19:L21" si="8">J19-K19</f>
+        <f t="shared" ref="L19:L21" si="10">J19-K19</f>
         <v>0</v>
       </c>
       <c r="M19" s="36"/>
       <c r="N19" s="36"/>
       <c r="O19" s="75">
-        <f t="shared" ref="O19:O21" si="9">L19-M19</f>
+        <f t="shared" ref="O19:O21" si="11">L19-M19</f>
         <v>0</v>
       </c>
       <c r="P19" s="75">
-        <f t="shared" ref="P19:P21" si="10">K19-N19</f>
+        <f t="shared" ref="P19:P21" si="12">K19-N19</f>
         <v>0</v>
       </c>
       <c r="Q19" s="75">
-        <f t="shared" ref="Q19:Q21" si="11">M19+O19</f>
+        <f t="shared" ref="Q19:Q21" si="13">M19+O19</f>
         <v>0</v>
       </c>
       <c r="R19" s="75">
-        <f t="shared" ref="R19:R21" si="12">M19+N19+O19+P19</f>
-        <v>0</v>
-      </c>
-      <c r="S19" s="36"/>
+        <f t="shared" ref="R19:R21" si="14">M19+N19+O19+P19</f>
+        <v>0</v>
+      </c>
+      <c r="S19" s="36">
+        <f t="shared" ref="S19:S21" si="15">SUM(T19:V19)</f>
+        <v>0</v>
+      </c>
       <c r="T19" s="36"/>
       <c r="U19" s="36"/>
       <c r="V19" s="36"/>
-      <c r="W19" s="36"/>
+      <c r="W19" s="36">
+        <f t="shared" ref="W19:W21" si="16">SUM(X19:Y19)</f>
+        <v>0</v>
+      </c>
       <c r="X19" s="36"/>
       <c r="Y19" s="36"/>
       <c r="Z19" s="36"/>
@@ -4105,37 +4138,43 @@
       <c r="H20" s="36"/>
       <c r="I20" s="36"/>
       <c r="J20" s="75">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K20" s="36"/>
       <c r="L20" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M20" s="36"/>
       <c r="N20" s="36"/>
       <c r="O20" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P20" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q20" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R20" s="75">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S20" s="36"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="S20" s="36">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="T20" s="36"/>
       <c r="U20" s="36"/>
       <c r="V20" s="36"/>
-      <c r="W20" s="36"/>
+      <c r="W20" s="36">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
       <c r="X20" s="36"/>
       <c r="Y20" s="36"/>
       <c r="Z20" s="36"/>
@@ -4165,37 +4204,43 @@
       <c r="H21" s="36"/>
       <c r="I21" s="36"/>
       <c r="J21" s="75">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="K21" s="36"/>
       <c r="L21" s="75">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M21" s="36"/>
       <c r="N21" s="36"/>
       <c r="O21" s="75">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="P21" s="75">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q21" s="75">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R21" s="75">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="S21" s="36"/>
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="S21" s="36">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="T21" s="36"/>
       <c r="U21" s="36"/>
       <c r="V21" s="36"/>
-      <c r="W21" s="36"/>
+      <c r="W21" s="36">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
       <c r="X21" s="36"/>
       <c r="Y21" s="36"/>
       <c r="Z21" s="36"/>
@@ -4265,123 +4310,123 @@
       <c r="F23" s="44"/>
       <c r="G23" s="44"/>
       <c r="H23" s="44">
-        <f t="shared" ref="H23:AK23" si="13">SUM(H19:H22)</f>
+        <f t="shared" ref="H23:AK23" si="17">SUM(H19:H22)</f>
         <v>0</v>
       </c>
       <c r="I23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="J23" s="76">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="K23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="L23" s="76">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="N23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O23" s="76">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P23" s="76">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Q23" s="76">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="R23" s="76">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="S23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="T23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="U23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="V23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="W23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="X23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Y23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Z23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AA23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AB23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AC23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AD23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AE23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AF23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AG23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AH23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AI23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AJ23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AK23" s="44">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AL23" s="96"/>
@@ -4483,37 +4528,43 @@
       <c r="H26" s="36"/>
       <c r="I26" s="36"/>
       <c r="J26" s="75">
-        <f t="shared" ref="J26:J28" si="14">H26+I26</f>
+        <f t="shared" ref="J26:J28" si="18">H26+I26</f>
         <v>0</v>
       </c>
       <c r="K26" s="36"/>
       <c r="L26" s="75">
-        <f t="shared" ref="L26:L28" si="15">J26-K26</f>
+        <f t="shared" ref="L26:L28" si="19">J26-K26</f>
         <v>0</v>
       </c>
       <c r="M26" s="36"/>
       <c r="N26" s="36"/>
       <c r="O26" s="75">
-        <f t="shared" ref="O26:O28" si="16">L26-M26</f>
+        <f t="shared" ref="O26:O28" si="20">L26-M26</f>
         <v>0</v>
       </c>
       <c r="P26" s="75">
-        <f t="shared" ref="P26:P28" si="17">K26-N26</f>
+        <f t="shared" ref="P26:P28" si="21">K26-N26</f>
         <v>0</v>
       </c>
       <c r="Q26" s="75">
-        <f t="shared" ref="Q26:Q32" si="18">M26+O26</f>
+        <f t="shared" ref="Q26:Q32" si="22">M26+O26</f>
         <v>0</v>
       </c>
       <c r="R26" s="75">
-        <f t="shared" ref="R26:R32" si="19">M26+N26+O26+P26</f>
-        <v>0</v>
-      </c>
-      <c r="S26" s="36"/>
+        <f t="shared" ref="R26:R32" si="23">M26+N26+O26+P26</f>
+        <v>0</v>
+      </c>
+      <c r="S26" s="36">
+        <f t="shared" ref="S26:S32" si="24">SUM(T26:V26)</f>
+        <v>0</v>
+      </c>
       <c r="T26" s="36"/>
       <c r="U26" s="36"/>
       <c r="V26" s="36"/>
-      <c r="W26" s="36"/>
+      <c r="W26" s="36">
+        <f t="shared" ref="W26:W32" si="25">SUM(X26:Y26)</f>
+        <v>0</v>
+      </c>
       <c r="X26" s="36"/>
       <c r="Y26" s="36"/>
       <c r="Z26" s="36"/>
@@ -4543,37 +4594,43 @@
       <c r="H27" s="36"/>
       <c r="I27" s="36"/>
       <c r="J27" s="75">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="K27" s="36"/>
       <c r="L27" s="75">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M27" s="36"/>
       <c r="N27" s="36"/>
       <c r="O27" s="75">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="P27" s="75">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="Q27" s="75">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="R27" s="75">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="S27" s="36"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="S27" s="36">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="T27" s="36"/>
       <c r="U27" s="36"/>
       <c r="V27" s="36"/>
-      <c r="W27" s="36"/>
+      <c r="W27" s="36">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="X27" s="36"/>
       <c r="Y27" s="36"/>
       <c r="Z27" s="36"/>
@@ -4603,37 +4660,43 @@
       <c r="H28" s="36"/>
       <c r="I28" s="36"/>
       <c r="J28" s="75">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="K28" s="36"/>
       <c r="L28" s="75">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M28" s="36"/>
       <c r="N28" s="36"/>
       <c r="O28" s="75">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="P28" s="75">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="Q28" s="75">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="R28" s="75">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="S28" s="36"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="S28" s="36">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="T28" s="36"/>
       <c r="U28" s="36"/>
       <c r="V28" s="36"/>
-      <c r="W28" s="36"/>
+      <c r="W28" s="36">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="X28" s="36"/>
       <c r="Y28" s="36"/>
       <c r="Z28" s="36"/>
@@ -4670,18 +4733,24 @@
       <c r="O29" s="75"/>
       <c r="P29" s="75"/>
       <c r="Q29" s="75">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="R29" s="75">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="S29" s="36"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="S29" s="36">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="T29" s="36"/>
       <c r="U29" s="36"/>
       <c r="V29" s="36"/>
-      <c r="W29" s="36"/>
+      <c r="W29" s="36">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="X29" s="36"/>
       <c r="Y29" s="36"/>
       <c r="Z29" s="36"/>
@@ -4713,37 +4782,43 @@
       <c r="H30" s="36"/>
       <c r="I30" s="36"/>
       <c r="J30" s="75">
-        <f t="shared" ref="J30:J32" si="20">H30+I30</f>
+        <f t="shared" ref="J30:J32" si="26">H30+I30</f>
         <v>0</v>
       </c>
       <c r="K30" s="36"/>
       <c r="L30" s="75">
-        <f t="shared" ref="L30:L32" si="21">J30-K30</f>
+        <f t="shared" ref="L30:L32" si="27">J30-K30</f>
         <v>0</v>
       </c>
       <c r="M30" s="36"/>
       <c r="N30" s="36"/>
       <c r="O30" s="75">
-        <f t="shared" ref="O30:O32" si="22">L30-M30</f>
+        <f t="shared" ref="O30:O32" si="28">L30-M30</f>
         <v>0</v>
       </c>
       <c r="P30" s="75">
-        <f t="shared" ref="P30:P32" si="23">K30-N30</f>
+        <f t="shared" ref="P30:P32" si="29">K30-N30</f>
         <v>0</v>
       </c>
       <c r="Q30" s="75">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="R30" s="75">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="S30" s="36"/>
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="S30" s="36">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="T30" s="36"/>
       <c r="U30" s="36"/>
       <c r="V30" s="36"/>
-      <c r="W30" s="36"/>
+      <c r="W30" s="36">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="X30" s="36"/>
       <c r="Y30" s="36"/>
       <c r="Z30" s="36"/>
@@ -4775,37 +4850,43 @@
       <c r="H31" s="50"/>
       <c r="I31" s="50"/>
       <c r="J31" s="75">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="K31" s="50"/>
       <c r="L31" s="75">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="M31" s="50"/>
       <c r="N31" s="50"/>
       <c r="O31" s="75">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="P31" s="75">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="75">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="P31" s="75">
+      <c r="R31" s="75">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="Q31" s="75">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="R31" s="75">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="S31" s="50"/>
+      <c r="S31" s="36">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="T31" s="50"/>
       <c r="U31" s="50"/>
       <c r="V31" s="50"/>
-      <c r="W31" s="50"/>
+      <c r="W31" s="36">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="X31" s="50"/>
       <c r="Y31" s="50"/>
       <c r="Z31" s="50"/>
@@ -4837,37 +4918,43 @@
       <c r="H32" s="50"/>
       <c r="I32" s="50"/>
       <c r="J32" s="75">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="K32" s="50"/>
       <c r="L32" s="75">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="M32" s="50"/>
       <c r="N32" s="50"/>
       <c r="O32" s="75">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="P32" s="75">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="Q32" s="75">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="P32" s="75">
+      <c r="R32" s="75">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="Q32" s="75">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="R32" s="75">
-        <f t="shared" si="19"/>
-        <v>0</v>
-      </c>
-      <c r="S32" s="50"/>
+      <c r="S32" s="36">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
       <c r="T32" s="50"/>
       <c r="U32" s="50"/>
       <c r="V32" s="50"/>
-      <c r="W32" s="50"/>
+      <c r="W32" s="36">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="X32" s="50"/>
       <c r="Y32" s="50"/>
       <c r="Z32" s="50"/>
@@ -4937,123 +5024,123 @@
       <c r="F34" s="44"/>
       <c r="G34" s="44"/>
       <c r="H34" s="44">
-        <f t="shared" ref="H34:AK34" si="24">SUM(H25:H33)</f>
+        <f t="shared" ref="H34:AK34" si="30">SUM(H25:H33)</f>
         <v>0</v>
       </c>
       <c r="I34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="J34" s="76">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="L34" s="76">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="N34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="O34" s="76">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="P34" s="76">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Q34" s="76">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="R34" s="76">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="S34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="T34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="U34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="V34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="W34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="X34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Y34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Z34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AA34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AB34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AC34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AD34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AE34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AF34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AG34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AH34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AI34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AJ34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AK34" s="44">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="AL34" s="96"/>
@@ -5113,37 +5200,43 @@
       <c r="H36" s="36"/>
       <c r="I36" s="36"/>
       <c r="J36" s="75">
-        <f t="shared" ref="J36:J44" si="25">H36+I36</f>
+        <f t="shared" ref="J36:J44" si="31">H36+I36</f>
         <v>0</v>
       </c>
       <c r="K36" s="36"/>
       <c r="L36" s="75">
-        <f t="shared" ref="L36:L44" si="26">J36-K36</f>
+        <f t="shared" ref="L36:L44" si="32">J36-K36</f>
         <v>0</v>
       </c>
       <c r="M36" s="36"/>
       <c r="N36" s="36"/>
       <c r="O36" s="75">
-        <f t="shared" ref="O36:O44" si="27">L36-M36</f>
+        <f t="shared" ref="O36:O44" si="33">L36-M36</f>
         <v>0</v>
       </c>
       <c r="P36" s="75">
-        <f t="shared" ref="P36:P44" si="28">K36-N36</f>
+        <f t="shared" ref="P36:P44" si="34">K36-N36</f>
         <v>0</v>
       </c>
       <c r="Q36" s="75">
-        <f t="shared" ref="Q36:Q44" si="29">M36+O36</f>
+        <f t="shared" ref="Q36:Q44" si="35">M36+O36</f>
         <v>0</v>
       </c>
       <c r="R36" s="75">
-        <f t="shared" ref="R36:R44" si="30">M36+N36+O36+P36</f>
-        <v>0</v>
-      </c>
-      <c r="S36" s="36"/>
+        <f t="shared" ref="R36:R44" si="36">M36+N36+O36+P36</f>
+        <v>0</v>
+      </c>
+      <c r="S36" s="36">
+        <f t="shared" ref="S36:S44" si="37">SUM(T36:V36)</f>
+        <v>0</v>
+      </c>
       <c r="T36" s="36"/>
       <c r="U36" s="36"/>
       <c r="V36" s="36"/>
-      <c r="W36" s="36"/>
+      <c r="W36" s="36">
+        <f t="shared" ref="W36:W44" si="38">SUM(X36:Y36)</f>
+        <v>0</v>
+      </c>
       <c r="X36" s="36"/>
       <c r="Y36" s="36"/>
       <c r="Z36" s="36"/>
@@ -5213,123 +5306,123 @@
       <c r="F38" s="54"/>
       <c r="G38" s="54"/>
       <c r="H38" s="44">
-        <f t="shared" ref="H38:AK38" si="31">SUM(H36:H37)</f>
+        <f t="shared" ref="H38:AK38" si="39">SUM(H36:H37)</f>
         <v>0</v>
       </c>
       <c r="I38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="J38" s="76">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="K38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="L38" s="76">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="M38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="N38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="O38" s="76">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="P38" s="76">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="Q38" s="76">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="R38" s="76">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="S38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="T38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="U38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="V38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="W38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="X38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="Y38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="Z38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AA38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AB38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AC38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AD38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AE38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AF38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AG38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AH38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AI38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AJ38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AK38" s="44">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="AL38" s="96"/>
@@ -5389,37 +5482,43 @@
       <c r="H40" s="36"/>
       <c r="I40" s="36"/>
       <c r="J40" s="75">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="K40" s="36"/>
       <c r="L40" s="75">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="M40" s="36"/>
       <c r="N40" s="36"/>
       <c r="O40" s="75">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="P40" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Q40" s="75">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="R40" s="75">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="S40" s="36"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="36">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="T40" s="36"/>
       <c r="U40" s="36"/>
       <c r="V40" s="36"/>
-      <c r="W40" s="36"/>
+      <c r="W40" s="36">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
       <c r="X40" s="36"/>
       <c r="Y40" s="36"/>
       <c r="Z40" s="36"/>
@@ -5449,37 +5548,43 @@
       <c r="H41" s="36"/>
       <c r="I41" s="36"/>
       <c r="J41" s="75">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="K41" s="36"/>
       <c r="L41" s="75">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="M41" s="36"/>
       <c r="N41" s="36"/>
       <c r="O41" s="75">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="P41" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Q41" s="75">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="R41" s="75">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="S41" s="36"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="S41" s="36">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="T41" s="36"/>
       <c r="U41" s="36"/>
       <c r="V41" s="36"/>
-      <c r="W41" s="36"/>
+      <c r="W41" s="36">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
       <c r="X41" s="36"/>
       <c r="Y41" s="36"/>
       <c r="Z41" s="36"/>
@@ -5509,37 +5614,43 @@
       <c r="H42" s="36"/>
       <c r="I42" s="36"/>
       <c r="J42" s="75">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="K42" s="36"/>
       <c r="L42" s="75">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="M42" s="36"/>
       <c r="N42" s="36"/>
       <c r="O42" s="75">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="P42" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Q42" s="75">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="R42" s="75">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="S42" s="36"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="S42" s="36">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="T42" s="36"/>
       <c r="U42" s="36"/>
       <c r="V42" s="36"/>
-      <c r="W42" s="36"/>
+      <c r="W42" s="36">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
       <c r="X42" s="36"/>
       <c r="Y42" s="36"/>
       <c r="Z42" s="36"/>
@@ -5569,37 +5680,43 @@
       <c r="H43" s="36"/>
       <c r="I43" s="36"/>
       <c r="J43" s="75">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="K43" s="36"/>
       <c r="L43" s="75">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="M43" s="36"/>
       <c r="N43" s="36"/>
       <c r="O43" s="75">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="P43" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Q43" s="75">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="R43" s="75">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="S43" s="36"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="36">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="T43" s="36"/>
       <c r="U43" s="36"/>
       <c r="V43" s="36"/>
-      <c r="W43" s="36"/>
+      <c r="W43" s="36">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
       <c r="X43" s="36"/>
       <c r="Y43" s="36"/>
       <c r="Z43" s="36"/>
@@ -5629,37 +5746,43 @@
       <c r="H44" s="36"/>
       <c r="I44" s="36"/>
       <c r="J44" s="75">
-        <f t="shared" si="25"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="K44" s="36"/>
       <c r="L44" s="75">
-        <f t="shared" si="26"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="M44" s="36"/>
       <c r="N44" s="36"/>
       <c r="O44" s="75">
-        <f t="shared" si="27"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="P44" s="75">
-        <f t="shared" si="28"/>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="Q44" s="75">
-        <f t="shared" si="29"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="R44" s="75">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="S44" s="36"/>
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="S44" s="36">
+        <f t="shared" si="37"/>
+        <v>0</v>
+      </c>
       <c r="T44" s="36"/>
       <c r="U44" s="36"/>
       <c r="V44" s="36"/>
-      <c r="W44" s="36"/>
+      <c r="W44" s="36">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
       <c r="X44" s="36"/>
       <c r="Y44" s="36"/>
       <c r="Z44" s="36"/>
@@ -5729,123 +5852,123 @@
       <c r="F46" s="57"/>
       <c r="G46" s="57"/>
       <c r="H46" s="44">
-        <f t="shared" ref="H46:AK46" si="32">SUM(H40:H45)</f>
+        <f t="shared" ref="H46:AK46" si="40">SUM(H40:H45)</f>
         <v>0</v>
       </c>
       <c r="I46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="J46" s="76">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="K46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="L46" s="76">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="M46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="N46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="O46" s="76">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="P46" s="76">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="Q46" s="76">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="R46" s="76">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="S46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="T46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="U46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="V46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="W46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="X46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="Y46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="Z46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AA46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AB46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AC46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AD46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AE46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AF46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AG46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AH46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AI46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AJ46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AK46" s="44">
-        <f t="shared" si="32"/>
+        <f t="shared" si="40"/>
         <v>0</v>
       </c>
       <c r="AL46" s="96"/>
@@ -5905,37 +6028,43 @@
       <c r="H48" s="59"/>
       <c r="I48" s="59"/>
       <c r="J48" s="75">
-        <f t="shared" ref="J48:J59" si="33">H48+I48</f>
+        <f t="shared" ref="J48:J59" si="41">H48+I48</f>
         <v>0</v>
       </c>
       <c r="K48" s="59"/>
       <c r="L48" s="75">
-        <f t="shared" ref="L48:L59" si="34">J48-K48</f>
+        <f t="shared" ref="L48:L59" si="42">J48-K48</f>
         <v>0</v>
       </c>
       <c r="M48" s="59"/>
       <c r="N48" s="59"/>
       <c r="O48" s="75">
-        <f t="shared" ref="O48:O59" si="35">L48-M48</f>
+        <f t="shared" ref="O48:O59" si="43">L48-M48</f>
         <v>0</v>
       </c>
       <c r="P48" s="75">
-        <f t="shared" ref="P48:P59" si="36">K48-N48</f>
+        <f t="shared" ref="P48:P59" si="44">K48-N48</f>
         <v>0</v>
       </c>
       <c r="Q48" s="75">
-        <f t="shared" ref="Q48:Q59" si="37">M48+O48</f>
+        <f t="shared" ref="Q48:Q59" si="45">M48+O48</f>
         <v>0</v>
       </c>
       <c r="R48" s="75">
-        <f t="shared" ref="R48:R59" si="38">M48+N48+O48+P48</f>
-        <v>0</v>
-      </c>
-      <c r="S48" s="59"/>
+        <f t="shared" ref="R48:R59" si="46">M48+N48+O48+P48</f>
+        <v>0</v>
+      </c>
+      <c r="S48" s="36">
+        <f t="shared" ref="S48:S59" si="47">SUM(T48:V48)</f>
+        <v>0</v>
+      </c>
       <c r="T48" s="59"/>
       <c r="U48" s="59"/>
       <c r="V48" s="59"/>
-      <c r="W48" s="59"/>
+      <c r="W48" s="36">
+        <f t="shared" ref="W48:W59" si="48">SUM(X48:Y48)</f>
+        <v>0</v>
+      </c>
       <c r="X48" s="59"/>
       <c r="Y48" s="59"/>
       <c r="Z48" s="59"/>
@@ -5965,37 +6094,43 @@
       <c r="H49" s="59"/>
       <c r="I49" s="59"/>
       <c r="J49" s="75">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K49" s="59"/>
       <c r="L49" s="75">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="M49" s="59"/>
       <c r="N49" s="59"/>
       <c r="O49" s="75">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P49" s="75">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="Q49" s="75">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="R49" s="75">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="S49" s="59"/>
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="S49" s="36">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
       <c r="T49" s="59"/>
       <c r="U49" s="59"/>
       <c r="V49" s="59"/>
-      <c r="W49" s="59"/>
+      <c r="W49" s="36">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
       <c r="X49" s="59"/>
       <c r="Y49" s="59"/>
       <c r="Z49" s="59"/>
@@ -6025,37 +6160,43 @@
       <c r="H50" s="59"/>
       <c r="I50" s="59"/>
       <c r="J50" s="75">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K50" s="59"/>
       <c r="L50" s="75">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="M50" s="59"/>
       <c r="N50" s="59"/>
       <c r="O50" s="75">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P50" s="75">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="Q50" s="75">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="R50" s="75">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="S50" s="59"/>
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="S50" s="36">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
       <c r="T50" s="59"/>
       <c r="U50" s="59"/>
       <c r="V50" s="59"/>
-      <c r="W50" s="59"/>
+      <c r="W50" s="36">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
       <c r="X50" s="59"/>
       <c r="Y50" s="59"/>
       <c r="Z50" s="59"/>
@@ -6085,37 +6226,43 @@
       <c r="H51" s="59"/>
       <c r="I51" s="59"/>
       <c r="J51" s="75">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K51" s="59"/>
       <c r="L51" s="75">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="M51" s="59"/>
       <c r="N51" s="59"/>
       <c r="O51" s="75">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P51" s="75">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="Q51" s="75">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="R51" s="75">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="S51" s="59"/>
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="S51" s="36">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
       <c r="T51" s="59"/>
       <c r="U51" s="59"/>
       <c r="V51" s="59"/>
-      <c r="W51" s="59"/>
+      <c r="W51" s="36">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
       <c r="X51" s="59"/>
       <c r="Y51" s="59"/>
       <c r="Z51" s="59"/>
@@ -6145,37 +6292,43 @@
       <c r="H52" s="59"/>
       <c r="I52" s="59"/>
       <c r="J52" s="75">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K52" s="59"/>
       <c r="L52" s="75">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="M52" s="59"/>
       <c r="N52" s="59"/>
       <c r="O52" s="75">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P52" s="75">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="Q52" s="75">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="R52" s="75">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="S52" s="59"/>
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="S52" s="36">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
       <c r="T52" s="59"/>
       <c r="U52" s="59"/>
       <c r="V52" s="59"/>
-      <c r="W52" s="59"/>
+      <c r="W52" s="36">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
       <c r="X52" s="59"/>
       <c r="Y52" s="59"/>
       <c r="Z52" s="59"/>
@@ -6205,37 +6358,43 @@
       <c r="H53" s="59"/>
       <c r="I53" s="59"/>
       <c r="J53" s="75">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K53" s="59"/>
       <c r="L53" s="75">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="M53" s="59"/>
       <c r="N53" s="59"/>
       <c r="O53" s="75">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P53" s="75">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="Q53" s="75">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="R53" s="75">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="S53" s="59"/>
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="S53" s="36">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
       <c r="T53" s="59"/>
       <c r="U53" s="59"/>
       <c r="V53" s="59"/>
-      <c r="W53" s="59"/>
+      <c r="W53" s="36">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
       <c r="X53" s="59"/>
       <c r="Y53" s="59"/>
       <c r="Z53" s="59"/>
@@ -6265,37 +6424,43 @@
       <c r="H54" s="59"/>
       <c r="I54" s="59"/>
       <c r="J54" s="75">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K54" s="59"/>
       <c r="L54" s="75">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="M54" s="59"/>
       <c r="N54" s="59"/>
       <c r="O54" s="75">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P54" s="75">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="Q54" s="75">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="R54" s="75">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="S54" s="59"/>
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="S54" s="36">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
       <c r="T54" s="59"/>
       <c r="U54" s="59"/>
       <c r="V54" s="59"/>
-      <c r="W54" s="59"/>
+      <c r="W54" s="36">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
       <c r="X54" s="59"/>
       <c r="Y54" s="59"/>
       <c r="Z54" s="59"/>
@@ -6325,37 +6490,43 @@
       <c r="H55" s="59"/>
       <c r="I55" s="59"/>
       <c r="J55" s="75">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K55" s="59"/>
       <c r="L55" s="75">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="M55" s="59"/>
       <c r="N55" s="59"/>
       <c r="O55" s="75">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P55" s="75">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="Q55" s="75">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="R55" s="75">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="S55" s="59"/>
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="S55" s="36">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
       <c r="T55" s="59"/>
       <c r="U55" s="59"/>
       <c r="V55" s="59"/>
-      <c r="W55" s="59"/>
+      <c r="W55" s="36">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
       <c r="X55" s="59"/>
       <c r="Y55" s="59"/>
       <c r="Z55" s="59"/>
@@ -6385,37 +6556,43 @@
       <c r="H56" s="59"/>
       <c r="I56" s="59"/>
       <c r="J56" s="75">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K56" s="59"/>
       <c r="L56" s="75">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="M56" s="59"/>
       <c r="N56" s="59"/>
       <c r="O56" s="75">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P56" s="75">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="Q56" s="75">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="R56" s="75">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="S56" s="59"/>
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="S56" s="36">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
       <c r="T56" s="59"/>
       <c r="U56" s="59"/>
       <c r="V56" s="59"/>
-      <c r="W56" s="59"/>
+      <c r="W56" s="36">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
       <c r="X56" s="59"/>
       <c r="Y56" s="59"/>
       <c r="Z56" s="59"/>
@@ -6445,37 +6622,43 @@
       <c r="H57" s="59"/>
       <c r="I57" s="59"/>
       <c r="J57" s="75">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K57" s="59"/>
       <c r="L57" s="75">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="M57" s="59"/>
       <c r="N57" s="59"/>
       <c r="O57" s="75">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P57" s="75">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="Q57" s="75">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="R57" s="75">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="S57" s="59"/>
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="S57" s="36">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
       <c r="T57" s="59"/>
       <c r="U57" s="59"/>
       <c r="V57" s="59"/>
-      <c r="W57" s="59"/>
+      <c r="W57" s="36">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
       <c r="X57" s="59"/>
       <c r="Y57" s="59"/>
       <c r="Z57" s="59"/>
@@ -6505,37 +6688,43 @@
       <c r="H58" s="59"/>
       <c r="I58" s="59"/>
       <c r="J58" s="75">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K58" s="59"/>
       <c r="L58" s="75">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="M58" s="59"/>
       <c r="N58" s="59"/>
       <c r="O58" s="75">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P58" s="75">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="Q58" s="75">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="R58" s="75">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="S58" s="59"/>
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="S58" s="36">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
       <c r="T58" s="59"/>
       <c r="U58" s="59"/>
       <c r="V58" s="59"/>
-      <c r="W58" s="59"/>
+      <c r="W58" s="36">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
       <c r="X58" s="59"/>
       <c r="Y58" s="59"/>
       <c r="Z58" s="59"/>
@@ -6565,37 +6754,43 @@
       <c r="H59" s="59"/>
       <c r="I59" s="59"/>
       <c r="J59" s="75">
-        <f t="shared" si="33"/>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="K59" s="59"/>
       <c r="L59" s="75">
-        <f t="shared" si="34"/>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="M59" s="59"/>
       <c r="N59" s="59"/>
       <c r="O59" s="75">
-        <f t="shared" si="35"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="P59" s="75">
-        <f t="shared" si="36"/>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="Q59" s="75">
-        <f t="shared" si="37"/>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="R59" s="75">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="S59" s="59"/>
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="S59" s="36">
+        <f t="shared" si="47"/>
+        <v>0</v>
+      </c>
       <c r="T59" s="59"/>
       <c r="U59" s="59"/>
       <c r="V59" s="59"/>
-      <c r="W59" s="59"/>
+      <c r="W59" s="36">
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
       <c r="X59" s="59"/>
       <c r="Y59" s="59"/>
       <c r="Z59" s="59"/>
@@ -6665,123 +6860,123 @@
       <c r="F61" s="57"/>
       <c r="G61" s="57"/>
       <c r="H61" s="44">
-        <f t="shared" ref="H61:AK61" si="39">SUM(H48:H60)</f>
+        <f t="shared" ref="H61:AK61" si="49">SUM(H48:H60)</f>
         <v>0</v>
       </c>
       <c r="I61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="J61" s="76">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="K61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="L61" s="76">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="M61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="N61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="O61" s="76">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="P61" s="76">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="Q61" s="76">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="R61" s="76">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="S61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="T61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="U61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="V61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="W61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="X61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="Y61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="Z61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AA61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AB61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AC61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AD61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AE61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AF61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AG61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AH61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AI61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AJ61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AK61" s="44">
-        <f t="shared" si="39"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AL61" s="97"/>
@@ -6841,37 +7036,43 @@
       <c r="H63" s="36"/>
       <c r="I63" s="36"/>
       <c r="J63" s="75">
-        <f t="shared" ref="J63:J66" si="40">H63+I63</f>
+        <f t="shared" ref="J63:J66" si="50">H63+I63</f>
         <v>0</v>
       </c>
       <c r="K63" s="36"/>
       <c r="L63" s="75">
-        <f t="shared" ref="L63:L66" si="41">J63-K63</f>
+        <f t="shared" ref="L63:L66" si="51">J63-K63</f>
         <v>0</v>
       </c>
       <c r="M63" s="36"/>
       <c r="N63" s="36"/>
       <c r="O63" s="75">
-        <f t="shared" ref="O63:O66" si="42">L63-M63</f>
+        <f t="shared" ref="O63:O66" si="52">L63-M63</f>
         <v>0</v>
       </c>
       <c r="P63" s="75">
-        <f t="shared" ref="P63:P66" si="43">K63-N63</f>
+        <f t="shared" ref="P63:P66" si="53">K63-N63</f>
         <v>0</v>
       </c>
       <c r="Q63" s="75">
-        <f t="shared" ref="Q63:Q66" si="44">M63+O63</f>
+        <f t="shared" ref="Q63:Q66" si="54">M63+O63</f>
         <v>0</v>
       </c>
       <c r="R63" s="75">
-        <f t="shared" ref="R63:R66" si="45">M63+N63+O63+P63</f>
-        <v>0</v>
-      </c>
-      <c r="S63" s="36"/>
+        <f t="shared" ref="R63:R66" si="55">M63+N63+O63+P63</f>
+        <v>0</v>
+      </c>
+      <c r="S63" s="36">
+        <f t="shared" ref="S63:S66" si="56">SUM(T63:V63)</f>
+        <v>0</v>
+      </c>
       <c r="T63" s="36"/>
       <c r="U63" s="36"/>
       <c r="V63" s="36"/>
-      <c r="W63" s="36"/>
+      <c r="W63" s="36">
+        <f t="shared" ref="W63:W66" si="57">SUM(X63:Y63)</f>
+        <v>0</v>
+      </c>
       <c r="X63" s="36"/>
       <c r="Y63" s="36"/>
       <c r="Z63" s="36"/>
@@ -6901,37 +7102,43 @@
       <c r="H64" s="36"/>
       <c r="I64" s="36"/>
       <c r="J64" s="75">
-        <f t="shared" si="40"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="K64" s="36"/>
       <c r="L64" s="75">
-        <f t="shared" si="41"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M64" s="36"/>
       <c r="N64" s="36"/>
       <c r="O64" s="75">
-        <f t="shared" si="42"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="P64" s="75">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="Q64" s="75">
-        <f t="shared" si="44"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="R64" s="75">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="S64" s="36"/>
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="S64" s="36">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
       <c r="T64" s="36"/>
       <c r="U64" s="36"/>
       <c r="V64" s="36"/>
-      <c r="W64" s="36"/>
+      <c r="W64" s="36">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
       <c r="X64" s="36"/>
       <c r="Y64" s="36"/>
       <c r="Z64" s="36"/>
@@ -6961,37 +7168,43 @@
       <c r="H65" s="36"/>
       <c r="I65" s="36"/>
       <c r="J65" s="75">
-        <f t="shared" si="40"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="K65" s="36"/>
       <c r="L65" s="75">
-        <f t="shared" si="41"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M65" s="36"/>
       <c r="N65" s="36"/>
       <c r="O65" s="75">
-        <f t="shared" si="42"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="P65" s="75">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="Q65" s="75">
-        <f t="shared" si="44"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="R65" s="75">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="S65" s="36"/>
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="S65" s="36">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
       <c r="T65" s="36"/>
       <c r="U65" s="36"/>
       <c r="V65" s="36"/>
-      <c r="W65" s="36"/>
+      <c r="W65" s="36">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
       <c r="X65" s="36"/>
       <c r="Y65" s="36"/>
       <c r="Z65" s="36"/>
@@ -7021,37 +7234,43 @@
       <c r="H66" s="36"/>
       <c r="I66" s="36"/>
       <c r="J66" s="75">
-        <f t="shared" si="40"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="K66" s="36"/>
       <c r="L66" s="75">
-        <f t="shared" si="41"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="M66" s="36"/>
       <c r="N66" s="36"/>
       <c r="O66" s="75">
-        <f t="shared" si="42"/>
+        <f t="shared" si="52"/>
         <v>0</v>
       </c>
       <c r="P66" s="75">
-        <f t="shared" si="43"/>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="Q66" s="75">
-        <f t="shared" si="44"/>
+        <f t="shared" si="54"/>
         <v>0</v>
       </c>
       <c r="R66" s="75">
-        <f t="shared" si="45"/>
-        <v>0</v>
-      </c>
-      <c r="S66" s="36"/>
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="S66" s="36">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
       <c r="T66" s="36"/>
       <c r="U66" s="36"/>
       <c r="V66" s="36"/>
-      <c r="W66" s="36"/>
+      <c r="W66" s="36">
+        <f t="shared" si="57"/>
+        <v>0</v>
+      </c>
       <c r="X66" s="36"/>
       <c r="Y66" s="36"/>
       <c r="Z66" s="36"/>
@@ -7079,123 +7298,123 @@
       <c r="F67" s="53"/>
       <c r="G67" s="53"/>
       <c r="H67" s="44">
-        <f t="shared" ref="H67:AK67" si="46">SUM(H63:H66)</f>
+        <f t="shared" ref="H67:AK67" si="58">SUM(H63:H66)</f>
         <v>0</v>
       </c>
       <c r="I67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="J67" s="76">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="K67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="L67" s="76">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="M67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="N67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="O67" s="76">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="P67" s="76">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="Q67" s="76">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="R67" s="76">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="S67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="T67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="U67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="V67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="W67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="X67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="Y67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="Z67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AA67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AB67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AC67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AD67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AE67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AF67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AG67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AH67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AI67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AJ67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AK67" s="44">
-        <f t="shared" si="46"/>
+        <f t="shared" si="58"/>
         <v>0</v>
       </c>
       <c r="AL67" s="151"/>
@@ -7211,123 +7430,123 @@
       <c r="F68" s="57"/>
       <c r="G68" s="57"/>
       <c r="H68" s="44">
-        <f t="shared" ref="H68:AK68" si="47">H17+H23+H34+H38+H46+H61+H67</f>
+        <f t="shared" ref="H68:AK68" si="59">H17+H23+H34+H38+H46+H61+H67</f>
         <v>0</v>
       </c>
       <c r="I68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="J68" s="76">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="K68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="L68" s="76">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="M68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="N68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="O68" s="76">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="P68" s="76">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="Q68" s="76">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="R68" s="76">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="S68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="T68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="U68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="V68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="W68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="X68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="Y68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="Z68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="AA68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="AB68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="AC68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="AD68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="AE68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="AF68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="AG68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="AH68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="AI68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="AJ68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="AK68" s="44">
-        <f t="shared" si="47"/>
+        <f t="shared" si="59"/>
         <v>0</v>
       </c>
       <c r="AL68" s="151"/>
@@ -7347,12 +7566,12 @@
       <c r="H69" s="58"/>
       <c r="I69" s="58"/>
       <c r="J69" s="76">
-        <f t="shared" ref="J69:J76" si="48">H69+I69</f>
+        <f t="shared" ref="J69:J76" si="60">H69+I69</f>
         <v>0</v>
       </c>
       <c r="K69" s="58"/>
       <c r="L69" s="120">
-        <f t="shared" ref="L69:L75" si="49">J69-K69</f>
+        <f t="shared" ref="L69:L75" si="61">J69-K69</f>
         <v>0</v>
       </c>
       <c r="M69" s="36"/>
@@ -7362,22 +7581,28 @@
         <v>0</v>
       </c>
       <c r="P69" s="75">
-        <f t="shared" ref="P69:P72" si="50">K69-N69</f>
+        <f t="shared" ref="P69:P72" si="62">K69-N69</f>
         <v>0</v>
       </c>
       <c r="Q69" s="75">
-        <f t="shared" ref="Q69:Q72" si="51">M69+O69</f>
+        <f t="shared" ref="Q69:Q72" si="63">M69+O69</f>
         <v>0</v>
       </c>
       <c r="R69" s="75">
-        <f t="shared" ref="R69:R72" si="52">M69+N69+O69+P69</f>
-        <v>0</v>
-      </c>
-      <c r="S69" s="141"/>
+        <f t="shared" ref="R69:R72" si="64">M69+N69+O69+P69</f>
+        <v>0</v>
+      </c>
+      <c r="S69" s="36">
+        <f t="shared" ref="S69:S72" si="65">SUM(T69:V69)</f>
+        <v>0</v>
+      </c>
       <c r="T69" s="141"/>
       <c r="U69" s="141"/>
       <c r="V69" s="141"/>
-      <c r="W69" s="141"/>
+      <c r="W69" s="36">
+        <f t="shared" ref="W69:W72" si="66">SUM(X69:Y69)</f>
+        <v>0</v>
+      </c>
       <c r="X69" s="141"/>
       <c r="Y69" s="141"/>
       <c r="Z69" s="141"/>
@@ -7410,37 +7635,43 @@
       <c r="H70" s="58"/>
       <c r="I70" s="58"/>
       <c r="J70" s="76">
-        <f t="shared" si="48"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="K70" s="58"/>
       <c r="L70" s="120">
-        <f t="shared" si="49"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="M70" s="36"/>
       <c r="N70" s="36"/>
       <c r="O70" s="75">
-        <f t="shared" ref="O69:O72" si="53">L70-M70</f>
+        <f t="shared" ref="O69:O72" si="67">L70-M70</f>
         <v>0</v>
       </c>
       <c r="P70" s="75">
-        <f t="shared" si="50"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="Q70" s="75">
-        <f t="shared" si="51"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="R70" s="75">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="S70" s="141"/>
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="S70" s="36">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
       <c r="T70" s="141"/>
       <c r="U70" s="141"/>
       <c r="V70" s="141"/>
-      <c r="W70" s="141"/>
+      <c r="W70" s="36">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
       <c r="X70" s="141"/>
       <c r="Y70" s="141"/>
       <c r="Z70" s="141"/>
@@ -7470,37 +7701,43 @@
       <c r="H71" s="36"/>
       <c r="I71" s="36"/>
       <c r="J71" s="76">
-        <f t="shared" si="48"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="K71" s="36"/>
       <c r="L71" s="120">
-        <f t="shared" si="49"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="M71" s="36"/>
       <c r="N71" s="36"/>
       <c r="O71" s="75">
-        <f t="shared" si="53"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="P71" s="75">
-        <f t="shared" si="50"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="Q71" s="75">
-        <f t="shared" si="51"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="R71" s="75">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="S71" s="141"/>
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="S71" s="36">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
       <c r="T71" s="141"/>
       <c r="U71" s="141"/>
       <c r="V71" s="141"/>
-      <c r="W71" s="141"/>
+      <c r="W71" s="36">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
       <c r="X71" s="141"/>
       <c r="Y71" s="141"/>
       <c r="Z71" s="141"/>
@@ -7530,37 +7767,43 @@
       <c r="H72" s="36"/>
       <c r="I72" s="36"/>
       <c r="J72" s="76">
-        <f t="shared" si="48"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="K72" s="36"/>
       <c r="L72" s="120">
-        <f t="shared" si="49"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="M72" s="36"/>
       <c r="N72" s="36"/>
       <c r="O72" s="75">
-        <f t="shared" si="53"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="P72" s="75">
-        <f t="shared" si="50"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="Q72" s="75">
-        <f t="shared" si="51"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="R72" s="75">
-        <f t="shared" si="52"/>
-        <v>0</v>
-      </c>
-      <c r="S72" s="141"/>
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="S72" s="36">
+        <f t="shared" si="65"/>
+        <v>0</v>
+      </c>
       <c r="T72" s="141"/>
       <c r="U72" s="141"/>
       <c r="V72" s="141"/>
-      <c r="W72" s="141"/>
+      <c r="W72" s="36">
+        <f t="shared" si="66"/>
+        <v>0</v>
+      </c>
       <c r="X72" s="141"/>
       <c r="Y72" s="141"/>
       <c r="Z72" s="141"/>
@@ -7590,112 +7833,112 @@
       <c r="H73" s="44"/>
       <c r="I73" s="44"/>
       <c r="J73" s="76">
-        <f t="shared" si="48"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="K73" s="44"/>
       <c r="L73" s="121">
-        <f t="shared" si="49"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="M73" s="122">
-        <f t="shared" ref="M73:AK73" si="54">SUM(M74:M76)</f>
+        <f t="shared" ref="M73:AK73" si="68">SUM(M74:M76)</f>
         <v>0</v>
       </c>
       <c r="N73" s="122">
-        <f t="shared" si="54"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="O73" s="76">
-        <f t="shared" si="54"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="P73" s="76">
-        <f t="shared" si="54"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="Q73" s="76">
-        <f t="shared" si="54"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="R73" s="76">
-        <f t="shared" si="54"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="S73" s="122">
-        <f>SUM(S74:S76)</f>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="T73" s="122">
-        <f t="shared" si="54"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="U73" s="122">
-        <f t="shared" si="54"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="V73" s="122">
-        <f t="shared" si="54"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="W73" s="122">
-        <f t="shared" si="54"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="X73" s="122">
-        <f t="shared" si="54"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="Y73" s="122">
-        <f t="shared" si="54"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="Z73" s="122">
-        <f t="shared" si="54"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AA73" s="122">
-        <f t="shared" si="54"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AB73" s="122">
-        <f t="shared" si="54"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AC73" s="122">
-        <f t="shared" si="54"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AD73" s="122">
-        <f t="shared" si="54"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AE73" s="122">
-        <f t="shared" si="54"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AF73" s="122">
-        <f t="shared" si="54"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AG73" s="122">
-        <f t="shared" si="54"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AH73" s="122">
-        <f t="shared" si="54"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AI73" s="122">
-        <f t="shared" si="54"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AJ73" s="122">
-        <f t="shared" si="54"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AK73" s="122">
-        <f t="shared" si="54"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="AL73" s="151"/>
@@ -7713,37 +7956,43 @@
       <c r="H74" s="36"/>
       <c r="I74" s="36"/>
       <c r="J74" s="76">
-        <f t="shared" si="48"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="K74" s="36"/>
       <c r="L74" s="120">
-        <f t="shared" si="49"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="M74" s="36"/>
       <c r="N74" s="36"/>
       <c r="O74" s="75">
-        <f t="shared" ref="O74:O76" si="55">L74-M74</f>
+        <f t="shared" ref="O74:O76" si="69">L74-M74</f>
         <v>0</v>
       </c>
       <c r="P74" s="75">
-        <f t="shared" ref="P74:P76" si="56">K74-N74</f>
+        <f t="shared" ref="P74:P76" si="70">K74-N74</f>
         <v>0</v>
       </c>
       <c r="Q74" s="75">
-        <f t="shared" ref="Q74:Q76" si="57">M74+O74</f>
+        <f t="shared" ref="Q74:Q76" si="71">M74+O74</f>
         <v>0</v>
       </c>
       <c r="R74" s="75">
-        <f t="shared" ref="R74:R76" si="58">M74+N74+O74+P74</f>
-        <v>0</v>
-      </c>
-      <c r="S74" s="141"/>
+        <f t="shared" ref="R74:R76" si="72">M74+N74+O74+P74</f>
+        <v>0</v>
+      </c>
+      <c r="S74" s="36">
+        <f t="shared" ref="S74:S76" si="73">SUM(T74:V74)</f>
+        <v>0</v>
+      </c>
       <c r="T74" s="141"/>
       <c r="U74" s="141"/>
       <c r="V74" s="141"/>
-      <c r="W74" s="141"/>
+      <c r="W74" s="36">
+        <f t="shared" ref="W74:W76" si="74">SUM(X74:Y74)</f>
+        <v>0</v>
+      </c>
       <c r="X74" s="141"/>
       <c r="Y74" s="141"/>
       <c r="Z74" s="141"/>
@@ -7773,7 +8022,7 @@
       <c r="H75" s="36"/>
       <c r="I75" s="36"/>
       <c r="J75" s="76">
-        <f t="shared" si="48"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="K75" s="36"/>
@@ -7781,26 +8030,32 @@
       <c r="M75" s="36"/>
       <c r="N75" s="36"/>
       <c r="O75" s="75">
-        <f t="shared" si="55"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="P75" s="75">
-        <f t="shared" si="56"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="Q75" s="75">
-        <f t="shared" si="57"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="R75" s="75">
-        <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-      <c r="S75" s="141"/>
+        <f t="shared" si="72"/>
+        <v>0</v>
+      </c>
+      <c r="S75" s="36">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
       <c r="T75" s="141"/>
       <c r="U75" s="141"/>
       <c r="V75" s="141"/>
-      <c r="W75" s="141"/>
+      <c r="W75" s="36">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
       <c r="X75" s="141"/>
       <c r="Y75" s="141"/>
       <c r="Z75" s="141"/>
@@ -7830,7 +8085,7 @@
       <c r="H76" s="36"/>
       <c r="I76" s="36"/>
       <c r="J76" s="76">
-        <f t="shared" si="48"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="K76" s="36"/>
@@ -7838,26 +8093,32 @@
       <c r="M76" s="36"/>
       <c r="N76" s="36"/>
       <c r="O76" s="75">
-        <f t="shared" si="55"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="P76" s="75">
-        <f t="shared" si="56"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="Q76" s="75">
-        <f t="shared" si="57"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="R76" s="75">
-        <f t="shared" si="58"/>
-        <v>0</v>
-      </c>
-      <c r="S76" s="141"/>
+        <f t="shared" si="72"/>
+        <v>0</v>
+      </c>
+      <c r="S76" s="36">
+        <f t="shared" si="73"/>
+        <v>0</v>
+      </c>
       <c r="T76" s="141"/>
       <c r="U76" s="141"/>
       <c r="V76" s="141"/>
-      <c r="W76" s="141"/>
+      <c r="W76" s="36">
+        <f t="shared" si="74"/>
+        <v>0</v>
+      </c>
       <c r="X76" s="141"/>
       <c r="Y76" s="141"/>
       <c r="Z76" s="141"/>
@@ -7874,7 +8135,7 @@
       <c r="AK76" s="83"/>
       <c r="AL76" s="97"/>
     </row>
-    <row r="77" s="1" customFormat="1" ht="14" spans="1:38">
+    <row r="77" s="1" customFormat="1" ht="26" spans="1:38">
       <c r="A77" s="41"/>
       <c r="B77" s="42"/>
       <c r="C77" s="42"/>
@@ -7884,79 +8145,127 @@
       <c r="E77" s="54"/>
       <c r="F77" s="54"/>
       <c r="G77" s="54"/>
-      <c r="H77" s="44" t="e">
-        <f>H68+H69+H70+H71+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I77" s="44" t="e">
-        <f>I68+I69+I70+I71+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="J77" s="123" t="e">
-        <f>J68+J69+J70+J71+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="K77" s="44" t="e">
-        <f>K68+K69+K70+K71+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="L77" s="124" t="e">
-        <f>L68+L69+L70+L71+#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="M77" s="124">
-        <f>M68+M69+M70+M71</f>
-        <v>0</v>
-      </c>
-      <c r="N77" s="124">
-        <f t="shared" ref="M77:S77" si="59">N68+N69+N70+N71</f>
-        <v>0</v>
-      </c>
-      <c r="O77" s="125">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="P77" s="124">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="Q77" s="124">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="R77" s="124">
-        <f t="shared" si="59"/>
-        <v>0</v>
-      </c>
-      <c r="S77" s="122">
-        <f>S68+S69+S70+S71</f>
-        <v>0</v>
-      </c>
-      <c r="T77" s="122"/>
-      <c r="U77" s="122"/>
-      <c r="V77" s="122"/>
-      <c r="W77" s="122"/>
-      <c r="X77" s="122"/>
-      <c r="Y77" s="122"/>
-      <c r="Z77" s="122">
-        <f>Z68+Z69+Z70+Z71</f>
-        <v>0</v>
-      </c>
-      <c r="AA77" s="122">
-        <f>AA68+AA69+AA70+AA71</f>
-        <v>0</v>
-      </c>
-      <c r="AB77" s="145"/>
-      <c r="AC77" s="145"/>
-      <c r="AD77" s="145"/>
-      <c r="AE77" s="145"/>
-      <c r="AF77" s="145"/>
-      <c r="AG77" s="145"/>
-      <c r="AH77" s="145"/>
-      <c r="AI77" s="145"/>
-      <c r="AJ77" s="145"/>
-      <c r="AK77" s="152"/>
-      <c r="AL77" s="153"/>
+      <c r="H77" s="44">
+        <f t="shared" ref="H77:AK77" si="75">H68+H69+H70+H71+H72+H73</f>
+        <v>0</v>
+      </c>
+      <c r="I77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="J77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="K77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="L77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="M77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="N77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="O77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="P77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="Q77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="R77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="S77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="T77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="U77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="V77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="W77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="X77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="Y77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="Z77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="AA77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="AB77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="AC77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="AD77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="AE77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="AF77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="AG77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="AH77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="AI77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="AJ77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="AK77" s="44">
+        <f t="shared" si="75"/>
+        <v>0</v>
+      </c>
+      <c r="AL77" s="152"/>
     </row>
     <row r="78" s="1" customFormat="1" ht="26" spans="1:38">
       <c r="A78" s="41"/>
@@ -7996,11 +8305,17 @@
         <f>N78+P78</f>
         <v>0</v>
       </c>
-      <c r="S78" s="122"/>
+      <c r="S78" s="44">
+        <f>SUM(T78:V78)</f>
+        <v>0</v>
+      </c>
       <c r="T78" s="122"/>
       <c r="U78" s="122"/>
       <c r="V78" s="122"/>
-      <c r="W78" s="122"/>
+      <c r="W78" s="122">
+        <f>SUM(X78:Y78)</f>
+        <v>0</v>
+      </c>
       <c r="X78" s="122"/>
       <c r="Y78" s="122"/>
       <c r="Z78" s="122"/>
@@ -8014,8 +8329,8 @@
       <c r="AH78" s="145"/>
       <c r="AI78" s="145"/>
       <c r="AJ78" s="145"/>
-      <c r="AK78" s="152"/>
-      <c r="AL78" s="153"/>
+      <c r="AK78" s="153"/>
+      <c r="AL78" s="152"/>
     </row>
     <row r="79" s="1" customFormat="1" ht="26" spans="1:38">
       <c r="A79" s="41"/>
@@ -8055,11 +8370,17 @@
         <f>Q79</f>
         <v>0</v>
       </c>
-      <c r="S79" s="122"/>
+      <c r="S79" s="44">
+        <f>SUM(T79:V79)</f>
+        <v>0</v>
+      </c>
       <c r="T79" s="122"/>
       <c r="U79" s="122"/>
       <c r="V79" s="122"/>
-      <c r="W79" s="122"/>
+      <c r="W79" s="122">
+        <f>SUM(X79:Y79)</f>
+        <v>0</v>
+      </c>
       <c r="X79" s="122"/>
       <c r="Y79" s="122"/>
       <c r="Z79" s="122"/>
@@ -8073,8 +8394,8 @@
       <c r="AH79" s="145"/>
       <c r="AI79" s="145"/>
       <c r="AJ79" s="145"/>
-      <c r="AK79" s="152"/>
-      <c r="AL79" s="153"/>
+      <c r="AK79" s="153"/>
+      <c r="AL79" s="152"/>
     </row>
     <row r="80" s="1" customFormat="1" ht="14" spans="1:38">
       <c r="A80" s="41"/>
@@ -8088,9 +8409,9 @@
       <c r="G80" s="54"/>
       <c r="H80" s="44"/>
       <c r="I80" s="44"/>
-      <c r="J80" s="123" t="e">
+      <c r="J80" s="123">
         <f>J6-J77-J78-J79</f>
-        <v>#REF!</v>
+        <v>0</v>
       </c>
       <c r="K80" s="44"/>
       <c r="L80" s="124"/>
@@ -8118,8 +8439,8 @@
       <c r="AH80" s="145"/>
       <c r="AI80" s="145"/>
       <c r="AJ80" s="145"/>
-      <c r="AK80" s="152"/>
-      <c r="AL80" s="153"/>
+      <c r="AK80" s="153"/>
+      <c r="AL80" s="152"/>
     </row>
     <row r="81" s="3" customFormat="1" ht="14" spans="1:38">
       <c r="A81" s="101"/>
@@ -8134,16 +8455,16 @@
       <c r="H81" s="105"/>
       <c r="I81" s="105"/>
       <c r="J81" s="105" t="e">
-        <f t="shared" ref="J81:M81" si="60">J80/J6</f>
-        <v>#REF!</v>
+        <f t="shared" ref="J81:M81" si="76">J80/J6</f>
+        <v>#DIV/0!</v>
       </c>
       <c r="K81" s="105"/>
       <c r="L81" s="126" t="e">
-        <f t="shared" si="60"/>
+        <f t="shared" si="76"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M81" s="126" t="e">
-        <f t="shared" si="60"/>
+        <f t="shared" si="76"/>
         <v>#DIV/0!</v>
       </c>
       <c r="N81" s="126"/>
@@ -8178,7 +8499,7 @@
       <c r="AK81" s="154"/>
       <c r="AL81" s="155"/>
     </row>
-    <row r="82" ht="14" spans="1:38">
+    <row r="82" spans="1:38">
       <c r="A82" s="106"/>
       <c r="B82" s="107"/>
       <c r="C82" s="107"/>
@@ -8200,8 +8521,13 @@
       <c r="O82" s="130"/>
       <c r="P82" s="130"/>
       <c r="Q82" s="130"/>
-      <c r="R82" s="130"/>
-      <c r="S82" s="130"/>
+      <c r="R82" s="130" t="s">
+        <v>64</v>
+      </c>
+      <c r="S82" s="130">
+        <f>S77+S78+S79</f>
+        <v>0</v>
+      </c>
       <c r="T82" s="130"/>
       <c r="U82" s="130"/>
       <c r="V82" s="130"/>
@@ -8222,7 +8548,7 @@
       <c r="AK82" s="148"/>
       <c r="AL82" s="156"/>
     </row>
-    <row r="83" ht="14" spans="1:38">
+    <row r="83" spans="1:38">
       <c r="A83" s="106"/>
       <c r="B83" s="107"/>
       <c r="C83" s="107"/>
